--- a/data/results.xlsx
+++ b/data/results.xlsx
@@ -985,19 +985,19 @@
         <v>103.46</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AA2" s="2" t="n">
         <v>102.85</v>
@@ -1227,19 +1227,19 @@
         <v>97.91</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>1.84</v>
+        <v>1.3</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>1.01</v>
+        <v>0.9</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="AA3" s="2" t="n">
         <v>101.22</v>
@@ -1471,19 +1471,19 @@
         <v>94.44</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>1.44</v>
+        <v>1.02</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>0.93</v>
+        <v>0.83</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AA4" s="2" t="n">
         <v>101.99</v>
@@ -1715,19 +1715,19 @@
         <v>104.35</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AA5" s="2" t="n">
         <v>103.57</v>
@@ -1959,19 +1959,19 @@
         <v>106.9</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>1.12</v>
+        <v>0.79</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>2.87</v>
+        <v>2.73</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>3.32</v>
+        <v>3.21</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="AA6" s="2" t="n">
         <v>103.14</v>
@@ -2203,19 +2203,19 @@
         <v>96.14</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.57</v>
+        <v>0.51</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AA7" s="2" t="n">
         <v>103.88</v>
@@ -2449,19 +2449,19 @@
         <v>94.79000000000001</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.31</v>
+        <v>0.22</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="AA8" s="2" t="n">
         <v>100.39</v>
@@ -2695,19 +2695,19 @@
         <v>81.22</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>0.41</v>
+        <v>0.37</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>7.41</v>
+        <v>7.16</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>8.380000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="AA9" s="2" t="n">
         <v>100.35</v>
@@ -2941,19 +2941,19 @@
         <v>98.14</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.54</v>
+        <v>0.38</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AA10" s="2" t="n">
         <v>100.92</v>
@@ -3187,19 +3187,19 @@
         <v>99.34</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>1.04</v>
+        <v>0.73</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>0.84</v>
+        <v>0.75</v>
       </c>
       <c r="X11" s="2" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Y11" s="2" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z11" s="2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AA11" s="2" t="n">
         <v>98.13</v>
@@ -3433,19 +3433,19 @@
         <v>100.77</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>1.12</v>
+        <v>0.79</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>0.96</v>
+        <v>0.86</v>
       </c>
       <c r="X12" s="2" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Y12" s="2" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="Z12" s="2" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AA12" s="2" t="n">
         <v>100.11</v>
@@ -3679,19 +3679,19 @@
         <v>87.75</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>1.31</v>
+        <v>0.93</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="X13" s="2" t="n">
-        <v>5.49</v>
+        <v>5.21</v>
       </c>
       <c r="Y13" s="2" t="n">
-        <v>7.41</v>
+        <v>7.15</v>
       </c>
       <c r="Z13" s="2" t="n">
-        <v>7.25</v>
+        <v>7.07</v>
       </c>
       <c r="AA13" s="2" t="n">
         <v>101.55</v>
@@ -3925,19 +3925,19 @@
         <v>89.77</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>1.18</v>
+        <v>0.83</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>0.88</v>
+        <v>0.79</v>
       </c>
       <c r="X14" s="2" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="Y14" s="2" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="Z14" s="2" t="n">
-        <v>3.49</v>
+        <v>3.4</v>
       </c>
       <c r="AA14" s="2" t="n">
         <v>102.05</v>
@@ -4171,19 +4171,19 @@
         <v>91.98</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>0.84</v>
+        <v>0.59</v>
       </c>
       <c r="W15" s="2" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="X15" s="2" t="n">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="Y15" s="2" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="Z15" s="2" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="AA15" s="2" t="n">
         <v>104.27</v>
@@ -4417,19 +4417,19 @@
         <v>93.77</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>0.51</v>
+        <v>0.36</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="Z16" s="2" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="AA16" s="2" t="n">
         <v>108.53</v>
@@ -4663,19 +4663,19 @@
         <v>84.14</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>1.01</v>
+        <v>0.72</v>
       </c>
       <c r="W17" s="2" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="X17" s="2" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="Y17" s="2" t="n">
-        <v>5.64</v>
+        <v>5.45</v>
       </c>
       <c r="Z17" s="2" t="n">
-        <v>7.75</v>
+        <v>7.55</v>
       </c>
       <c r="AA17" s="2" t="n">
         <v>104.16</v>
@@ -4909,19 +4909,19 @@
         <v>105.69</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="W18" s="2" t="n">
-        <v>3.94</v>
+        <v>3.53</v>
       </c>
       <c r="X18" s="2" t="n">
-        <v>3.46</v>
+        <v>3.28</v>
       </c>
       <c r="Y18" s="2" t="n">
-        <v>3.61</v>
+        <v>3.49</v>
       </c>
       <c r="Z18" s="2" t="n">
-        <v>5.51</v>
+        <v>5.37</v>
       </c>
       <c r="AA18" s="2" t="n">
         <v>101.59</v>
@@ -5155,19 +5155,19 @@
         <v>108.02</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>0.28</v>
+        <v>0.2</v>
       </c>
       <c r="W19" s="2" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="X19" s="2" t="n">
-        <v>3.69</v>
+        <v>3.5</v>
       </c>
       <c r="Y19" s="2" t="n">
-        <v>3.56</v>
+        <v>3.44</v>
       </c>
       <c r="Z19" s="2" t="n">
-        <v>4.06</v>
+        <v>3.96</v>
       </c>
       <c r="AA19" s="2" t="n">
         <v>101.78</v>
@@ -5401,19 +5401,19 @@
         <v>90.92</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="W20" s="2" t="n">
-        <v>2.59</v>
+        <v>2.32</v>
       </c>
       <c r="X20" s="2" t="n">
-        <v>2.56</v>
+        <v>2.43</v>
       </c>
       <c r="Y20" s="2" t="n">
-        <v>3.65</v>
+        <v>3.53</v>
       </c>
       <c r="Z20" s="2" t="n">
-        <v>4.42</v>
+        <v>4.3</v>
       </c>
       <c r="AA20" s="2" t="n">
         <v>107.01</v>
@@ -5647,19 +5647,19 @@
         <v>106.96</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="W21" s="2" t="n">
-        <v>11.44</v>
+        <v>10.23</v>
       </c>
       <c r="X21" s="2" t="n">
-        <v>8.960000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="Y21" s="2" t="n">
-        <v>7.36</v>
+        <v>7.11</v>
       </c>
       <c r="Z21" s="2" t="n">
-        <v>7.44</v>
+        <v>7.25</v>
       </c>
       <c r="AA21" s="2" t="n">
         <v>101.77</v>
@@ -5893,19 +5893,19 @@
         <v>102.41</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>0.72</v>
+        <v>0.51</v>
       </c>
       <c r="W22" s="2" t="n">
-        <v>2.19</v>
+        <v>1.96</v>
       </c>
       <c r="X22" s="2" t="n">
-        <v>3.34</v>
+        <v>3.16</v>
       </c>
       <c r="Y22" s="2" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="Z22" s="2" t="n">
-        <v>3.79</v>
+        <v>3.69</v>
       </c>
       <c r="AA22" s="2" t="n">
         <v>107.14</v>
@@ -6139,19 +6139,19 @@
         <v>89.73</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>0.86</v>
+        <v>0.61</v>
       </c>
       <c r="W23" s="2" t="n">
-        <v>2.01</v>
+        <v>1.79</v>
       </c>
       <c r="X23" s="2" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="Y23" s="2" t="n">
-        <v>4.11</v>
+        <v>3.98</v>
       </c>
       <c r="Z23" s="2" t="n">
-        <v>3.91</v>
+        <v>3.81</v>
       </c>
       <c r="AA23" s="2" t="n">
         <v>104.24</v>
@@ -6385,19 +6385,19 @@
         <v>85.93000000000001</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>0.95</v>
+        <v>0.67</v>
       </c>
       <c r="W24" s="2" t="n">
-        <v>0.92</v>
+        <v>0.82</v>
       </c>
       <c r="X24" s="2" t="n">
-        <v>2.81</v>
+        <v>2.67</v>
       </c>
       <c r="Y24" s="2" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="Z24" s="2" t="n">
-        <v>5.28</v>
+        <v>5.15</v>
       </c>
       <c r="AA24" s="2" t="n">
         <v>99.18000000000001</v>
@@ -6631,19 +6631,19 @@
         <v>105.21</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>2.16</v>
+        <v>1.53</v>
       </c>
       <c r="W25" s="2" t="n">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="X25" s="2" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="Y25" s="2" t="n">
-        <v>2.66</v>
+        <v>2.57</v>
       </c>
       <c r="Z25" s="2" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="AA25" s="2" t="n">
         <v>110.46</v>
@@ -6877,19 +6877,19 @@
         <v>95.28</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>1.29</v>
+        <v>0.91</v>
       </c>
       <c r="W26" s="2" t="n">
-        <v>2.59</v>
+        <v>2.32</v>
       </c>
       <c r="X26" s="2" t="n">
-        <v>3.34</v>
+        <v>3.17</v>
       </c>
       <c r="Y26" s="2" t="n">
-        <v>3.01</v>
+        <v>2.91</v>
       </c>
       <c r="Z26" s="2" t="n">
-        <v>3.66</v>
+        <v>3.57</v>
       </c>
       <c r="AA26" s="2" t="n">
         <v>97.51000000000001</v>
@@ -7123,19 +7123,19 @@
         <v>118.27</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>0.45</v>
+        <v>0.32</v>
       </c>
       <c r="W27" s="2" t="n">
-        <v>1.02</v>
+        <v>0.92</v>
       </c>
       <c r="X27" s="2" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="Y27" s="2" t="n">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="Z27" s="2" t="n">
-        <v>5.1</v>
+        <v>4.97</v>
       </c>
       <c r="AA27" s="2" t="n">
         <v>102.98</v>
@@ -7369,19 +7369,19 @@
         <v>118.98</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>0.67</v>
+        <v>0.47</v>
       </c>
       <c r="W28" s="2" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="X28" s="2" t="n">
-        <v>3.84</v>
+        <v>3.64</v>
       </c>
       <c r="Y28" s="2" t="n">
-        <v>6.41</v>
+        <v>6.19</v>
       </c>
       <c r="Z28" s="2" t="n">
-        <v>7.37</v>
+        <v>7.18</v>
       </c>
       <c r="AA28" s="2" t="n">
         <v>106.15</v>
@@ -7615,19 +7615,19 @@
         <v>111.03</v>
       </c>
       <c r="V29" s="2" t="n">
-        <v>1.1</v>
+        <v>0.78</v>
       </c>
       <c r="W29" s="2" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="X29" s="2" t="n">
-        <v>2.51</v>
+        <v>2.39</v>
       </c>
       <c r="Y29" s="2" t="n">
-        <v>4.05</v>
+        <v>3.91</v>
       </c>
       <c r="Z29" s="2" t="n">
-        <v>4.53</v>
+        <v>4.41</v>
       </c>
       <c r="AA29" s="2" t="n">
         <v>98.64</v>
@@ -7861,19 +7861,19 @@
         <v>116.45</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>1.38</v>
+        <v>0.97</v>
       </c>
       <c r="W30" s="2" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="X30" s="2" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="Y30" s="2" t="n">
-        <v>3.58</v>
+        <v>3.46</v>
       </c>
       <c r="Z30" s="2" t="n">
-        <v>5.03</v>
+        <v>4.91</v>
       </c>
       <c r="AA30" s="2" t="n">
         <v>103.51</v>
@@ -8107,19 +8107,19 @@
         <v>106.97</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>2.28</v>
+        <v>1.61</v>
       </c>
       <c r="W31" s="2" t="n">
-        <v>3.48</v>
+        <v>3.11</v>
       </c>
       <c r="X31" s="2" t="n">
-        <v>3.43</v>
+        <v>3.26</v>
       </c>
       <c r="Y31" s="2" t="n">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
       <c r="Z31" s="2" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="AA31" s="2" t="n">
         <v>98.22</v>
@@ -8353,19 +8353,19 @@
         <v>96.97</v>
       </c>
       <c r="V32" s="2" t="n">
-        <v>0.48</v>
+        <v>0.34</v>
       </c>
       <c r="W32" s="2" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="X32" s="2" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="Y32" s="2" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="Z32" s="2" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="AA32" s="2" t="n">
         <v>98.34</v>
@@ -8599,19 +8599,19 @@
         <v>119.62</v>
       </c>
       <c r="V33" s="2" t="n">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="W33" s="2" t="n">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="X33" s="2" t="n">
-        <v>5.73</v>
+        <v>5.44</v>
       </c>
       <c r="Y33" s="2" t="n">
-        <v>6.47</v>
+        <v>6.26</v>
       </c>
       <c r="Z33" s="2" t="n">
-        <v>6.89</v>
+        <v>6.72</v>
       </c>
       <c r="AA33" s="2" t="n">
         <v>100.02</v>
@@ -8845,19 +8845,19 @@
         <v>107.57</v>
       </c>
       <c r="V34" s="2" t="n">
-        <v>2.18</v>
+        <v>1.54</v>
       </c>
       <c r="W34" s="2" t="n">
-        <v>2.21</v>
+        <v>1.98</v>
       </c>
       <c r="X34" s="2" t="n">
-        <v>3.39</v>
+        <v>3.21</v>
       </c>
       <c r="Y34" s="2" t="n">
-        <v>4.18</v>
+        <v>4.04</v>
       </c>
       <c r="Z34" s="2" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="AA34" s="2" t="n">
         <v>100.32</v>
@@ -9091,19 +9091,19 @@
         <v>107.09</v>
       </c>
       <c r="V35" s="2" t="n">
-        <v>3.04</v>
+        <v>2.15</v>
       </c>
       <c r="W35" s="2" t="n">
-        <v>2.41</v>
+        <v>2.15</v>
       </c>
       <c r="X35" s="2" t="n">
-        <v>3.07</v>
+        <v>2.91</v>
       </c>
       <c r="Y35" s="2" t="n">
-        <v>3.07</v>
+        <v>2.97</v>
       </c>
       <c r="Z35" s="2" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="AA35" s="2" t="n">
         <v>98.48</v>
@@ -9337,19 +9337,19 @@
         <v>113.69</v>
       </c>
       <c r="V36" s="2" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="W36" s="2" t="n">
-        <v>0.79</v>
+        <v>0.71</v>
       </c>
       <c r="X36" s="2" t="n">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="Y36" s="2" t="n">
-        <v>3.98</v>
+        <v>3.84</v>
       </c>
       <c r="Z36" s="2" t="n">
-        <v>4.82</v>
+        <v>4.7</v>
       </c>
       <c r="AA36" s="2" t="n">
         <v>99.03</v>
@@ -9583,19 +9583,19 @@
         <v>105.32</v>
       </c>
       <c r="V37" s="2" t="n">
-        <v>0.66</v>
+        <v>0.47</v>
       </c>
       <c r="W37" s="2" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="X37" s="2" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="Y37" s="2" t="n">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="Z37" s="2" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AA37" s="2" t="n">
         <v>96.94</v>
@@ -9829,19 +9829,19 @@
         <v>114.7</v>
       </c>
       <c r="V38" s="2" t="n">
-        <v>1.26</v>
+        <v>0.89</v>
       </c>
       <c r="W38" s="2" t="n">
-        <v>2.73</v>
+        <v>2.44</v>
       </c>
       <c r="X38" s="2" t="n">
-        <v>5.88</v>
+        <v>5.58</v>
       </c>
       <c r="Y38" s="2" t="n">
-        <v>6.2</v>
+        <v>5.99</v>
       </c>
       <c r="Z38" s="2" t="n">
-        <v>6.04</v>
+        <v>5.89</v>
       </c>
       <c r="AA38" s="2" t="n">
         <v>99.59999999999999</v>
@@ -10075,19 +10075,19 @@
         <v>106.77</v>
       </c>
       <c r="V39" s="2" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="W39" s="2" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="X39" s="2" t="n">
-        <v>3.12</v>
+        <v>2.96</v>
       </c>
       <c r="Y39" s="2" t="n">
-        <v>3.68</v>
+        <v>3.55</v>
       </c>
       <c r="Z39" s="2" t="n">
-        <v>3.26</v>
+        <v>3.17</v>
       </c>
       <c r="AA39" s="2" t="n">
         <v>101.67</v>
@@ -10321,19 +10321,19 @@
         <v>123.41</v>
       </c>
       <c r="V40" s="2" t="n">
-        <v>1.15</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="W40" s="2" t="n">
-        <v>1.08</v>
+        <v>0.97</v>
       </c>
       <c r="X40" s="2" t="n">
-        <v>5.03</v>
+        <v>4.77</v>
       </c>
       <c r="Y40" s="2" t="n">
-        <v>6.59</v>
+        <v>6.36</v>
       </c>
       <c r="Z40" s="2" t="n">
-        <v>7.33</v>
+        <v>7.14</v>
       </c>
       <c r="AA40" s="2" t="n">
         <v>106.22</v>
@@ -10567,19 +10567,19 @@
         <v>110.6</v>
       </c>
       <c r="V41" s="2" t="n">
-        <v>0.55</v>
+        <v>0.39</v>
       </c>
       <c r="W41" s="2" t="n">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="X41" s="2" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="Y41" s="2" t="n">
-        <v>2.58</v>
+        <v>2.49</v>
       </c>
       <c r="Z41" s="2" t="n">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="AA41" s="2" t="n">
         <v>106.39</v>
@@ -10813,19 +10813,19 @@
         <v>118.27</v>
       </c>
       <c r="V42" s="2" t="n">
-        <v>0.45</v>
+        <v>0.32</v>
       </c>
       <c r="W42" s="2" t="n">
-        <v>1.02</v>
+        <v>0.92</v>
       </c>
       <c r="X42" s="2" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="Y42" s="2" t="n">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="Z42" s="2" t="n">
-        <v>5.1</v>
+        <v>4.97</v>
       </c>
       <c r="AA42" s="2" t="n">
         <v>102.98</v>
@@ -11059,19 +11059,19 @@
         <v>130.13</v>
       </c>
       <c r="V43" s="2" t="n">
-        <v>1.34</v>
+        <v>0.95</v>
       </c>
       <c r="W43" s="2" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="X43" s="2" t="n">
-        <v>4.17</v>
+        <v>3.96</v>
       </c>
       <c r="Y43" s="2" t="n">
-        <v>6.73</v>
+        <v>6.5</v>
       </c>
       <c r="Z43" s="2" t="n">
-        <v>11.81</v>
+        <v>11.51</v>
       </c>
       <c r="AA43" s="2" t="n">
         <v>107.62</v>
@@ -11305,19 +11305,19 @@
         <v>106.78</v>
       </c>
       <c r="V44" s="2" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="W44" s="2" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="X44" s="2" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="Y44" s="2" t="n">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="Z44" s="2" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="AA44" s="2" t="n">
         <v>100.18</v>
@@ -11551,19 +11551,19 @@
         <v>100.77</v>
       </c>
       <c r="V45" s="2" t="n">
-        <v>1.12</v>
+        <v>0.79</v>
       </c>
       <c r="W45" s="2" t="n">
-        <v>0.96</v>
+        <v>0.86</v>
       </c>
       <c r="X45" s="2" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Y45" s="2" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="Z45" s="2" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AA45" s="2" t="n">
         <v>100.11</v>
@@ -11797,19 +11797,19 @@
         <v>103.49</v>
       </c>
       <c r="V46" s="2" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="W46" s="2" t="n">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="X46" s="2" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="Y46" s="2" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="Z46" s="2" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AA46" s="2" t="n">
         <v>101.93</v>

--- a/data/results.xlsx
+++ b/data/results.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE11"/>
+  <dimension ref="A1:CE39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2.2</v>
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2.9</v>
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2.46</v>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2.14</v>
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>1.52</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>1.64</v>
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2.03</v>
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2.21</v>
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2.24</v>
@@ -3241,7 +3241,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2.9</v>
@@ -3481,6 +3481,7144 @@
         <v>0</v>
       </c>
       <c r="CE11" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>101.64</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>101.67</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>98.58</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>101.57</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>60.08</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>100.12</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>106.83</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>100.72</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>98.39</v>
+      </c>
+      <c r="U12" s="2" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="V12" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="W12" s="2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="X12" s="2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Y12" s="2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Z12" s="2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AA12" s="2" t="n">
+        <v>98.23999999999999</v>
+      </c>
+      <c r="AB12" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="AC12" s="2" t="n">
+        <v>99.29000000000001</v>
+      </c>
+      <c r="AD12" s="2" t="n">
+        <v>100.93</v>
+      </c>
+      <c r="AE12" s="2" t="n">
+        <v>160.06</v>
+      </c>
+      <c r="AF12" s="2" t="n">
+        <v>126.16</v>
+      </c>
+      <c r="AG12" s="2" t="n">
+        <v>111.61</v>
+      </c>
+      <c r="AH12" s="2" t="n">
+        <v>105.23</v>
+      </c>
+      <c r="AI12" s="2" t="n">
+        <v>101.61</v>
+      </c>
+      <c r="AJ12" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="AK12" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="AL12" s="2" t="n">
+        <v>148.17</v>
+      </c>
+      <c r="AM12" s="2" t="n">
+        <v>123.77</v>
+      </c>
+      <c r="AN12" s="2" t="n">
+        <v>110.67</v>
+      </c>
+      <c r="AO12" s="2" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="AP12" s="2" t="n">
+        <v>103.44</v>
+      </c>
+      <c r="AQ12" s="2" t="n">
+        <v>101.67</v>
+      </c>
+      <c r="AR12" s="2" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="AS12" s="2" t="n">
+        <v>102.54</v>
+      </c>
+      <c r="AT12" s="2" t="n">
+        <v>101.28</v>
+      </c>
+      <c r="AU12" s="2" t="n">
+        <v>100.28</v>
+      </c>
+      <c r="AV12" s="2" t="n">
+        <v>99.87</v>
+      </c>
+      <c r="AW12" s="2" t="n">
+        <v>102.04</v>
+      </c>
+      <c r="AX12" s="2" t="n">
+        <v>99.47</v>
+      </c>
+      <c r="AY12" s="2" t="n">
+        <v>100.01</v>
+      </c>
+      <c r="AZ12" s="2" t="n">
+        <v>104.28</v>
+      </c>
+      <c r="BA12" s="2" t="n">
+        <v>100.56</v>
+      </c>
+      <c r="BB12" s="2" t="n">
+        <v>104.21</v>
+      </c>
+      <c r="BC12" s="2" t="n">
+        <v>106.67</v>
+      </c>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" s="2" t="n">
+        <v>112.37</v>
+      </c>
+      <c r="BF12" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG12" s="2" t="n">
+        <v>99.19</v>
+      </c>
+      <c r="BH12" s="2" t="n">
+        <v>100.63</v>
+      </c>
+      <c r="BI12" s="2" t="n">
+        <v>98.18000000000001</v>
+      </c>
+      <c r="BJ12" s="2" t="n">
+        <v>97.38</v>
+      </c>
+      <c r="BK12" s="2" t="n">
+        <v>99.48</v>
+      </c>
+      <c r="BL12" s="2" t="n">
+        <v>99.55</v>
+      </c>
+      <c r="BM12" s="2" t="n">
+        <v>99.23999999999999</v>
+      </c>
+      <c r="BN12" s="2" t="n">
+        <v>96.66</v>
+      </c>
+      <c r="BO12" s="2" t="n">
+        <v>95.56</v>
+      </c>
+      <c r="BP12" s="2" t="n">
+        <v>96.62</v>
+      </c>
+      <c r="BQ12" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR12" s="2" t="n">
+        <v>98.68000000000001</v>
+      </c>
+      <c r="BS12" s="2" t="n">
+        <v>100.19</v>
+      </c>
+      <c r="BT12" s="2" t="n">
+        <v>96.64</v>
+      </c>
+      <c r="BU12" s="2" t="n">
+        <v>95.04000000000001</v>
+      </c>
+      <c r="BV12" s="2" t="n">
+        <v>97.19</v>
+      </c>
+      <c r="BW12" s="2" t="n">
+        <v>99.27</v>
+      </c>
+      <c r="BX12" s="2" t="n">
+        <v>98.47</v>
+      </c>
+      <c r="BY12" s="2" t="n">
+        <v>95.52</v>
+      </c>
+      <c r="BZ12" s="2" t="n">
+        <v>95.95999999999999</v>
+      </c>
+      <c r="CA12" s="2" t="n">
+        <v>97.31999999999999</v>
+      </c>
+      <c r="CB12" s="2" t="n">
+        <v>43.49</v>
+      </c>
+      <c r="CC12" s="2" t="n">
+        <v>101.14</v>
+      </c>
+      <c r="CD12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE12" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>99.11</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>101.49</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>51.23</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>101.29</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>99.53</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>100.94</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>32.37</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>100.83</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>103.32</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>100.55</v>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="V13" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W13" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="X13" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y13" s="2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z13" s="2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AA13" s="2" t="n">
+        <v>97.34</v>
+      </c>
+      <c r="AB13" s="2" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="AC13" s="2" t="n">
+        <v>106.05</v>
+      </c>
+      <c r="AD13" s="2" t="n">
+        <v>111.34</v>
+      </c>
+      <c r="AE13" s="2" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="AF13" s="2" t="n">
+        <v>102.39</v>
+      </c>
+      <c r="AG13" s="2" t="n">
+        <v>95.39</v>
+      </c>
+      <c r="AH13" s="2" t="n">
+        <v>92.93000000000001</v>
+      </c>
+      <c r="AI13" s="2" t="n">
+        <v>95.29000000000001</v>
+      </c>
+      <c r="AJ13" s="2" t="n">
+        <v>76.87</v>
+      </c>
+      <c r="AK13" s="2" t="n">
+        <v>112.08</v>
+      </c>
+      <c r="AL13" s="2" t="n">
+        <v>99.03</v>
+      </c>
+      <c r="AM13" s="2" t="n">
+        <v>110.65</v>
+      </c>
+      <c r="AN13" s="2" t="n">
+        <v>100.65</v>
+      </c>
+      <c r="AO13" s="2" t="n">
+        <v>102.66</v>
+      </c>
+      <c r="AP13" s="2" t="n">
+        <v>103.63</v>
+      </c>
+      <c r="AQ13" s="2" t="n">
+        <v>102.34</v>
+      </c>
+      <c r="AR13" s="2" t="n">
+        <v>104.43</v>
+      </c>
+      <c r="AS13" s="2" t="n">
+        <v>103.74</v>
+      </c>
+      <c r="AT13" s="2" t="n">
+        <v>102.34</v>
+      </c>
+      <c r="AU13" s="2" t="n">
+        <v>103.06</v>
+      </c>
+      <c r="AV13" s="2" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="AW13" s="2" t="n">
+        <v>101.96</v>
+      </c>
+      <c r="AX13" s="2" t="n">
+        <v>100.14</v>
+      </c>
+      <c r="AY13" s="2" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="AZ13" s="2" t="n">
+        <v>102.28</v>
+      </c>
+      <c r="BA13" s="2" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="BB13" s="2" t="n">
+        <v>102.32</v>
+      </c>
+      <c r="BC13" s="2" t="n">
+        <v>104.62</v>
+      </c>
+      <c r="BD13" s="2" t="n">
+        <v>103.44</v>
+      </c>
+      <c r="BE13" s="2" t="n">
+        <v>116.23</v>
+      </c>
+      <c r="BF13" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG13" s="2" t="n">
+        <v>99.45</v>
+      </c>
+      <c r="BH13" s="2" t="n">
+        <v>102.96</v>
+      </c>
+      <c r="BI13" s="2" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="BJ13" s="2" t="n">
+        <v>99.56999999999999</v>
+      </c>
+      <c r="BK13" s="2" t="n">
+        <v>100.61</v>
+      </c>
+      <c r="BL13" s="2" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="BM13" s="2" t="n">
+        <v>98.73</v>
+      </c>
+      <c r="BN13" s="2" t="n">
+        <v>103.08</v>
+      </c>
+      <c r="BO13" s="2" t="n">
+        <v>105.84</v>
+      </c>
+      <c r="BP13" s="2" t="n">
+        <v>106.84</v>
+      </c>
+      <c r="BQ13" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR13" s="2" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="BS13" s="2" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="BT13" s="2" t="n">
+        <v>102.62</v>
+      </c>
+      <c r="BU13" s="2" t="n">
+        <v>98.78</v>
+      </c>
+      <c r="BV13" s="2" t="n">
+        <v>98.64</v>
+      </c>
+      <c r="BW13" s="2" t="n">
+        <v>95.68000000000001</v>
+      </c>
+      <c r="BX13" s="2" t="n">
+        <v>97.72</v>
+      </c>
+      <c r="BY13" s="2" t="n">
+        <v>103.73</v>
+      </c>
+      <c r="BZ13" s="2" t="n">
+        <v>107.23</v>
+      </c>
+      <c r="CA13" s="2" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="CB13" s="2" t="n">
+        <v>41.83</v>
+      </c>
+      <c r="CC13" s="2" t="n">
+        <v>101.16</v>
+      </c>
+      <c r="CD13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE13" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2023-11-17</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>100.04</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>101.27</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>100.96</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>30.94</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>100.69</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>101.77</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>76.84999999999999</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>98.84999999999999</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>93.56</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>89.09</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>91.56</v>
+      </c>
+      <c r="V14" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="W14" s="2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="X14" s="2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Y14" s="2" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Z14" s="2" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AA14" s="2" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="AB14" s="2" t="n">
+        <v>100.65</v>
+      </c>
+      <c r="AC14" s="2" t="n">
+        <v>100.46</v>
+      </c>
+      <c r="AD14" s="2" t="n">
+        <v>103.88</v>
+      </c>
+      <c r="AE14" s="2" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="AF14" s="2" t="n">
+        <v>97.04000000000001</v>
+      </c>
+      <c r="AG14" s="2" t="n">
+        <v>103.89</v>
+      </c>
+      <c r="AH14" s="2" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="AI14" s="2" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="AJ14" s="2" t="n">
+        <v>88.86</v>
+      </c>
+      <c r="AK14" s="2" t="n">
+        <v>73.84</v>
+      </c>
+      <c r="AL14" s="2" t="n">
+        <v>65.91</v>
+      </c>
+      <c r="AM14" s="2" t="n">
+        <v>71.22</v>
+      </c>
+      <c r="AN14" s="2" t="n">
+        <v>91.78</v>
+      </c>
+      <c r="AO14" s="2" t="n">
+        <v>98.51000000000001</v>
+      </c>
+      <c r="AP14" s="2" t="n">
+        <v>96.81999999999999</v>
+      </c>
+      <c r="AQ14" s="2" t="n">
+        <v>93.84999999999999</v>
+      </c>
+      <c r="AR14" s="2" t="n">
+        <v>96.70999999999999</v>
+      </c>
+      <c r="AS14" s="2" t="n">
+        <v>94.39</v>
+      </c>
+      <c r="AT14" s="2" t="n">
+        <v>93.08</v>
+      </c>
+      <c r="AU14" s="2" t="n">
+        <v>92.06999999999999</v>
+      </c>
+      <c r="AV14" s="2" t="n">
+        <v>91.19</v>
+      </c>
+      <c r="AW14" s="2" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="AX14" s="2" t="n">
+        <v>90.31</v>
+      </c>
+      <c r="AY14" s="2" t="n">
+        <v>91.77</v>
+      </c>
+      <c r="AZ14" s="2" t="n">
+        <v>92.73</v>
+      </c>
+      <c r="BA14" s="2" t="n">
+        <v>93.22</v>
+      </c>
+      <c r="BB14" s="2" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="BC14" s="2" t="n">
+        <v>92.93000000000001</v>
+      </c>
+      <c r="BD14" s="2" t="n">
+        <v>93.70999999999999</v>
+      </c>
+      <c r="BE14" s="2" t="n">
+        <v>105.54</v>
+      </c>
+      <c r="BF14" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG14" s="2" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="BH14" s="2" t="n">
+        <v>97.81</v>
+      </c>
+      <c r="BI14" s="2" t="n">
+        <v>96.55</v>
+      </c>
+      <c r="BJ14" s="2" t="n">
+        <v>91.20999999999999</v>
+      </c>
+      <c r="BK14" s="2" t="n">
+        <v>93.58</v>
+      </c>
+      <c r="BL14" s="2" t="n">
+        <v>100.54</v>
+      </c>
+      <c r="BM14" s="2" t="n">
+        <v>100.81</v>
+      </c>
+      <c r="BN14" s="2" t="n">
+        <v>101.24</v>
+      </c>
+      <c r="BO14" s="2" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="BP14" s="2" t="n">
+        <v>105.02</v>
+      </c>
+      <c r="BQ14" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR14" s="2" t="n">
+        <v>99.87</v>
+      </c>
+      <c r="BS14" s="2" t="n">
+        <v>98.05</v>
+      </c>
+      <c r="BT14" s="2" t="n">
+        <v>95.34</v>
+      </c>
+      <c r="BU14" s="2" t="n">
+        <v>89.53</v>
+      </c>
+      <c r="BV14" s="2" t="n">
+        <v>91.94</v>
+      </c>
+      <c r="BW14" s="2" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="BX14" s="2" t="n">
+        <v>100.78</v>
+      </c>
+      <c r="BY14" s="2" t="n">
+        <v>100.01</v>
+      </c>
+      <c r="BZ14" s="2" t="n">
+        <v>102.42</v>
+      </c>
+      <c r="CA14" s="2" t="n">
+        <v>105.63</v>
+      </c>
+      <c r="CB14" s="2" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="CC14" s="2" t="n">
+        <v>100.59</v>
+      </c>
+      <c r="CD14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE14" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>102.19</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>39.06</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>101.39</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>101.46</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>103.71</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>76.06999999999999</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>101.33</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>101.19</v>
+      </c>
+      <c r="T15" s="2" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="U15" s="2" t="n">
+        <v>94.11</v>
+      </c>
+      <c r="V15" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="W15" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X15" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="Y15" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="Z15" s="2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA15" s="2" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="AB15" s="2" t="n">
+        <v>103.06</v>
+      </c>
+      <c r="AC15" s="2" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="AD15" s="2" t="n">
+        <v>98.29000000000001</v>
+      </c>
+      <c r="AE15" s="2" t="n">
+        <v>83.81999999999999</v>
+      </c>
+      <c r="AF15" s="2" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="AG15" s="2" t="n">
+        <v>73.73999999999999</v>
+      </c>
+      <c r="AH15" s="2" t="n">
+        <v>82.05</v>
+      </c>
+      <c r="AI15" s="2" t="n">
+        <v>89.68000000000001</v>
+      </c>
+      <c r="AJ15" s="2" t="n">
+        <v>76.97</v>
+      </c>
+      <c r="AK15" s="2" t="n">
+        <v>95.54000000000001</v>
+      </c>
+      <c r="AL15" s="2" t="n">
+        <v>95.63</v>
+      </c>
+      <c r="AM15" s="2" t="n">
+        <v>114.2</v>
+      </c>
+      <c r="AN15" s="2" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="AO15" s="2" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="AP15" s="2" t="n">
+        <v>101.48</v>
+      </c>
+      <c r="AQ15" s="2" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="AR15" s="2" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="AS15" s="2" t="n">
+        <v>100.98</v>
+      </c>
+      <c r="AT15" s="2" t="n">
+        <v>97.97</v>
+      </c>
+      <c r="AU15" s="2" t="n">
+        <v>100.26</v>
+      </c>
+      <c r="AV15" s="2" t="n">
+        <v>98.77</v>
+      </c>
+      <c r="AW15" s="2" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="AX15" s="2" t="n">
+        <v>97.28</v>
+      </c>
+      <c r="AY15" s="2" t="n">
+        <v>94.95</v>
+      </c>
+      <c r="AZ15" s="2" t="n">
+        <v>93.63</v>
+      </c>
+      <c r="BA15" s="2" t="n">
+        <v>92.62</v>
+      </c>
+      <c r="BB15" s="2" t="n">
+        <v>91.73999999999999</v>
+      </c>
+      <c r="BC15" s="2" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="BD15" s="2" t="n">
+        <v>95.81</v>
+      </c>
+      <c r="BE15" s="2" t="n">
+        <v>106.17</v>
+      </c>
+      <c r="BF15" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG15" s="2" t="n">
+        <v>99.95999999999999</v>
+      </c>
+      <c r="BH15" s="2" t="n">
+        <v>99.58</v>
+      </c>
+      <c r="BI15" s="2" t="n">
+        <v>98.78</v>
+      </c>
+      <c r="BJ15" s="2" t="n">
+        <v>96.62</v>
+      </c>
+      <c r="BK15" s="2" t="n">
+        <v>95.37</v>
+      </c>
+      <c r="BL15" s="2" t="n">
+        <v>99.55</v>
+      </c>
+      <c r="BM15" s="2" t="n">
+        <v>101.15</v>
+      </c>
+      <c r="BN15" s="2" t="n">
+        <v>103.74</v>
+      </c>
+      <c r="BO15" s="2" t="n">
+        <v>104.49</v>
+      </c>
+      <c r="BP15" s="2" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="BQ15" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR15" s="2" t="n">
+        <v>100.68</v>
+      </c>
+      <c r="BS15" s="2" t="n">
+        <v>100.77</v>
+      </c>
+      <c r="BT15" s="2" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="BU15" s="2" t="n">
+        <v>98.04000000000001</v>
+      </c>
+      <c r="BV15" s="2" t="n">
+        <v>95.33</v>
+      </c>
+      <c r="BW15" s="2" t="n">
+        <v>99.67</v>
+      </c>
+      <c r="BX15" s="2" t="n">
+        <v>102.41</v>
+      </c>
+      <c r="BY15" s="2" t="n">
+        <v>105.62</v>
+      </c>
+      <c r="BZ15" s="2" t="n">
+        <v>106.56</v>
+      </c>
+      <c r="CA15" s="2" t="n">
+        <v>103.34</v>
+      </c>
+      <c r="CB15" s="2" t="n">
+        <v>61.07</v>
+      </c>
+      <c r="CC15" s="2" t="n">
+        <v>101.06</v>
+      </c>
+      <c r="CD15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE15" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2023-12-27</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>100.91</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>101.47</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>52.83</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>101.26</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>101.09</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>101.87</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>37.58</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>101.31</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>103.06</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>101.89</v>
+      </c>
+      <c r="T16" s="2" t="n">
+        <v>101.22</v>
+      </c>
+      <c r="U16" s="2" t="n">
+        <v>99.64</v>
+      </c>
+      <c r="V16" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="W16" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="X16" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="Y16" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Z16" s="2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AA16" s="2" t="n">
+        <v>100.75</v>
+      </c>
+      <c r="AB16" s="2" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="AC16" s="2" t="n">
+        <v>97.12</v>
+      </c>
+      <c r="AD16" s="2" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="AE16" s="2" t="n">
+        <v>57.71</v>
+      </c>
+      <c r="AF16" s="2" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="AG16" s="2" t="n">
+        <v>101.27</v>
+      </c>
+      <c r="AH16" s="2" t="n">
+        <v>98.91</v>
+      </c>
+      <c r="AI16" s="2" t="n">
+        <v>93.33</v>
+      </c>
+      <c r="AJ16" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="AK16" s="2" t="n">
+        <v>67.01000000000001</v>
+      </c>
+      <c r="AL16" s="2" t="n">
+        <v>101.18</v>
+      </c>
+      <c r="AM16" s="2" t="n">
+        <v>96.06</v>
+      </c>
+      <c r="AN16" s="2" t="n">
+        <v>96.58</v>
+      </c>
+      <c r="AO16" s="2" t="n">
+        <v>102.14</v>
+      </c>
+      <c r="AP16" s="2" t="n">
+        <v>102.44</v>
+      </c>
+      <c r="AQ16" s="2" t="n">
+        <v>101.35</v>
+      </c>
+      <c r="AR16" s="2" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="AS16" s="2" t="n">
+        <v>102.39</v>
+      </c>
+      <c r="AT16" s="2" t="n">
+        <v>101.06</v>
+      </c>
+      <c r="AU16" s="2" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="AV16" s="2" t="n">
+        <v>100.66</v>
+      </c>
+      <c r="AW16" s="2" t="n">
+        <v>100.01</v>
+      </c>
+      <c r="AX16" s="2" t="n">
+        <v>99.79000000000001</v>
+      </c>
+      <c r="AY16" s="2" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="AZ16" s="2" t="n">
+        <v>98.63</v>
+      </c>
+      <c r="BA16" s="2" t="n">
+        <v>99.65000000000001</v>
+      </c>
+      <c r="BB16" s="2" t="n">
+        <v>99.34999999999999</v>
+      </c>
+      <c r="BC16" s="2" t="n">
+        <v>96.63</v>
+      </c>
+      <c r="BD16" s="2" t="n">
+        <v>97.28</v>
+      </c>
+      <c r="BE16" s="2" t="n">
+        <v>104.14</v>
+      </c>
+      <c r="BF16" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG16" s="2" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="BH16" s="2" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="BI16" s="2" t="n">
+        <v>97.12</v>
+      </c>
+      <c r="BJ16" s="2" t="n">
+        <v>95.52</v>
+      </c>
+      <c r="BK16" s="2" t="n">
+        <v>95.26000000000001</v>
+      </c>
+      <c r="BL16" s="2" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="BM16" s="2" t="n">
+        <v>98.06</v>
+      </c>
+      <c r="BN16" s="2" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="BO16" s="2" t="n">
+        <v>101.22</v>
+      </c>
+      <c r="BP16" s="2" t="n">
+        <v>102.29</v>
+      </c>
+      <c r="BQ16" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR16" s="2" t="n">
+        <v>99.23</v>
+      </c>
+      <c r="BS16" s="2" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="BT16" s="2" t="n">
+        <v>96.73</v>
+      </c>
+      <c r="BU16" s="2" t="n">
+        <v>93.91</v>
+      </c>
+      <c r="BV16" s="2" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="BW16" s="2" t="n">
+        <v>99.52</v>
+      </c>
+      <c r="BX16" s="2" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="BY16" s="2" t="n">
+        <v>99.48999999999999</v>
+      </c>
+      <c r="BZ16" s="2" t="n">
+        <v>102.41</v>
+      </c>
+      <c r="CA16" s="2" t="n">
+        <v>103.04</v>
+      </c>
+      <c r="CB16" s="2" t="n">
+        <v>53.35</v>
+      </c>
+      <c r="CC16" s="2" t="n">
+        <v>101.08</v>
+      </c>
+      <c r="CD16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2024-01-11</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>100.16</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>101.51</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>74.19</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>101.87</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>100.86</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>100.83</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>99.06999999999999</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>105.19</v>
+      </c>
+      <c r="T17" s="2" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="U17" s="2" t="n">
+        <v>106.04</v>
+      </c>
+      <c r="V17" s="2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="W17" s="2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X17" s="2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y17" s="2" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Z17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA17" s="2" t="n">
+        <v>100.01</v>
+      </c>
+      <c r="AB17" s="2" t="n">
+        <v>104.32</v>
+      </c>
+      <c r="AC17" s="2" t="n">
+        <v>104.79</v>
+      </c>
+      <c r="AD17" s="2" t="n">
+        <v>102.98</v>
+      </c>
+      <c r="AE17" s="2" t="n">
+        <v>79.68000000000001</v>
+      </c>
+      <c r="AF17" s="2" t="n">
+        <v>100.68</v>
+      </c>
+      <c r="AG17" s="2" t="n">
+        <v>97.58</v>
+      </c>
+      <c r="AH17" s="2" t="n">
+        <v>89.41</v>
+      </c>
+      <c r="AI17" s="2" t="n">
+        <v>100.33</v>
+      </c>
+      <c r="AJ17" s="2" t="n">
+        <v>87.34999999999999</v>
+      </c>
+      <c r="AK17" s="2" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="AL17" s="2" t="n">
+        <v>106.78</v>
+      </c>
+      <c r="AM17" s="2" t="n">
+        <v>98.81999999999999</v>
+      </c>
+      <c r="AN17" s="2" t="n">
+        <v>100.85</v>
+      </c>
+      <c r="AO17" s="2" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="AP17" s="2" t="n">
+        <v>102.17</v>
+      </c>
+      <c r="AQ17" s="2" t="n">
+        <v>104.39</v>
+      </c>
+      <c r="AR17" s="2" t="n">
+        <v>102.16</v>
+      </c>
+      <c r="AS17" s="2" t="n">
+        <v>103.87</v>
+      </c>
+      <c r="AT17" s="2" t="n">
+        <v>105.21</v>
+      </c>
+      <c r="AU17" s="2" t="n">
+        <v>105.58</v>
+      </c>
+      <c r="AV17" s="2" t="n">
+        <v>106.51</v>
+      </c>
+      <c r="AW17" s="2" t="n">
+        <v>105.64</v>
+      </c>
+      <c r="AX17" s="2" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="AY17" s="2" t="n">
+        <v>106.56</v>
+      </c>
+      <c r="AZ17" s="2" t="n">
+        <v>105.17</v>
+      </c>
+      <c r="BA17" s="2" t="n">
+        <v>105.67</v>
+      </c>
+      <c r="BB17" s="2" t="n">
+        <v>104.76</v>
+      </c>
+      <c r="BC17" s="2" t="n">
+        <v>104.07</v>
+      </c>
+      <c r="BD17" s="2" t="n">
+        <v>102.76</v>
+      </c>
+      <c r="BE17" s="2" t="n">
+        <v>108.38</v>
+      </c>
+      <c r="BF17" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG17" s="2" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="BH17" s="2" t="n">
+        <v>98.08</v>
+      </c>
+      <c r="BI17" s="2" t="n">
+        <v>100.03</v>
+      </c>
+      <c r="BJ17" s="2" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="BK17" s="2" t="n">
+        <v>97.14</v>
+      </c>
+      <c r="BL17" s="2" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="BM17" s="2" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="BN17" s="2" t="n">
+        <v>102.32</v>
+      </c>
+      <c r="BO17" s="2" t="n">
+        <v>103.73</v>
+      </c>
+      <c r="BP17" s="2" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="BQ17" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR17" s="2" t="n">
+        <v>99.15000000000001</v>
+      </c>
+      <c r="BS17" s="2" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="BT17" s="2" t="n">
+        <v>100.51</v>
+      </c>
+      <c r="BU17" s="2" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="BV17" s="2" t="n">
+        <v>97.23</v>
+      </c>
+      <c r="BW17" s="2" t="n">
+        <v>100.06</v>
+      </c>
+      <c r="BX17" s="2" t="n">
+        <v>102.93</v>
+      </c>
+      <c r="BY17" s="2" t="n">
+        <v>103.57</v>
+      </c>
+      <c r="BZ17" s="2" t="n">
+        <v>104.89</v>
+      </c>
+      <c r="CA17" s="2" t="n">
+        <v>106.79</v>
+      </c>
+      <c r="CB17" s="2" t="n">
+        <v>42.16</v>
+      </c>
+      <c r="CC17" s="2" t="n">
+        <v>101.07</v>
+      </c>
+      <c r="CD17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE17" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>101.24</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>102.73</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>101.38</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>98.89</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>101.17</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>66.97</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>102.42</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>102.27</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>98.06999999999999</v>
+      </c>
+      <c r="T18" s="2" t="n">
+        <v>95.56999999999999</v>
+      </c>
+      <c r="U18" s="2" t="n">
+        <v>102.11</v>
+      </c>
+      <c r="V18" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="W18" s="2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="X18" s="2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y18" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Z18" s="2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AA18" s="2" t="n">
+        <v>97.27</v>
+      </c>
+      <c r="AB18" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="AC18" s="2" t="n">
+        <v>98.84</v>
+      </c>
+      <c r="AD18" s="2" t="n">
+        <v>96.45999999999999</v>
+      </c>
+      <c r="AE18" s="2" t="n">
+        <v>87.87</v>
+      </c>
+      <c r="AF18" s="2" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="AG18" s="2" t="n">
+        <v>98.26000000000001</v>
+      </c>
+      <c r="AH18" s="2" t="n">
+        <v>96.18000000000001</v>
+      </c>
+      <c r="AI18" s="2" t="n">
+        <v>97.73999999999999</v>
+      </c>
+      <c r="AJ18" s="2" t="n">
+        <v>83.34</v>
+      </c>
+      <c r="AK18" s="2" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="AL18" s="2" t="n">
+        <v>123.19</v>
+      </c>
+      <c r="AM18" s="2" t="n">
+        <v>101.34</v>
+      </c>
+      <c r="AN18" s="2" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="AO18" s="2" t="n">
+        <v>102.26</v>
+      </c>
+      <c r="AP18" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AQ18" s="2" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="AR18" s="2" t="n">
+        <v>99.20999999999999</v>
+      </c>
+      <c r="AS18" s="2" t="n">
+        <v>98.58</v>
+      </c>
+      <c r="AT18" s="2" t="n">
+        <v>99.23</v>
+      </c>
+      <c r="AU18" s="2" t="n">
+        <v>97.94</v>
+      </c>
+      <c r="AV18" s="2" t="n">
+        <v>97.79000000000001</v>
+      </c>
+      <c r="AW18" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="AX18" s="2" t="n">
+        <v>97.64</v>
+      </c>
+      <c r="AY18" s="2" t="n">
+        <v>99.88</v>
+      </c>
+      <c r="AZ18" s="2" t="n">
+        <v>101.61</v>
+      </c>
+      <c r="BA18" s="2" t="n">
+        <v>102.13</v>
+      </c>
+      <c r="BB18" s="2" t="n">
+        <v>102.93</v>
+      </c>
+      <c r="BC18" s="2" t="n">
+        <v>102.43</v>
+      </c>
+      <c r="BD18" s="2" t="n">
+        <v>100.71</v>
+      </c>
+      <c r="BE18" s="2" t="n">
+        <v>104.97</v>
+      </c>
+      <c r="BF18" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG18" s="2" t="n">
+        <v>99.31</v>
+      </c>
+      <c r="BH18" s="2" t="n">
+        <v>98.43000000000001</v>
+      </c>
+      <c r="BI18" s="2" t="n">
+        <v>97.08</v>
+      </c>
+      <c r="BJ18" s="2" t="n">
+        <v>95.31999999999999</v>
+      </c>
+      <c r="BK18" s="2" t="n">
+        <v>97.06999999999999</v>
+      </c>
+      <c r="BL18" s="2" t="n">
+        <v>98.33</v>
+      </c>
+      <c r="BM18" s="2" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="BN18" s="2" t="n">
+        <v>101.91</v>
+      </c>
+      <c r="BO18" s="2" t="n">
+        <v>100.97</v>
+      </c>
+      <c r="BP18" s="2" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="BQ18" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR18" s="2" t="n">
+        <v>99.55</v>
+      </c>
+      <c r="BS18" s="2" t="n">
+        <v>98.48999999999999</v>
+      </c>
+      <c r="BT18" s="2" t="n">
+        <v>95.66</v>
+      </c>
+      <c r="BU18" s="2" t="n">
+        <v>92.67</v>
+      </c>
+      <c r="BV18" s="2" t="n">
+        <v>96.03</v>
+      </c>
+      <c r="BW18" s="2" t="n">
+        <v>97.39</v>
+      </c>
+      <c r="BX18" s="2" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="BY18" s="2" t="n">
+        <v>101.63</v>
+      </c>
+      <c r="BZ18" s="2" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="CA18" s="2" t="n">
+        <v>102.13</v>
+      </c>
+      <c r="CB18" s="2" t="n">
+        <v>53.94</v>
+      </c>
+      <c r="CC18" s="2" t="n">
+        <v>101.13</v>
+      </c>
+      <c r="CD18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE18" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2024-02-13</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>101.79</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>102.81</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>67.55</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>101.47</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>27.04</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>99.42</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>37.86</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>102.91</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>103.02</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>102.34</v>
+      </c>
+      <c r="T19" s="2" t="n">
+        <v>106.22</v>
+      </c>
+      <c r="U19" s="2" t="n">
+        <v>99.94</v>
+      </c>
+      <c r="V19" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="W19" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="X19" s="2" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="Y19" s="2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z19" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA19" s="2" t="n">
+        <v>100.19</v>
+      </c>
+      <c r="AB19" s="2" t="n">
+        <v>99.34999999999999</v>
+      </c>
+      <c r="AC19" s="2" t="n">
+        <v>98.86</v>
+      </c>
+      <c r="AD19" s="2" t="n">
+        <v>93.25</v>
+      </c>
+      <c r="AE19" s="2" t="n">
+        <v>79.77</v>
+      </c>
+      <c r="AF19" s="2" t="n">
+        <v>82.52</v>
+      </c>
+      <c r="AG19" s="2" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="AH19" s="2" t="n">
+        <v>99.81</v>
+      </c>
+      <c r="AI19" s="2" t="n">
+        <v>104.21</v>
+      </c>
+      <c r="AJ19" s="2" t="n">
+        <v>103.74</v>
+      </c>
+      <c r="AK19" s="2" t="n">
+        <v>110.17</v>
+      </c>
+      <c r="AL19" s="2" t="n">
+        <v>97.20999999999999</v>
+      </c>
+      <c r="AM19" s="2" t="n">
+        <v>92.93000000000001</v>
+      </c>
+      <c r="AN19" s="2" t="n">
+        <v>117.67</v>
+      </c>
+      <c r="AO19" s="2" t="n">
+        <v>102.73</v>
+      </c>
+      <c r="AP19" s="2" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="AQ19" s="2" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="AR19" s="2" t="n">
+        <v>101.67</v>
+      </c>
+      <c r="AS19" s="2" t="n">
+        <v>103.13</v>
+      </c>
+      <c r="AT19" s="2" t="n">
+        <v>102.68</v>
+      </c>
+      <c r="AU19" s="2" t="n">
+        <v>104.59</v>
+      </c>
+      <c r="AV19" s="2" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="AW19" s="2" t="n">
+        <v>102.26</v>
+      </c>
+      <c r="AX19" s="2" t="n">
+        <v>103.62</v>
+      </c>
+      <c r="AY19" s="2" t="n">
+        <v>102.23</v>
+      </c>
+      <c r="AZ19" s="2" t="n">
+        <v>102.39</v>
+      </c>
+      <c r="BA19" s="2" t="n">
+        <v>100.84</v>
+      </c>
+      <c r="BB19" s="2" t="n">
+        <v>100.41</v>
+      </c>
+      <c r="BC19" s="2" t="n">
+        <v>103.16</v>
+      </c>
+      <c r="BD19" s="2" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="BE19" s="2" t="n">
+        <v>108.31</v>
+      </c>
+      <c r="BF19" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG19" s="2" t="n">
+        <v>101.48</v>
+      </c>
+      <c r="BH19" s="2" t="n">
+        <v>100.02</v>
+      </c>
+      <c r="BI19" s="2" t="n">
+        <v>99.43000000000001</v>
+      </c>
+      <c r="BJ19" s="2" t="n">
+        <v>98.20999999999999</v>
+      </c>
+      <c r="BK19" s="2" t="n">
+        <v>96.22</v>
+      </c>
+      <c r="BL19" s="2" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="BM19" s="2" t="n">
+        <v>100.58</v>
+      </c>
+      <c r="BN19" s="2" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="BO19" s="2" t="n">
+        <v>103.06</v>
+      </c>
+      <c r="BP19" s="2" t="n">
+        <v>104.28</v>
+      </c>
+      <c r="BQ19" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR19" s="2" t="n">
+        <v>102.06</v>
+      </c>
+      <c r="BS19" s="2" t="n">
+        <v>99.84</v>
+      </c>
+      <c r="BT19" s="2" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="BU19" s="2" t="n">
+        <v>98.89</v>
+      </c>
+      <c r="BV19" s="2" t="n">
+        <v>95.63</v>
+      </c>
+      <c r="BW19" s="2" t="n">
+        <v>101.39</v>
+      </c>
+      <c r="BX19" s="2" t="n">
+        <v>99.31</v>
+      </c>
+      <c r="BY19" s="2" t="n">
+        <v>101.56</v>
+      </c>
+      <c r="BZ19" s="2" t="n">
+        <v>102.37</v>
+      </c>
+      <c r="CA19" s="2" t="n">
+        <v>102.66</v>
+      </c>
+      <c r="CB19" s="2" t="n">
+        <v>42.23</v>
+      </c>
+      <c r="CC19" s="2" t="n">
+        <v>100.83</v>
+      </c>
+      <c r="CD19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE19" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>98.95999999999999</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>101.07</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>101.48</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>106.89</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>109.43</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>75.34999999999999</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>99.67</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>99.41</v>
+      </c>
+      <c r="S20" s="2" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="T20" s="2" t="n">
+        <v>102.43</v>
+      </c>
+      <c r="U20" s="2" t="n">
+        <v>98.79000000000001</v>
+      </c>
+      <c r="V20" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W20" s="2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="X20" s="2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Y20" s="2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Z20" s="2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA20" s="2" t="n">
+        <v>106.33</v>
+      </c>
+      <c r="AB20" s="2" t="n">
+        <v>108.01</v>
+      </c>
+      <c r="AC20" s="2" t="n">
+        <v>111.24</v>
+      </c>
+      <c r="AD20" s="2" t="n">
+        <v>112.65</v>
+      </c>
+      <c r="AE20" s="2" t="n">
+        <v>97.83</v>
+      </c>
+      <c r="AF20" s="2" t="n">
+        <v>94.16</v>
+      </c>
+      <c r="AG20" s="2" t="n">
+        <v>90.34</v>
+      </c>
+      <c r="AH20" s="2" t="n">
+        <v>104.06</v>
+      </c>
+      <c r="AI20" s="2" t="n">
+        <v>96.98999999999999</v>
+      </c>
+      <c r="AJ20" s="2" t="n">
+        <v>158.48</v>
+      </c>
+      <c r="AK20" s="2" t="n">
+        <v>203.36</v>
+      </c>
+      <c r="AL20" s="2" t="n">
+        <v>138.99</v>
+      </c>
+      <c r="AM20" s="2" t="n">
+        <v>119.69</v>
+      </c>
+      <c r="AN20" s="2" t="n">
+        <v>100.24</v>
+      </c>
+      <c r="AO20" s="2" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="AP20" s="2" t="n">
+        <v>98.59</v>
+      </c>
+      <c r="AQ20" s="2" t="n">
+        <v>99.26000000000001</v>
+      </c>
+      <c r="AR20" s="2" t="n">
+        <v>97.92</v>
+      </c>
+      <c r="AS20" s="2" t="n">
+        <v>98.91</v>
+      </c>
+      <c r="AT20" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="AU20" s="2" t="n">
+        <v>99.91</v>
+      </c>
+      <c r="AV20" s="2" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="AW20" s="2" t="n">
+        <v>99.79000000000001</v>
+      </c>
+      <c r="AX20" s="2" t="n">
+        <v>99.54000000000001</v>
+      </c>
+      <c r="AY20" s="2" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="AZ20" s="2" t="n">
+        <v>100.38</v>
+      </c>
+      <c r="BA20" s="2" t="n">
+        <v>99.34</v>
+      </c>
+      <c r="BB20" s="2" t="n">
+        <v>99.84999999999999</v>
+      </c>
+      <c r="BC20" s="2" t="n">
+        <v>100.57</v>
+      </c>
+      <c r="BD20" s="2" t="n">
+        <v>100.89</v>
+      </c>
+      <c r="BE20" s="2" t="n">
+        <v>116.31</v>
+      </c>
+      <c r="BF20" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG20" s="2" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="BH20" s="2" t="n">
+        <v>99.69</v>
+      </c>
+      <c r="BI20" s="2" t="n">
+        <v>98.95</v>
+      </c>
+      <c r="BJ20" s="2" t="n">
+        <v>102.66</v>
+      </c>
+      <c r="BK20" s="2" t="n">
+        <v>101.64</v>
+      </c>
+      <c r="BL20" s="2" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="BM20" s="2" t="n">
+        <v>102.96</v>
+      </c>
+      <c r="BN20" s="2" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="BO20" s="2" t="n">
+        <v>104.02</v>
+      </c>
+      <c r="BP20" s="2" t="n">
+        <v>104.21</v>
+      </c>
+      <c r="BQ20" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR20" s="2" t="n">
+        <v>99.43000000000001</v>
+      </c>
+      <c r="BS20" s="2" t="n">
+        <v>99.37</v>
+      </c>
+      <c r="BT20" s="2" t="n">
+        <v>99.16</v>
+      </c>
+      <c r="BU20" s="2" t="n">
+        <v>104.37</v>
+      </c>
+      <c r="BV20" s="2" t="n">
+        <v>101.92</v>
+      </c>
+      <c r="BW20" s="2" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="BX20" s="2" t="n">
+        <v>103.26</v>
+      </c>
+      <c r="BY20" s="2" t="n">
+        <v>105.79</v>
+      </c>
+      <c r="BZ20" s="2" t="n">
+        <v>106.17</v>
+      </c>
+      <c r="CA20" s="2" t="n">
+        <v>105.67</v>
+      </c>
+      <c r="CB20" s="2" t="n">
+        <v>54.16</v>
+      </c>
+      <c r="CC20" s="2" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="CD20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE20" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>99.28</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>101.43</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>97.70999999999999</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>102.06</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>15.87</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>99.23999999999999</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>94.34</v>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>92.94</v>
+      </c>
+      <c r="T21" s="2" t="n">
+        <v>95.95999999999999</v>
+      </c>
+      <c r="U21" s="2" t="n">
+        <v>87.11</v>
+      </c>
+      <c r="V21" s="2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W21" s="2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="X21" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y21" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z21" s="2" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="AA21" s="2" t="n">
+        <v>104.36</v>
+      </c>
+      <c r="AB21" s="2" t="n">
+        <v>104.99</v>
+      </c>
+      <c r="AC21" s="2" t="n">
+        <v>100.32</v>
+      </c>
+      <c r="AD21" s="2" t="n">
+        <v>93.73999999999999</v>
+      </c>
+      <c r="AE21" s="2" t="n">
+        <v>73.06999999999999</v>
+      </c>
+      <c r="AF21" s="2" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="AG21" s="2" t="n">
+        <v>118.49</v>
+      </c>
+      <c r="AH21" s="2" t="n">
+        <v>121.62</v>
+      </c>
+      <c r="AI21" s="2" t="n">
+        <v>133.19</v>
+      </c>
+      <c r="AJ21" s="2" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="AK21" s="2" t="n">
+        <v>82.72</v>
+      </c>
+      <c r="AL21" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="AM21" s="2" t="n">
+        <v>82.95</v>
+      </c>
+      <c r="AN21" s="2" t="n">
+        <v>87.08</v>
+      </c>
+      <c r="AO21" s="2" t="n">
+        <v>97.05</v>
+      </c>
+      <c r="AP21" s="2" t="n">
+        <v>95.45</v>
+      </c>
+      <c r="AQ21" s="2" t="n">
+        <v>93.81999999999999</v>
+      </c>
+      <c r="AR21" s="2" t="n">
+        <v>94.53</v>
+      </c>
+      <c r="AS21" s="2" t="n">
+        <v>94.77</v>
+      </c>
+      <c r="AT21" s="2" t="n">
+        <v>92.08</v>
+      </c>
+      <c r="AU21" s="2" t="n">
+        <v>95.02</v>
+      </c>
+      <c r="AV21" s="2" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="AW21" s="2" t="n">
+        <v>89.69</v>
+      </c>
+      <c r="AX21" s="2" t="n">
+        <v>91.78</v>
+      </c>
+      <c r="AY21" s="2" t="n">
+        <v>89.38</v>
+      </c>
+      <c r="AZ21" s="2" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="BA21" s="2" t="n">
+        <v>86.98999999999999</v>
+      </c>
+      <c r="BB21" s="2" t="n">
+        <v>85.98</v>
+      </c>
+      <c r="BC21" s="2" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="BD21" s="2" t="n">
+        <v>87.89</v>
+      </c>
+      <c r="BE21" s="2" t="n">
+        <v>88.91</v>
+      </c>
+      <c r="BF21" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG21" s="2" t="n">
+        <v>99.36</v>
+      </c>
+      <c r="BH21" s="2" t="n">
+        <v>97.98</v>
+      </c>
+      <c r="BI21" s="2" t="n">
+        <v>98.06</v>
+      </c>
+      <c r="BJ21" s="2" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="BK21" s="2" t="n">
+        <v>96.05</v>
+      </c>
+      <c r="BL21" s="2" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="BM21" s="2" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="BN21" s="2" t="n">
+        <v>99.84999999999999</v>
+      </c>
+      <c r="BO21" s="2" t="n">
+        <v>98.04000000000001</v>
+      </c>
+      <c r="BP21" s="2" t="n">
+        <v>93.06</v>
+      </c>
+      <c r="BQ21" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR21" s="2" t="n">
+        <v>98.76000000000001</v>
+      </c>
+      <c r="BS21" s="2" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="BT21" s="2" t="n">
+        <v>96.38</v>
+      </c>
+      <c r="BU21" s="2" t="n">
+        <v>95.78</v>
+      </c>
+      <c r="BV21" s="2" t="n">
+        <v>93.06</v>
+      </c>
+      <c r="BW21" s="2" t="n">
+        <v>101.15</v>
+      </c>
+      <c r="BX21" s="2" t="n">
+        <v>99.73999999999999</v>
+      </c>
+      <c r="BY21" s="2" t="n">
+        <v>96.98</v>
+      </c>
+      <c r="BZ21" s="2" t="n">
+        <v>93.25</v>
+      </c>
+      <c r="CA21" s="2" t="n">
+        <v>87.55</v>
+      </c>
+      <c r="CB21" s="2" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="CC21" s="2" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="CD21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE21" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>98.62</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>100.65</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>15.87</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>101.34</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>101.27</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>102.96</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>96.08</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>95.75</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="T22" s="2" t="n">
+        <v>93.87</v>
+      </c>
+      <c r="U22" s="2" t="n">
+        <v>86.98</v>
+      </c>
+      <c r="V22" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="W22" s="2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X22" s="2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="Y22" s="2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="Z22" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA22" s="2" t="n">
+        <v>100.53</v>
+      </c>
+      <c r="AB22" s="2" t="n">
+        <v>103.73</v>
+      </c>
+      <c r="AC22" s="2" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="AD22" s="2" t="n">
+        <v>91.54000000000001</v>
+      </c>
+      <c r="AE22" s="2" t="n">
+        <v>89.06</v>
+      </c>
+      <c r="AF22" s="2" t="n">
+        <v>82.08</v>
+      </c>
+      <c r="AG22" s="2" t="n">
+        <v>90.95</v>
+      </c>
+      <c r="AH22" s="2" t="n">
+        <v>117.45</v>
+      </c>
+      <c r="AI22" s="2" t="n">
+        <v>134.18</v>
+      </c>
+      <c r="AJ22" s="2" t="n">
+        <v>71.66</v>
+      </c>
+      <c r="AK22" s="2" t="n">
+        <v>94.91</v>
+      </c>
+      <c r="AL22" s="2" t="n">
+        <v>85.34</v>
+      </c>
+      <c r="AM22" s="2" t="n">
+        <v>81.53</v>
+      </c>
+      <c r="AN22" s="2" t="n">
+        <v>88.47</v>
+      </c>
+      <c r="AO22" s="2" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="AP22" s="2" t="n">
+        <v>94.87</v>
+      </c>
+      <c r="AQ22" s="2" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="AR22" s="2" t="n">
+        <v>93.98999999999999</v>
+      </c>
+      <c r="AS22" s="2" t="n">
+        <v>93.65000000000001</v>
+      </c>
+      <c r="AT22" s="2" t="n">
+        <v>91.34999999999999</v>
+      </c>
+      <c r="AU22" s="2" t="n">
+        <v>93.31999999999999</v>
+      </c>
+      <c r="AV22" s="2" t="n">
+        <v>92.61</v>
+      </c>
+      <c r="AW22" s="2" t="n">
+        <v>88.92</v>
+      </c>
+      <c r="AX22" s="2" t="n">
+        <v>91.89</v>
+      </c>
+      <c r="AY22" s="2" t="n">
+        <v>89.04000000000001</v>
+      </c>
+      <c r="AZ22" s="2" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="BA22" s="2" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="BB22" s="2" t="n">
+        <v>85.23</v>
+      </c>
+      <c r="BC22" s="2" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="BD22" s="2" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="BE22" s="2" t="n">
+        <v>87.68000000000001</v>
+      </c>
+      <c r="BF22" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG22" s="2" t="n">
+        <v>99.81999999999999</v>
+      </c>
+      <c r="BH22" s="2" t="n">
+        <v>98.17</v>
+      </c>
+      <c r="BI22" s="2" t="n">
+        <v>97.68000000000001</v>
+      </c>
+      <c r="BJ22" s="2" t="n">
+        <v>97.39</v>
+      </c>
+      <c r="BK22" s="2" t="n">
+        <v>95.88</v>
+      </c>
+      <c r="BL22" s="2" t="n">
+        <v>100.14</v>
+      </c>
+      <c r="BM22" s="2" t="n">
+        <v>101.62</v>
+      </c>
+      <c r="BN22" s="2" t="n">
+        <v>99.62</v>
+      </c>
+      <c r="BO22" s="2" t="n">
+        <v>97.48</v>
+      </c>
+      <c r="BP22" s="2" t="n">
+        <v>93.95999999999999</v>
+      </c>
+      <c r="BQ22" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR22" s="2" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="BS22" s="2" t="n">
+        <v>96.87</v>
+      </c>
+      <c r="BT22" s="2" t="n">
+        <v>95.22</v>
+      </c>
+      <c r="BU22" s="2" t="n">
+        <v>96.12</v>
+      </c>
+      <c r="BV22" s="2" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="BW22" s="2" t="n">
+        <v>98.81999999999999</v>
+      </c>
+      <c r="BX22" s="2" t="n">
+        <v>99.73</v>
+      </c>
+      <c r="BY22" s="2" t="n">
+        <v>96.58</v>
+      </c>
+      <c r="BZ22" s="2" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="CA22" s="2" t="n">
+        <v>88.39</v>
+      </c>
+      <c r="CB22" s="2" t="n">
+        <v>76.16</v>
+      </c>
+      <c r="CC22" s="2" t="n">
+        <v>101.02</v>
+      </c>
+      <c r="CD22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE22" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>100.27</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>66.98</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>101.32</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>101.08</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>43.02</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>100.75</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>97.53</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <v>93.72</v>
+      </c>
+      <c r="T23" s="2" t="n">
+        <v>97.73</v>
+      </c>
+      <c r="U23" s="2" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="V23" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W23" s="2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X23" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Y23" s="2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z23" s="2" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AA23" s="2" t="n">
+        <v>101.51</v>
+      </c>
+      <c r="AB23" s="2" t="n">
+        <v>101.86</v>
+      </c>
+      <c r="AC23" s="2" t="n">
+        <v>99.88</v>
+      </c>
+      <c r="AD23" s="2" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="AE23" s="2" t="n">
+        <v>71.31999999999999</v>
+      </c>
+      <c r="AF23" s="2" t="n">
+        <v>67.56</v>
+      </c>
+      <c r="AG23" s="2" t="n">
+        <v>87.55</v>
+      </c>
+      <c r="AH23" s="2" t="n">
+        <v>89.39</v>
+      </c>
+      <c r="AI23" s="2" t="n">
+        <v>86.13</v>
+      </c>
+      <c r="AJ23" s="2" t="n">
+        <v>63.95</v>
+      </c>
+      <c r="AK23" s="2" t="n">
+        <v>51.13</v>
+      </c>
+      <c r="AL23" s="2" t="n">
+        <v>55.97</v>
+      </c>
+      <c r="AM23" s="2" t="n">
+        <v>63.99</v>
+      </c>
+      <c r="AN23" s="2" t="n">
+        <v>69.04000000000001</v>
+      </c>
+      <c r="AO23" s="2" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="AP23" s="2" t="n">
+        <v>96.81999999999999</v>
+      </c>
+      <c r="AQ23" s="2" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="AR23" s="2" t="n">
+        <v>95.33</v>
+      </c>
+      <c r="AS23" s="2" t="n">
+        <v>96.41</v>
+      </c>
+      <c r="AT23" s="2" t="n">
+        <v>98.20999999999999</v>
+      </c>
+      <c r="AU23" s="2" t="n">
+        <v>97.48</v>
+      </c>
+      <c r="AV23" s="2" t="n">
+        <v>97.88</v>
+      </c>
+      <c r="AW23" s="2" t="n">
+        <v>100.22</v>
+      </c>
+      <c r="AX23" s="2" t="n">
+        <v>98.28</v>
+      </c>
+      <c r="AY23" s="2" t="n">
+        <v>100.02</v>
+      </c>
+      <c r="AZ23" s="2" t="n">
+        <v>100.77</v>
+      </c>
+      <c r="BA23" s="2" t="n">
+        <v>101.76</v>
+      </c>
+      <c r="BB23" s="2" t="n">
+        <v>102.57</v>
+      </c>
+      <c r="BC23" s="2" t="n">
+        <v>99.83</v>
+      </c>
+      <c r="BD23" s="2" t="n">
+        <v>97.76000000000001</v>
+      </c>
+      <c r="BE23" s="2" t="n">
+        <v>88.89</v>
+      </c>
+      <c r="BF23" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG23" s="2" t="n">
+        <v>98.84</v>
+      </c>
+      <c r="BH23" s="2" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="BI23" s="2" t="n">
+        <v>92.48</v>
+      </c>
+      <c r="BJ23" s="2" t="n">
+        <v>97.42</v>
+      </c>
+      <c r="BK23" s="2" t="n">
+        <v>99.22</v>
+      </c>
+      <c r="BL23" s="2" t="n">
+        <v>100.22</v>
+      </c>
+      <c r="BM23" s="2" t="n">
+        <v>100.15</v>
+      </c>
+      <c r="BN23" s="2" t="n">
+        <v>98.59</v>
+      </c>
+      <c r="BO23" s="2" t="n">
+        <v>97.98999999999999</v>
+      </c>
+      <c r="BP23" s="2" t="n">
+        <v>100.47</v>
+      </c>
+      <c r="BQ23" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR23" s="2" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="BS23" s="2" t="n">
+        <v>93.81</v>
+      </c>
+      <c r="BT23" s="2" t="n">
+        <v>90.53</v>
+      </c>
+      <c r="BU23" s="2" t="n">
+        <v>96.42</v>
+      </c>
+      <c r="BV23" s="2" t="n">
+        <v>100.29</v>
+      </c>
+      <c r="BW23" s="2" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="BX23" s="2" t="n">
+        <v>98.73</v>
+      </c>
+      <c r="BY23" s="2" t="n">
+        <v>95.91</v>
+      </c>
+      <c r="BZ23" s="2" t="n">
+        <v>95.26000000000001</v>
+      </c>
+      <c r="CA23" s="2" t="n">
+        <v>98.31</v>
+      </c>
+      <c r="CB23" s="2" t="n">
+        <v>60.67</v>
+      </c>
+      <c r="CC23" s="2" t="n">
+        <v>101.28</v>
+      </c>
+      <c r="CD23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE23" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>101.93</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>30.33</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>101.51</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>100.45</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>102.22</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>51.26</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>100.29</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>100.89</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>97.16</v>
+      </c>
+      <c r="T24" s="2" t="n">
+        <v>93.36</v>
+      </c>
+      <c r="U24" s="2" t="n">
+        <v>97.36</v>
+      </c>
+      <c r="V24" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="W24" s="2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="X24" s="2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Y24" s="2" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="Z24" s="2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AA24" s="2" t="n">
+        <v>101.16</v>
+      </c>
+      <c r="AB24" s="2" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="AC24" s="2" t="n">
+        <v>98.31</v>
+      </c>
+      <c r="AD24" s="2" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="AE24" s="2" t="n">
+        <v>65.67</v>
+      </c>
+      <c r="AF24" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG24" s="2" t="n">
+        <v>64.26000000000001</v>
+      </c>
+      <c r="AH24" s="2" t="n">
+        <v>79.20999999999999</v>
+      </c>
+      <c r="AI24" s="2" t="n">
+        <v>83.01000000000001</v>
+      </c>
+      <c r="AJ24" s="2" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="AK24" s="2" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="AL24" s="2" t="n">
+        <v>73.05</v>
+      </c>
+      <c r="AM24" s="2" t="n">
+        <v>76.02</v>
+      </c>
+      <c r="AN24" s="2" t="n">
+        <v>99.14</v>
+      </c>
+      <c r="AO24" s="2" t="n">
+        <v>100.89</v>
+      </c>
+      <c r="AP24" s="2" t="n">
+        <v>99.63</v>
+      </c>
+      <c r="AQ24" s="2" t="n">
+        <v>97.88</v>
+      </c>
+      <c r="AR24" s="2" t="n">
+        <v>100.02</v>
+      </c>
+      <c r="AS24" s="2" t="n">
+        <v>97.48999999999999</v>
+      </c>
+      <c r="AT24" s="2" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="AU24" s="2" t="n">
+        <v>94.97</v>
+      </c>
+      <c r="AV24" s="2" t="n">
+        <v>96.04000000000001</v>
+      </c>
+      <c r="AW24" s="2" t="n">
+        <v>97.84</v>
+      </c>
+      <c r="AX24" s="2" t="n">
+        <v>97.11</v>
+      </c>
+      <c r="AY24" s="2" t="n">
+        <v>97.51000000000001</v>
+      </c>
+      <c r="AZ24" s="2" t="n">
+        <v>99.84</v>
+      </c>
+      <c r="BA24" s="2" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="BB24" s="2" t="n">
+        <v>99.64</v>
+      </c>
+      <c r="BC24" s="2" t="n">
+        <v>100.39</v>
+      </c>
+      <c r="BD24" s="2" t="n">
+        <v>98.34999999999999</v>
+      </c>
+      <c r="BE24" s="2" t="n">
+        <v>88.55</v>
+      </c>
+      <c r="BF24" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG24" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="BH24" s="2" t="n">
+        <v>99.84999999999999</v>
+      </c>
+      <c r="BI24" s="2" t="n">
+        <v>95.15000000000001</v>
+      </c>
+      <c r="BJ24" s="2" t="n">
+        <v>92.34</v>
+      </c>
+      <c r="BK24" s="2" t="n">
+        <v>97.27</v>
+      </c>
+      <c r="BL24" s="2" t="n">
+        <v>99.56</v>
+      </c>
+      <c r="BM24" s="2" t="n">
+        <v>98.43000000000001</v>
+      </c>
+      <c r="BN24" s="2" t="n">
+        <v>97.84</v>
+      </c>
+      <c r="BO24" s="2" t="n">
+        <v>100.32</v>
+      </c>
+      <c r="BP24" s="2" t="n">
+        <v>102.07</v>
+      </c>
+      <c r="BQ24" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR24" s="2" t="n">
+        <v>99.87</v>
+      </c>
+      <c r="BS24" s="2" t="n">
+        <v>101.28</v>
+      </c>
+      <c r="BT24" s="2" t="n">
+        <v>95.01000000000001</v>
+      </c>
+      <c r="BU24" s="2" t="n">
+        <v>91.69</v>
+      </c>
+      <c r="BV24" s="2" t="n">
+        <v>97.66</v>
+      </c>
+      <c r="BW24" s="2" t="n">
+        <v>99.15000000000001</v>
+      </c>
+      <c r="BX24" s="2" t="n">
+        <v>97.14</v>
+      </c>
+      <c r="BY24" s="2" t="n">
+        <v>96.48</v>
+      </c>
+      <c r="BZ24" s="2" t="n">
+        <v>99.56999999999999</v>
+      </c>
+      <c r="CA24" s="2" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="CB24" s="2" t="n">
+        <v>61.12</v>
+      </c>
+      <c r="CC24" s="2" t="n">
+        <v>101.47</v>
+      </c>
+      <c r="CD24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE24" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>73.81999999999999</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>101.98</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>101.86</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>103.68</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>104.85</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="T25" s="2" t="n">
+        <v>101.74</v>
+      </c>
+      <c r="U25" s="2" t="n">
+        <v>95.18000000000001</v>
+      </c>
+      <c r="V25" s="2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W25" s="2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X25" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="Y25" s="2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z25" s="2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AA25" s="2" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="AB25" s="2" t="n">
+        <v>102.38</v>
+      </c>
+      <c r="AC25" s="2" t="n">
+        <v>101.48</v>
+      </c>
+      <c r="AD25" s="2" t="n">
+        <v>104.28</v>
+      </c>
+      <c r="AE25" s="2" t="n">
+        <v>82.44</v>
+      </c>
+      <c r="AF25" s="2" t="n">
+        <v>73.20999999999999</v>
+      </c>
+      <c r="AG25" s="2" t="n">
+        <v>65.06</v>
+      </c>
+      <c r="AH25" s="2" t="n">
+        <v>66.55</v>
+      </c>
+      <c r="AI25" s="2" t="n">
+        <v>70.73</v>
+      </c>
+      <c r="AJ25" s="2" t="n">
+        <v>70.05</v>
+      </c>
+      <c r="AK25" s="2" t="n">
+        <v>67.94</v>
+      </c>
+      <c r="AL25" s="2" t="n">
+        <v>79.39</v>
+      </c>
+      <c r="AM25" s="2" t="n">
+        <v>77.88</v>
+      </c>
+      <c r="AN25" s="2" t="n">
+        <v>98.61</v>
+      </c>
+      <c r="AO25" s="2" t="n">
+        <v>104.88</v>
+      </c>
+      <c r="AP25" s="2" t="n">
+        <v>104.41</v>
+      </c>
+      <c r="AQ25" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="AR25" s="2" t="n">
+        <v>104.19</v>
+      </c>
+      <c r="AS25" s="2" t="n">
+        <v>103.82</v>
+      </c>
+      <c r="AT25" s="2" t="n">
+        <v>101.41</v>
+      </c>
+      <c r="AU25" s="2" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="AV25" s="2" t="n">
+        <v>101.27</v>
+      </c>
+      <c r="AW25" s="2" t="n">
+        <v>100.41</v>
+      </c>
+      <c r="AX25" s="2" t="n">
+        <v>99.08</v>
+      </c>
+      <c r="AY25" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="AZ25" s="2" t="n">
+        <v>100.42</v>
+      </c>
+      <c r="BA25" s="2" t="n">
+        <v>98.91</v>
+      </c>
+      <c r="BB25" s="2" t="n">
+        <v>99.56</v>
+      </c>
+      <c r="BC25" s="2" t="n">
+        <v>102.29</v>
+      </c>
+      <c r="BD25" s="2" t="n">
+        <v>102.07</v>
+      </c>
+      <c r="BE25" s="2" t="n">
+        <v>91.16</v>
+      </c>
+      <c r="BF25" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG25" s="2" t="n">
+        <v>102.32</v>
+      </c>
+      <c r="BH25" s="2" t="n">
+        <v>101.92</v>
+      </c>
+      <c r="BI25" s="2" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="BJ25" s="2" t="n">
+        <v>98.45</v>
+      </c>
+      <c r="BK25" s="2" t="n">
+        <v>94.93000000000001</v>
+      </c>
+      <c r="BL25" s="2" t="n">
+        <v>97.98</v>
+      </c>
+      <c r="BM25" s="2" t="n">
+        <v>100.62</v>
+      </c>
+      <c r="BN25" s="2" t="n">
+        <v>101.78</v>
+      </c>
+      <c r="BO25" s="2" t="n">
+        <v>103.66</v>
+      </c>
+      <c r="BP25" s="2" t="n">
+        <v>103.43</v>
+      </c>
+      <c r="BQ25" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR25" s="2" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="BS25" s="2" t="n">
+        <v>103.49</v>
+      </c>
+      <c r="BT25" s="2" t="n">
+        <v>104.22</v>
+      </c>
+      <c r="BU25" s="2" t="n">
+        <v>100.45</v>
+      </c>
+      <c r="BV25" s="2" t="n">
+        <v>95.54000000000001</v>
+      </c>
+      <c r="BW25" s="2" t="n">
+        <v>97.36</v>
+      </c>
+      <c r="BX25" s="2" t="n">
+        <v>101.67</v>
+      </c>
+      <c r="BY25" s="2" t="n">
+        <v>102.24</v>
+      </c>
+      <c r="BZ25" s="2" t="n">
+        <v>105.56</v>
+      </c>
+      <c r="CA25" s="2" t="n">
+        <v>104.66</v>
+      </c>
+      <c r="CB25" s="2" t="n">
+        <v>46.41</v>
+      </c>
+      <c r="CC25" s="2" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="CD25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE25" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>99.47</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>102.39</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>100.89</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>101.39</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>101.36</v>
+      </c>
+      <c r="S26" s="2" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="T26" s="2" t="n">
+        <v>103.96</v>
+      </c>
+      <c r="U26" s="2" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="V26" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="W26" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X26" s="2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Y26" s="2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z26" s="2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA26" s="2" t="n">
+        <v>102.12</v>
+      </c>
+      <c r="AB26" s="2" t="n">
+        <v>101.29</v>
+      </c>
+      <c r="AC26" s="2" t="n">
+        <v>103.89</v>
+      </c>
+      <c r="AD26" s="2" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="AE26" s="2" t="n">
+        <v>97.12</v>
+      </c>
+      <c r="AF26" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="AG26" s="2" t="n">
+        <v>77.95999999999999</v>
+      </c>
+      <c r="AH26" s="2" t="n">
+        <v>71.39</v>
+      </c>
+      <c r="AI26" s="2" t="n">
+        <v>71.33</v>
+      </c>
+      <c r="AJ26" s="2" t="n">
+        <v>72.92</v>
+      </c>
+      <c r="AK26" s="2" t="n">
+        <v>60.69</v>
+      </c>
+      <c r="AL26" s="2" t="n">
+        <v>78.17</v>
+      </c>
+      <c r="AM26" s="2" t="n">
+        <v>125.02</v>
+      </c>
+      <c r="AN26" s="2" t="n">
+        <v>95.02</v>
+      </c>
+      <c r="AO26" s="2" t="n">
+        <v>101.68</v>
+      </c>
+      <c r="AP26" s="2" t="n">
+        <v>103.18</v>
+      </c>
+      <c r="AQ26" s="2" t="n">
+        <v>103.03</v>
+      </c>
+      <c r="AR26" s="2" t="n">
+        <v>103.62</v>
+      </c>
+      <c r="AS26" s="2" t="n">
+        <v>103.81</v>
+      </c>
+      <c r="AT26" s="2" t="n">
+        <v>102.44</v>
+      </c>
+      <c r="AU26" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="AV26" s="2" t="n">
+        <v>103.62</v>
+      </c>
+      <c r="AW26" s="2" t="n">
+        <v>101.22</v>
+      </c>
+      <c r="AX26" s="2" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="AY26" s="2" t="n">
+        <v>101.07</v>
+      </c>
+      <c r="AZ26" s="2" t="n">
+        <v>100.23</v>
+      </c>
+      <c r="BA26" s="2" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="BB26" s="2" t="n">
+        <v>98.81</v>
+      </c>
+      <c r="BC26" s="2" t="n">
+        <v>100.23</v>
+      </c>
+      <c r="BD26" s="2" t="n">
+        <v>102.29</v>
+      </c>
+      <c r="BE26" s="2" t="n">
+        <v>90.98999999999999</v>
+      </c>
+      <c r="BF26" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG26" s="2" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="BH26" s="2" t="n">
+        <v>99.39</v>
+      </c>
+      <c r="BI26" s="2" t="n">
+        <v>101.29</v>
+      </c>
+      <c r="BJ26" s="2" t="n">
+        <v>100.77</v>
+      </c>
+      <c r="BK26" s="2" t="n">
+        <v>97.84</v>
+      </c>
+      <c r="BL26" s="2" t="n">
+        <v>101.29</v>
+      </c>
+      <c r="BM26" s="2" t="n">
+        <v>101.15</v>
+      </c>
+      <c r="BN26" s="2" t="n">
+        <v>103.03</v>
+      </c>
+      <c r="BO26" s="2" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="BP26" s="2" t="n">
+        <v>104.28</v>
+      </c>
+      <c r="BQ26" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR26" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="BS26" s="2" t="n">
+        <v>98.36</v>
+      </c>
+      <c r="BT26" s="2" t="n">
+        <v>101.79</v>
+      </c>
+      <c r="BU26" s="2" t="n">
+        <v>102.51</v>
+      </c>
+      <c r="BV26" s="2" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="BW26" s="2" t="n">
+        <v>101.44</v>
+      </c>
+      <c r="BX26" s="2" t="n">
+        <v>100.56</v>
+      </c>
+      <c r="BY26" s="2" t="n">
+        <v>103.82</v>
+      </c>
+      <c r="BZ26" s="2" t="n">
+        <v>102.94</v>
+      </c>
+      <c r="CA26" s="2" t="n">
+        <v>105.36</v>
+      </c>
+      <c r="CB26" s="2" t="n">
+        <v>50.43</v>
+      </c>
+      <c r="CC26" s="2" t="n">
+        <v>102.19</v>
+      </c>
+      <c r="CD26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE26" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>100.32</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>102.97</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>56.01</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>20.46</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>100.13</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>15.19</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>104.47</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>98.95999999999999</v>
+      </c>
+      <c r="T27" s="2" t="n">
+        <v>99.84</v>
+      </c>
+      <c r="U27" s="2" t="n">
+        <v>99.03</v>
+      </c>
+      <c r="V27" s="2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W27" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X27" s="2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Y27" s="2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z27" s="2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA27" s="2" t="n">
+        <v>101.69</v>
+      </c>
+      <c r="AB27" s="2" t="n">
+        <v>102.92</v>
+      </c>
+      <c r="AC27" s="2" t="n">
+        <v>103.93</v>
+      </c>
+      <c r="AD27" s="2" t="n">
+        <v>103.17</v>
+      </c>
+      <c r="AE27" s="2" t="n">
+        <v>96.31</v>
+      </c>
+      <c r="AF27" s="2" t="n">
+        <v>75.45999999999999</v>
+      </c>
+      <c r="AG27" s="2" t="n">
+        <v>126.51</v>
+      </c>
+      <c r="AH27" s="2" t="n">
+        <v>108.72</v>
+      </c>
+      <c r="AI27" s="2" t="n">
+        <v>101.78</v>
+      </c>
+      <c r="AJ27" s="2" t="n">
+        <v>53.75</v>
+      </c>
+      <c r="AK27" s="2" t="n">
+        <v>58.27</v>
+      </c>
+      <c r="AL27" s="2" t="n">
+        <v>57.62</v>
+      </c>
+      <c r="AM27" s="2" t="n">
+        <v>61.29</v>
+      </c>
+      <c r="AN27" s="2" t="n">
+        <v>62.96</v>
+      </c>
+      <c r="AO27" s="2" t="n">
+        <v>102.42</v>
+      </c>
+      <c r="AP27" s="2" t="n">
+        <v>101.47</v>
+      </c>
+      <c r="AQ27" s="2" t="n">
+        <v>100.33</v>
+      </c>
+      <c r="AR27" s="2" t="n">
+        <v>101.99</v>
+      </c>
+      <c r="AS27" s="2" t="n">
+        <v>100.28</v>
+      </c>
+      <c r="AT27" s="2" t="n">
+        <v>100.26</v>
+      </c>
+      <c r="AU27" s="2" t="n">
+        <v>98.56</v>
+      </c>
+      <c r="AV27" s="2" t="n">
+        <v>98.91</v>
+      </c>
+      <c r="AW27" s="2" t="n">
+        <v>100.17</v>
+      </c>
+      <c r="AX27" s="2" t="n">
+        <v>99.26000000000001</v>
+      </c>
+      <c r="AY27" s="2" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="AZ27" s="2" t="n">
+        <v>100.75</v>
+      </c>
+      <c r="BA27" s="2" t="n">
+        <v>101.24</v>
+      </c>
+      <c r="BB27" s="2" t="n">
+        <v>101.42</v>
+      </c>
+      <c r="BC27" s="2" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="BD27" s="2" t="n">
+        <v>99.67</v>
+      </c>
+      <c r="BE27" s="2" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="BF27" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG27" s="2" t="n">
+        <v>100.93</v>
+      </c>
+      <c r="BH27" s="2" t="n">
+        <v>100.22</v>
+      </c>
+      <c r="BI27" s="2" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="BJ27" s="2" t="n">
+        <v>97.28</v>
+      </c>
+      <c r="BK27" s="2" t="n">
+        <v>96.68000000000001</v>
+      </c>
+      <c r="BL27" s="2" t="n">
+        <v>100.73</v>
+      </c>
+      <c r="BM27" s="2" t="n">
+        <v>101.44</v>
+      </c>
+      <c r="BN27" s="2" t="n">
+        <v>102.33</v>
+      </c>
+      <c r="BO27" s="2" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="BP27" s="2" t="n">
+        <v>101.82</v>
+      </c>
+      <c r="BQ27" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR27" s="2" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="BS27" s="2" t="n">
+        <v>100.86</v>
+      </c>
+      <c r="BT27" s="2" t="n">
+        <v>97.69</v>
+      </c>
+      <c r="BU27" s="2" t="n">
+        <v>97.15000000000001</v>
+      </c>
+      <c r="BV27" s="2" t="n">
+        <v>95.55</v>
+      </c>
+      <c r="BW27" s="2" t="n">
+        <v>101.17</v>
+      </c>
+      <c r="BX27" s="2" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="BY27" s="2" t="n">
+        <v>101.88</v>
+      </c>
+      <c r="BZ27" s="2" t="n">
+        <v>101.34</v>
+      </c>
+      <c r="CA27" s="2" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="CB27" s="2" t="n">
+        <v>53.11</v>
+      </c>
+      <c r="CC27" s="2" t="n">
+        <v>101.69</v>
+      </c>
+      <c r="CD27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE27" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>99.64</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>15.19</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>101.73</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>28.42</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>101.18</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>101.63</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>101.82</v>
+      </c>
+      <c r="T28" s="2" t="n">
+        <v>99.27</v>
+      </c>
+      <c r="U28" s="2" t="n">
+        <v>98.52</v>
+      </c>
+      <c r="V28" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W28" s="2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X28" s="2" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Y28" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z28" s="2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AA28" s="2" t="n">
+        <v>100.73</v>
+      </c>
+      <c r="AB28" s="2" t="n">
+        <v>101.53</v>
+      </c>
+      <c r="AC28" s="2" t="n">
+        <v>104.85</v>
+      </c>
+      <c r="AD28" s="2" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="AE28" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF28" s="2" t="n">
+        <v>71.92</v>
+      </c>
+      <c r="AG28" s="2" t="n">
+        <v>117.37</v>
+      </c>
+      <c r="AH28" s="2" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="AI28" s="2" t="n">
+        <v>101.22</v>
+      </c>
+      <c r="AJ28" s="2" t="n">
+        <v>61.22</v>
+      </c>
+      <c r="AK28" s="2" t="n">
+        <v>58.65</v>
+      </c>
+      <c r="AL28" s="2" t="n">
+        <v>54.21</v>
+      </c>
+      <c r="AM28" s="2" t="n">
+        <v>62.96</v>
+      </c>
+      <c r="AN28" s="2" t="n">
+        <v>68.09</v>
+      </c>
+      <c r="AO28" s="2" t="n">
+        <v>101.84</v>
+      </c>
+      <c r="AP28" s="2" t="n">
+        <v>101.66</v>
+      </c>
+      <c r="AQ28" s="2" t="n">
+        <v>100.04</v>
+      </c>
+      <c r="AR28" s="2" t="n">
+        <v>101.33</v>
+      </c>
+      <c r="AS28" s="2" t="n">
+        <v>100.23</v>
+      </c>
+      <c r="AT28" s="2" t="n">
+        <v>99.73999999999999</v>
+      </c>
+      <c r="AU28" s="2" t="n">
+        <v>99.13</v>
+      </c>
+      <c r="AV28" s="2" t="n">
+        <v>99.04000000000001</v>
+      </c>
+      <c r="AW28" s="2" t="n">
+        <v>99.81</v>
+      </c>
+      <c r="AX28" s="2" t="n">
+        <v>98.95999999999999</v>
+      </c>
+      <c r="AY28" s="2" t="n">
+        <v>99.26000000000001</v>
+      </c>
+      <c r="AZ28" s="2" t="n">
+        <v>100.22</v>
+      </c>
+      <c r="BA28" s="2" t="n">
+        <v>99.56999999999999</v>
+      </c>
+      <c r="BB28" s="2" t="n">
+        <v>100.57</v>
+      </c>
+      <c r="BC28" s="2" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="BD28" s="2" t="n">
+        <v>99.33</v>
+      </c>
+      <c r="BE28" s="2" t="n">
+        <v>88.45999999999999</v>
+      </c>
+      <c r="BF28" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG28" s="2" t="n">
+        <v>99.28</v>
+      </c>
+      <c r="BH28" s="2" t="n">
+        <v>99.78</v>
+      </c>
+      <c r="BI28" s="2" t="n">
+        <v>99.16</v>
+      </c>
+      <c r="BJ28" s="2" t="n">
+        <v>97.83</v>
+      </c>
+      <c r="BK28" s="2" t="n">
+        <v>94.04000000000001</v>
+      </c>
+      <c r="BL28" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BM28" s="2" t="n">
+        <v>101.11</v>
+      </c>
+      <c r="BN28" s="2" t="n">
+        <v>101.98</v>
+      </c>
+      <c r="BO28" s="2" t="n">
+        <v>100.99</v>
+      </c>
+      <c r="BP28" s="2" t="n">
+        <v>99.61</v>
+      </c>
+      <c r="BQ28" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR28" s="2" t="n">
+        <v>98.84</v>
+      </c>
+      <c r="BS28" s="2" t="n">
+        <v>99.87</v>
+      </c>
+      <c r="BT28" s="2" t="n">
+        <v>98.78</v>
+      </c>
+      <c r="BU28" s="2" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="BV28" s="2" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="BW28" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="BX28" s="2" t="n">
+        <v>101.18</v>
+      </c>
+      <c r="BY28" s="2" t="n">
+        <v>101.44</v>
+      </c>
+      <c r="BZ28" s="2" t="n">
+        <v>101.58</v>
+      </c>
+      <c r="CA28" s="2" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="CB28" s="2" t="n">
+        <v>53.05</v>
+      </c>
+      <c r="CC28" s="2" t="n">
+        <v>101.19</v>
+      </c>
+      <c r="CD28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE28" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>44.99</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>101.06</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>24.48</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>100.51</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>102.11</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>45.75</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>103.26</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>101.64</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>100.28</v>
+      </c>
+      <c r="T29" s="2" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="U29" s="2" t="n">
+        <v>99.61</v>
+      </c>
+      <c r="V29" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W29" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="X29" s="2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Y29" s="2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z29" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA29" s="2" t="n">
+        <v>102.18</v>
+      </c>
+      <c r="AB29" s="2" t="n">
+        <v>98.91</v>
+      </c>
+      <c r="AC29" s="2" t="n">
+        <v>99.59</v>
+      </c>
+      <c r="AD29" s="2" t="n">
+        <v>100.16</v>
+      </c>
+      <c r="AE29" s="2" t="n">
+        <v>77.18000000000001</v>
+      </c>
+      <c r="AF29" s="2" t="n">
+        <v>70.06</v>
+      </c>
+      <c r="AG29" s="2" t="n">
+        <v>68.68000000000001</v>
+      </c>
+      <c r="AH29" s="2" t="n">
+        <v>65.69</v>
+      </c>
+      <c r="AI29" s="2" t="n">
+        <v>68.02</v>
+      </c>
+      <c r="AJ29" s="2" t="n">
+        <v>52.69</v>
+      </c>
+      <c r="AK29" s="2" t="n">
+        <v>63.43</v>
+      </c>
+      <c r="AL29" s="2" t="n">
+        <v>75.12</v>
+      </c>
+      <c r="AM29" s="2" t="n">
+        <v>77.37</v>
+      </c>
+      <c r="AN29" s="2" t="n">
+        <v>74.28</v>
+      </c>
+      <c r="AO29" s="2" t="n">
+        <v>102.56</v>
+      </c>
+      <c r="AP29" s="2" t="n">
+        <v>101.68</v>
+      </c>
+      <c r="AQ29" s="2" t="n">
+        <v>100.48</v>
+      </c>
+      <c r="AR29" s="2" t="n">
+        <v>101.28</v>
+      </c>
+      <c r="AS29" s="2" t="n">
+        <v>100.24</v>
+      </c>
+      <c r="AT29" s="2" t="n">
+        <v>99.93000000000001</v>
+      </c>
+      <c r="AU29" s="2" t="n">
+        <v>99.19</v>
+      </c>
+      <c r="AV29" s="2" t="n">
+        <v>99.48</v>
+      </c>
+      <c r="AW29" s="2" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="AX29" s="2" t="n">
+        <v>99.77</v>
+      </c>
+      <c r="AY29" s="2" t="n">
+        <v>99.62</v>
+      </c>
+      <c r="AZ29" s="2" t="n">
+        <v>98.23999999999999</v>
+      </c>
+      <c r="BA29" s="2" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="BB29" s="2" t="n">
+        <v>98.12</v>
+      </c>
+      <c r="BC29" s="2" t="n">
+        <v>97.92</v>
+      </c>
+      <c r="BD29" s="2" t="n">
+        <v>99.23999999999999</v>
+      </c>
+      <c r="BE29" s="2" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="BF29" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG29" s="2" t="n">
+        <v>100.71</v>
+      </c>
+      <c r="BH29" s="2" t="n">
+        <v>100.54</v>
+      </c>
+      <c r="BI29" s="2" t="n">
+        <v>99.48999999999999</v>
+      </c>
+      <c r="BJ29" s="2" t="n">
+        <v>98.11</v>
+      </c>
+      <c r="BK29" s="2" t="n">
+        <v>98.89</v>
+      </c>
+      <c r="BL29" s="2" t="n">
+        <v>100.24</v>
+      </c>
+      <c r="BM29" s="2" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="BN29" s="2" t="n">
+        <v>102.81</v>
+      </c>
+      <c r="BO29" s="2" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="BP29" s="2" t="n">
+        <v>102.39</v>
+      </c>
+      <c r="BQ29" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR29" s="2" t="n">
+        <v>100.78</v>
+      </c>
+      <c r="BS29" s="2" t="n">
+        <v>99.79000000000001</v>
+      </c>
+      <c r="BT29" s="2" t="n">
+        <v>100.04</v>
+      </c>
+      <c r="BU29" s="2" t="n">
+        <v>97.83</v>
+      </c>
+      <c r="BV29" s="2" t="n">
+        <v>99.42</v>
+      </c>
+      <c r="BW29" s="2" t="n">
+        <v>100.58</v>
+      </c>
+      <c r="BX29" s="2" t="n">
+        <v>98.31</v>
+      </c>
+      <c r="BY29" s="2" t="n">
+        <v>104.29</v>
+      </c>
+      <c r="BZ29" s="2" t="n">
+        <v>103.28</v>
+      </c>
+      <c r="CA29" s="2" t="n">
+        <v>102.51</v>
+      </c>
+      <c r="CB29" s="2" t="n">
+        <v>52.28</v>
+      </c>
+      <c r="CC29" s="2" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="CD29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE29" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2024-11-11</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>102.22</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>103.23</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>100.84</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>102.59</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>100.12</v>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>105.26</v>
+      </c>
+      <c r="T30" s="2" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="U30" s="2" t="n">
+        <v>104.31</v>
+      </c>
+      <c r="V30" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="W30" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X30" s="2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y30" s="2" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Z30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA30" s="2" t="n">
+        <v>101.63</v>
+      </c>
+      <c r="AB30" s="2" t="n">
+        <v>102.94</v>
+      </c>
+      <c r="AC30" s="2" t="n">
+        <v>105.13</v>
+      </c>
+      <c r="AD30" s="2" t="n">
+        <v>111.86</v>
+      </c>
+      <c r="AE30" s="2" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="AF30" s="2" t="n">
+        <v>77.43000000000001</v>
+      </c>
+      <c r="AG30" s="2" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="AH30" s="2" t="n">
+        <v>81.06999999999999</v>
+      </c>
+      <c r="AI30" s="2" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="AJ30" s="2" t="n">
+        <v>78.15000000000001</v>
+      </c>
+      <c r="AK30" s="2" t="n">
+        <v>82.76000000000001</v>
+      </c>
+      <c r="AL30" s="2" t="n">
+        <v>84.26000000000001</v>
+      </c>
+      <c r="AM30" s="2" t="n">
+        <v>87.12</v>
+      </c>
+      <c r="AN30" s="2" t="n">
+        <v>80.56999999999999</v>
+      </c>
+      <c r="AO30" s="2" t="n">
+        <v>100.89</v>
+      </c>
+      <c r="AP30" s="2" t="n">
+        <v>102.51</v>
+      </c>
+      <c r="AQ30" s="2" t="n">
+        <v>103.69</v>
+      </c>
+      <c r="AR30" s="2" t="n">
+        <v>102.33</v>
+      </c>
+      <c r="AS30" s="2" t="n">
+        <v>103.57</v>
+      </c>
+      <c r="AT30" s="2" t="n">
+        <v>103.93</v>
+      </c>
+      <c r="AU30" s="2" t="n">
+        <v>104.81</v>
+      </c>
+      <c r="AV30" s="2" t="n">
+        <v>105.13</v>
+      </c>
+      <c r="AW30" s="2" t="n">
+        <v>103.76</v>
+      </c>
+      <c r="AX30" s="2" t="n">
+        <v>105.46</v>
+      </c>
+      <c r="AY30" s="2" t="n">
+        <v>104.29</v>
+      </c>
+      <c r="AZ30" s="2" t="n">
+        <v>103.31</v>
+      </c>
+      <c r="BA30" s="2" t="n">
+        <v>103.11</v>
+      </c>
+      <c r="BB30" s="2" t="n">
+        <v>102.39</v>
+      </c>
+      <c r="BC30" s="2" t="n">
+        <v>102.22</v>
+      </c>
+      <c r="BD30" s="2" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="BE30" s="2" t="n">
+        <v>89.41</v>
+      </c>
+      <c r="BF30" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG30" s="2" t="n">
+        <v>99.53</v>
+      </c>
+      <c r="BH30" s="2" t="n">
+        <v>95.19</v>
+      </c>
+      <c r="BI30" s="2" t="n">
+        <v>97.04000000000001</v>
+      </c>
+      <c r="BJ30" s="2" t="n">
+        <v>97.54000000000001</v>
+      </c>
+      <c r="BK30" s="2" t="n">
+        <v>97.64</v>
+      </c>
+      <c r="BL30" s="2" t="n">
+        <v>99.73</v>
+      </c>
+      <c r="BM30" s="2" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="BN30" s="2" t="n">
+        <v>99.77</v>
+      </c>
+      <c r="BO30" s="2" t="n">
+        <v>100.81</v>
+      </c>
+      <c r="BP30" s="2" t="n">
+        <v>100.56</v>
+      </c>
+      <c r="BQ30" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR30" s="2" t="n">
+        <v>99.98</v>
+      </c>
+      <c r="BS30" s="2" t="n">
+        <v>94.58</v>
+      </c>
+      <c r="BT30" s="2" t="n">
+        <v>96.42</v>
+      </c>
+      <c r="BU30" s="2" t="n">
+        <v>96.47</v>
+      </c>
+      <c r="BV30" s="2" t="n">
+        <v>96.84</v>
+      </c>
+      <c r="BW30" s="2" t="n">
+        <v>99.67</v>
+      </c>
+      <c r="BX30" s="2" t="n">
+        <v>97.31</v>
+      </c>
+      <c r="BY30" s="2" t="n">
+        <v>98.56999999999999</v>
+      </c>
+      <c r="BZ30" s="2" t="n">
+        <v>100.58</v>
+      </c>
+      <c r="CA30" s="2" t="n">
+        <v>101.24</v>
+      </c>
+      <c r="CB30" s="2" t="n">
+        <v>44.39</v>
+      </c>
+      <c r="CC30" s="2" t="n">
+        <v>101.23</v>
+      </c>
+      <c r="CD30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE30" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2024-11-20</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>100.34</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>101.89</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>101.79</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>23.27</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>101.89</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>100.94</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>99.66</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>98.48999999999999</v>
+      </c>
+      <c r="T31" s="2" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="U31" s="2" t="n">
+        <v>102.04</v>
+      </c>
+      <c r="V31" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="W31" s="2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="X31" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="Y31" s="2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z31" s="2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA31" s="2" t="n">
+        <v>101.76</v>
+      </c>
+      <c r="AB31" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="AC31" s="2" t="n">
+        <v>107.59</v>
+      </c>
+      <c r="AD31" s="2" t="n">
+        <v>110.58</v>
+      </c>
+      <c r="AE31" s="2" t="n">
+        <v>80.58</v>
+      </c>
+      <c r="AF31" s="2" t="n">
+        <v>88.61</v>
+      </c>
+      <c r="AG31" s="2" t="n">
+        <v>87.65000000000001</v>
+      </c>
+      <c r="AH31" s="2" t="n">
+        <v>91.62</v>
+      </c>
+      <c r="AI31" s="2" t="n">
+        <v>88.02</v>
+      </c>
+      <c r="AJ31" s="2" t="n">
+        <v>70.11</v>
+      </c>
+      <c r="AK31" s="2" t="n">
+        <v>80.01000000000001</v>
+      </c>
+      <c r="AL31" s="2" t="n">
+        <v>99.63</v>
+      </c>
+      <c r="AM31" s="2" t="n">
+        <v>89.66</v>
+      </c>
+      <c r="AN31" s="2" t="n">
+        <v>89.70999999999999</v>
+      </c>
+      <c r="AO31" s="2" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="AP31" s="2" t="n">
+        <v>99.81</v>
+      </c>
+      <c r="AQ31" s="2" t="n">
+        <v>100.69</v>
+      </c>
+      <c r="AR31" s="2" t="n">
+        <v>99.84999999999999</v>
+      </c>
+      <c r="AS31" s="2" t="n">
+        <v>99.31999999999999</v>
+      </c>
+      <c r="AT31" s="2" t="n">
+        <v>101.16</v>
+      </c>
+      <c r="AU31" s="2" t="n">
+        <v>98.79000000000001</v>
+      </c>
+      <c r="AV31" s="2" t="n">
+        <v>100.65</v>
+      </c>
+      <c r="AW31" s="2" t="n">
+        <v>101.71</v>
+      </c>
+      <c r="AX31" s="2" t="n">
+        <v>102.52</v>
+      </c>
+      <c r="AY31" s="2" t="n">
+        <v>103.01</v>
+      </c>
+      <c r="AZ31" s="2" t="n">
+        <v>101.98</v>
+      </c>
+      <c r="BA31" s="2" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="BB31" s="2" t="n">
+        <v>102.76</v>
+      </c>
+      <c r="BC31" s="2" t="n">
+        <v>101.59</v>
+      </c>
+      <c r="BD31" s="2" t="n">
+        <v>100.61</v>
+      </c>
+      <c r="BE31" s="2" t="n">
+        <v>87.67</v>
+      </c>
+      <c r="BF31" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG31" s="2" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="BH31" s="2" t="n">
+        <v>101.15</v>
+      </c>
+      <c r="BI31" s="2" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="BJ31" s="2" t="n">
+        <v>98.25</v>
+      </c>
+      <c r="BK31" s="2" t="n">
+        <v>97.98</v>
+      </c>
+      <c r="BL31" s="2" t="n">
+        <v>100.88</v>
+      </c>
+      <c r="BM31" s="2" t="n">
+        <v>101.38</v>
+      </c>
+      <c r="BN31" s="2" t="n">
+        <v>102.67</v>
+      </c>
+      <c r="BO31" s="2" t="n">
+        <v>102.27</v>
+      </c>
+      <c r="BP31" s="2" t="n">
+        <v>99.15000000000001</v>
+      </c>
+      <c r="BQ31" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR31" s="2" t="n">
+        <v>99.38</v>
+      </c>
+      <c r="BS31" s="2" t="n">
+        <v>101.79</v>
+      </c>
+      <c r="BT31" s="2" t="n">
+        <v>100.55</v>
+      </c>
+      <c r="BU31" s="2" t="n">
+        <v>98.65000000000001</v>
+      </c>
+      <c r="BV31" s="2" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="BW31" s="2" t="n">
+        <v>100.53</v>
+      </c>
+      <c r="BX31" s="2" t="n">
+        <v>100.37</v>
+      </c>
+      <c r="BY31" s="2" t="n">
+        <v>103.67</v>
+      </c>
+      <c r="BZ31" s="2" t="n">
+        <v>104.59</v>
+      </c>
+      <c r="CA31" s="2" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="CB31" s="2" t="n">
+        <v>53.54</v>
+      </c>
+      <c r="CC31" s="2" t="n">
+        <v>101.38</v>
+      </c>
+      <c r="CD31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE31" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2024-12-23</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>96.94</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>100.61</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>69.28</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>100.87</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>100.73</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>101.88</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>92.81</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>98.56</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>99.05</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>97.36</v>
+      </c>
+      <c r="T32" s="2" t="n">
+        <v>94.53</v>
+      </c>
+      <c r="U32" s="2" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="V32" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="W32" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="X32" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y32" s="2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z32" s="2" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AA32" s="2" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="AB32" s="2" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="AC32" s="2" t="n">
+        <v>95.76000000000001</v>
+      </c>
+      <c r="AD32" s="2" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="AE32" s="2" t="n">
+        <v>210.64</v>
+      </c>
+      <c r="AF32" s="2" t="n">
+        <v>148.88</v>
+      </c>
+      <c r="AG32" s="2" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="AH32" s="2" t="n">
+        <v>103.67</v>
+      </c>
+      <c r="AI32" s="2" t="n">
+        <v>101.64</v>
+      </c>
+      <c r="AJ32" s="2" t="n">
+        <v>82.61</v>
+      </c>
+      <c r="AK32" s="2" t="n">
+        <v>51.02</v>
+      </c>
+      <c r="AL32" s="2" t="n">
+        <v>67.88</v>
+      </c>
+      <c r="AM32" s="2" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="AN32" s="2" t="n">
+        <v>100.62</v>
+      </c>
+      <c r="AO32" s="2" t="n">
+        <v>98.68000000000001</v>
+      </c>
+      <c r="AP32" s="2" t="n">
+        <v>97.94</v>
+      </c>
+      <c r="AQ32" s="2" t="n">
+        <v>95.66</v>
+      </c>
+      <c r="AR32" s="2" t="n">
+        <v>97.95999999999999</v>
+      </c>
+      <c r="AS32" s="2" t="n">
+        <v>97.05</v>
+      </c>
+      <c r="AT32" s="2" t="n">
+        <v>94.36</v>
+      </c>
+      <c r="AU32" s="2" t="n">
+        <v>96.14</v>
+      </c>
+      <c r="AV32" s="2" t="n">
+        <v>94.62</v>
+      </c>
+      <c r="AW32" s="2" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="AX32" s="2" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="AY32" s="2" t="n">
+        <v>91.67</v>
+      </c>
+      <c r="AZ32" s="2" t="n">
+        <v>90.19</v>
+      </c>
+      <c r="BA32" s="2" t="n">
+        <v>90.25</v>
+      </c>
+      <c r="BB32" s="2" t="n">
+        <v>89.58</v>
+      </c>
+      <c r="BC32" s="2" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="BD32" s="2" t="n">
+        <v>92.83</v>
+      </c>
+      <c r="BE32" s="2" t="n">
+        <v>78.14</v>
+      </c>
+      <c r="BF32" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG32" s="2" t="n">
+        <v>98.20999999999999</v>
+      </c>
+      <c r="BH32" s="2" t="n">
+        <v>101.67</v>
+      </c>
+      <c r="BI32" s="2" t="n">
+        <v>101.32</v>
+      </c>
+      <c r="BJ32" s="2" t="n">
+        <v>101.22</v>
+      </c>
+      <c r="BK32" s="2" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="BL32" s="2" t="n">
+        <v>101.06</v>
+      </c>
+      <c r="BM32" s="2" t="n">
+        <v>98.45</v>
+      </c>
+      <c r="BN32" s="2" t="n">
+        <v>99.06999999999999</v>
+      </c>
+      <c r="BO32" s="2" t="n">
+        <v>99.39</v>
+      </c>
+      <c r="BP32" s="2" t="n">
+        <v>102.13</v>
+      </c>
+      <c r="BQ32" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR32" s="2" t="n">
+        <v>98.17</v>
+      </c>
+      <c r="BS32" s="2" t="n">
+        <v>102.76</v>
+      </c>
+      <c r="BT32" s="2" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="BU32" s="2" t="n">
+        <v>98.43000000000001</v>
+      </c>
+      <c r="BV32" s="2" t="n">
+        <v>96.62</v>
+      </c>
+      <c r="BW32" s="2" t="n">
+        <v>101.23</v>
+      </c>
+      <c r="BX32" s="2" t="n">
+        <v>97.72</v>
+      </c>
+      <c r="BY32" s="2" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="BZ32" s="2" t="n">
+        <v>98.08</v>
+      </c>
+      <c r="CA32" s="2" t="n">
+        <v>101.26</v>
+      </c>
+      <c r="CB32" s="2" t="n">
+        <v>73.09</v>
+      </c>
+      <c r="CC32" s="2" t="n">
+        <v>100.72</v>
+      </c>
+      <c r="CD32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE32" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>101.43</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>44.13</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>102.79</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>40.27</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>105.65</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>105.94</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>112.75</v>
+      </c>
+      <c r="T33" s="2" t="n">
+        <v>107.98</v>
+      </c>
+      <c r="U33" s="2" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="V33" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W33" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X33" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y33" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Z33" s="2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AA33" s="2" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="AB33" s="2" t="n">
+        <v>96.92</v>
+      </c>
+      <c r="AC33" s="2" t="n">
+        <v>103.72</v>
+      </c>
+      <c r="AD33" s="2" t="n">
+        <v>101.37</v>
+      </c>
+      <c r="AE33" s="2" t="n">
+        <v>105.43</v>
+      </c>
+      <c r="AF33" s="2" t="n">
+        <v>95.72</v>
+      </c>
+      <c r="AG33" s="2" t="n">
+        <v>90.39</v>
+      </c>
+      <c r="AH33" s="2" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="AI33" s="2" t="n">
+        <v>102.87</v>
+      </c>
+      <c r="AJ33" s="2" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="AK33" s="2" t="n">
+        <v>84.13</v>
+      </c>
+      <c r="AL33" s="2" t="n">
+        <v>134.82</v>
+      </c>
+      <c r="AM33" s="2" t="n">
+        <v>141.62</v>
+      </c>
+      <c r="AN33" s="2" t="n">
+        <v>125.61</v>
+      </c>
+      <c r="AO33" s="2" t="n">
+        <v>105.97</v>
+      </c>
+      <c r="AP33" s="2" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="AQ33" s="2" t="n">
+        <v>108.72</v>
+      </c>
+      <c r="AR33" s="2" t="n">
+        <v>108.43</v>
+      </c>
+      <c r="AS33" s="2" t="n">
+        <v>109.79</v>
+      </c>
+      <c r="AT33" s="2" t="n">
+        <v>108.78</v>
+      </c>
+      <c r="AU33" s="2" t="n">
+        <v>111.16</v>
+      </c>
+      <c r="AV33" s="2" t="n">
+        <v>109.94</v>
+      </c>
+      <c r="AW33" s="2" t="n">
+        <v>107.74</v>
+      </c>
+      <c r="AX33" s="2" t="n">
+        <v>108.71</v>
+      </c>
+      <c r="AY33" s="2" t="n">
+        <v>107.76</v>
+      </c>
+      <c r="AZ33" s="2" t="n">
+        <v>105.09</v>
+      </c>
+      <c r="BA33" s="2" t="n">
+        <v>106.82</v>
+      </c>
+      <c r="BB33" s="2" t="n">
+        <v>105.54</v>
+      </c>
+      <c r="BC33" s="2" t="n">
+        <v>102.61</v>
+      </c>
+      <c r="BD33" s="2" t="n">
+        <v>103.91</v>
+      </c>
+      <c r="BE33" s="2" t="n">
+        <v>86.20999999999999</v>
+      </c>
+      <c r="BF33" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG33" s="2" t="n">
+        <v>101.41</v>
+      </c>
+      <c r="BH33" s="2" t="n">
+        <v>101.82</v>
+      </c>
+      <c r="BI33" s="2" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="BJ33" s="2" t="n">
+        <v>100.62</v>
+      </c>
+      <c r="BK33" s="2" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="BL33" s="2" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="BM33" s="2" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="BN33" s="2" t="n">
+        <v>103.97</v>
+      </c>
+      <c r="BO33" s="2" t="n">
+        <v>103.46</v>
+      </c>
+      <c r="BP33" s="2" t="n">
+        <v>103.98</v>
+      </c>
+      <c r="BQ33" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR33" s="2" t="n">
+        <v>101.91</v>
+      </c>
+      <c r="BS33" s="2" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="BT33" s="2" t="n">
+        <v>104.73</v>
+      </c>
+      <c r="BU33" s="2" t="n">
+        <v>102.04</v>
+      </c>
+      <c r="BV33" s="2" t="n">
+        <v>104.71</v>
+      </c>
+      <c r="BW33" s="2" t="n">
+        <v>102.18</v>
+      </c>
+      <c r="BX33" s="2" t="n">
+        <v>103.76</v>
+      </c>
+      <c r="BY33" s="2" t="n">
+        <v>103.26</v>
+      </c>
+      <c r="BZ33" s="2" t="n">
+        <v>103.76</v>
+      </c>
+      <c r="CA33" s="2" t="n">
+        <v>104.37</v>
+      </c>
+      <c r="CB33" s="2" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="CC33" s="2" t="n">
+        <v>102.04</v>
+      </c>
+      <c r="CD33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE33" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2025-01-21</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>105.88</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>56.17</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>26.98</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>100.19</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>102.16</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>110.93</v>
+      </c>
+      <c r="T34" s="2" t="n">
+        <v>118.07</v>
+      </c>
+      <c r="U34" s="2" t="n">
+        <v>113.07</v>
+      </c>
+      <c r="V34" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="W34" s="2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X34" s="2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Y34" s="2" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="Z34" s="2" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="AA34" s="2" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="AB34" s="2" t="n">
+        <v>108.61</v>
+      </c>
+      <c r="AC34" s="2" t="n">
+        <v>106.12</v>
+      </c>
+      <c r="AD34" s="2" t="n">
+        <v>111.74</v>
+      </c>
+      <c r="AE34" s="2" t="n">
+        <v>146.33</v>
+      </c>
+      <c r="AF34" s="2" t="n">
+        <v>112.33</v>
+      </c>
+      <c r="AG34" s="2" t="n">
+        <v>103.22</v>
+      </c>
+      <c r="AH34" s="2" t="n">
+        <v>96.69</v>
+      </c>
+      <c r="AI34" s="2" t="n">
+        <v>106.87</v>
+      </c>
+      <c r="AJ34" s="2" t="n">
+        <v>204.65</v>
+      </c>
+      <c r="AK34" s="2" t="n">
+        <v>129.75</v>
+      </c>
+      <c r="AL34" s="2" t="n">
+        <v>145.92</v>
+      </c>
+      <c r="AM34" s="2" t="n">
+        <v>139.78</v>
+      </c>
+      <c r="AN34" s="2" t="n">
+        <v>113.39</v>
+      </c>
+      <c r="AO34" s="2" t="n">
+        <v>106.72</v>
+      </c>
+      <c r="AP34" s="2" t="n">
+        <v>108.84</v>
+      </c>
+      <c r="AQ34" s="2" t="n">
+        <v>112.23</v>
+      </c>
+      <c r="AR34" s="2" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="AS34" s="2" t="n">
+        <v>111.52</v>
+      </c>
+      <c r="AT34" s="2" t="n">
+        <v>113.32</v>
+      </c>
+      <c r="AU34" s="2" t="n">
+        <v>113.54</v>
+      </c>
+      <c r="AV34" s="2" t="n">
+        <v>114.97</v>
+      </c>
+      <c r="AW34" s="2" t="n">
+        <v>113.91</v>
+      </c>
+      <c r="AX34" s="2" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="AY34" s="2" t="n">
+        <v>115.12</v>
+      </c>
+      <c r="AZ34" s="2" t="n">
+        <v>112.81</v>
+      </c>
+      <c r="BA34" s="2" t="n">
+        <v>113.84</v>
+      </c>
+      <c r="BB34" s="2" t="n">
+        <v>112.84</v>
+      </c>
+      <c r="BC34" s="2" t="n">
+        <v>110.05</v>
+      </c>
+      <c r="BD34" s="2" t="n">
+        <v>109.07</v>
+      </c>
+      <c r="BE34" s="2" t="n">
+        <v>90.27</v>
+      </c>
+      <c r="BF34" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG34" s="2" t="n">
+        <v>98.15000000000001</v>
+      </c>
+      <c r="BH34" s="2" t="n">
+        <v>96.48</v>
+      </c>
+      <c r="BI34" s="2" t="n">
+        <v>98.23</v>
+      </c>
+      <c r="BJ34" s="2" t="n">
+        <v>99.81</v>
+      </c>
+      <c r="BK34" s="2" t="n">
+        <v>97.06999999999999</v>
+      </c>
+      <c r="BL34" s="2" t="n">
+        <v>101.15</v>
+      </c>
+      <c r="BM34" s="2" t="n">
+        <v>100.31</v>
+      </c>
+      <c r="BN34" s="2" t="n">
+        <v>99.81</v>
+      </c>
+      <c r="BO34" s="2" t="n">
+        <v>100.32</v>
+      </c>
+      <c r="BP34" s="2" t="n">
+        <v>101.57</v>
+      </c>
+      <c r="BQ34" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR34" s="2" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="BS34" s="2" t="n">
+        <v>96.37</v>
+      </c>
+      <c r="BT34" s="2" t="n">
+        <v>98.89</v>
+      </c>
+      <c r="BU34" s="2" t="n">
+        <v>100.94</v>
+      </c>
+      <c r="BV34" s="2" t="n">
+        <v>98.34</v>
+      </c>
+      <c r="BW34" s="2" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="BX34" s="2" t="n">
+        <v>99.52</v>
+      </c>
+      <c r="BY34" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BZ34" s="2" t="n">
+        <v>100.59</v>
+      </c>
+      <c r="CA34" s="2" t="n">
+        <v>102.82</v>
+      </c>
+      <c r="CB34" s="2" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="CC34" s="2" t="n">
+        <v>101.49</v>
+      </c>
+      <c r="CD34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE34" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>104.07</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>39.29</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>102.56</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>100.38</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>102.06</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>103.52</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>97.23999999999999</v>
+      </c>
+      <c r="T35" s="2" t="n">
+        <v>102.74</v>
+      </c>
+      <c r="U35" s="2" t="n">
+        <v>94.44</v>
+      </c>
+      <c r="V35" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="W35" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="X35" s="2" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="Y35" s="2" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="Z35" s="2" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA35" s="2" t="n">
+        <v>98.94</v>
+      </c>
+      <c r="AB35" s="2" t="n">
+        <v>98.02</v>
+      </c>
+      <c r="AC35" s="2" t="n">
+        <v>99.52</v>
+      </c>
+      <c r="AD35" s="2" t="n">
+        <v>95.78</v>
+      </c>
+      <c r="AE35" s="2" t="n">
+        <v>85.42</v>
+      </c>
+      <c r="AF35" s="2" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="AG35" s="2" t="n">
+        <v>92.55</v>
+      </c>
+      <c r="AH35" s="2" t="n">
+        <v>94.37</v>
+      </c>
+      <c r="AI35" s="2" t="n">
+        <v>91.17</v>
+      </c>
+      <c r="AJ35" s="2" t="n">
+        <v>79.01000000000001</v>
+      </c>
+      <c r="AK35" s="2" t="n">
+        <v>87.08</v>
+      </c>
+      <c r="AL35" s="2" t="n">
+        <v>96.98</v>
+      </c>
+      <c r="AM35" s="2" t="n">
+        <v>91.19</v>
+      </c>
+      <c r="AN35" s="2" t="n">
+        <v>89.34999999999999</v>
+      </c>
+      <c r="AO35" s="2" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="AP35" s="2" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="AQ35" s="2" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="AR35" s="2" t="n">
+        <v>97.97</v>
+      </c>
+      <c r="AS35" s="2" t="n">
+        <v>99.89</v>
+      </c>
+      <c r="AT35" s="2" t="n">
+        <v>99.36</v>
+      </c>
+      <c r="AU35" s="2" t="n">
+        <v>101.82</v>
+      </c>
+      <c r="AV35" s="2" t="n">
+        <v>101.37</v>
+      </c>
+      <c r="AW35" s="2" t="n">
+        <v>97.88</v>
+      </c>
+      <c r="AX35" s="2" t="n">
+        <v>100.93</v>
+      </c>
+      <c r="AY35" s="2" t="n">
+        <v>98.81999999999999</v>
+      </c>
+      <c r="AZ35" s="2" t="n">
+        <v>98.36</v>
+      </c>
+      <c r="BA35" s="2" t="n">
+        <v>96.72</v>
+      </c>
+      <c r="BB35" s="2" t="n">
+        <v>94.38</v>
+      </c>
+      <c r="BC35" s="2" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="BD35" s="2" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="BE35" s="2" t="n">
+        <v>96.72</v>
+      </c>
+      <c r="BF35" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG35" s="2" t="n">
+        <v>99.22</v>
+      </c>
+      <c r="BH35" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="BI35" s="2" t="n">
+        <v>94.75</v>
+      </c>
+      <c r="BJ35" s="2" t="n">
+        <v>92.70999999999999</v>
+      </c>
+      <c r="BK35" s="2" t="n">
+        <v>86.48999999999999</v>
+      </c>
+      <c r="BL35" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="BM35" s="2" t="n">
+        <v>99.29000000000001</v>
+      </c>
+      <c r="BN35" s="2" t="n">
+        <v>100.11</v>
+      </c>
+      <c r="BO35" s="2" t="n">
+        <v>101.26</v>
+      </c>
+      <c r="BP35" s="2" t="n">
+        <v>100.32</v>
+      </c>
+      <c r="BQ35" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR35" s="2" t="n">
+        <v>99.48</v>
+      </c>
+      <c r="BS35" s="2" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="BT35" s="2" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="BU35" s="2" t="n">
+        <v>90.58</v>
+      </c>
+      <c r="BV35" s="2" t="n">
+        <v>83.03</v>
+      </c>
+      <c r="BW35" s="2" t="n">
+        <v>98.29000000000001</v>
+      </c>
+      <c r="BX35" s="2" t="n">
+        <v>99.84999999999999</v>
+      </c>
+      <c r="BY35" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="BZ35" s="2" t="n">
+        <v>102.31</v>
+      </c>
+      <c r="CA35" s="2" t="n">
+        <v>101.27</v>
+      </c>
+      <c r="CB35" s="2" t="n">
+        <v>52.17</v>
+      </c>
+      <c r="CC35" s="2" t="n">
+        <v>102.21</v>
+      </c>
+      <c r="CD35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE35" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>99.62</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>102.17</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>101.68</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>97.89</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>100.98</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>48.66</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>103.04</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>96.69</v>
+      </c>
+      <c r="T36" s="2" t="n">
+        <v>102.88</v>
+      </c>
+      <c r="U36" s="2" t="n">
+        <v>97.29000000000001</v>
+      </c>
+      <c r="V36" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W36" s="2" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="X36" s="2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Y36" s="2" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="Z36" s="2" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AA36" s="2" t="n">
+        <v>98.20999999999999</v>
+      </c>
+      <c r="AB36" s="2" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="AC36" s="2" t="n">
+        <v>98.92</v>
+      </c>
+      <c r="AD36" s="2" t="n">
+        <v>95.88</v>
+      </c>
+      <c r="AE36" s="2" t="n">
+        <v>87.89</v>
+      </c>
+      <c r="AF36" s="2" t="n">
+        <v>86.13</v>
+      </c>
+      <c r="AG36" s="2" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="AH36" s="2" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="AI36" s="2" t="n">
+        <v>92.73</v>
+      </c>
+      <c r="AJ36" s="2" t="n">
+        <v>74.05</v>
+      </c>
+      <c r="AK36" s="2" t="n">
+        <v>92.31999999999999</v>
+      </c>
+      <c r="AL36" s="2" t="n">
+        <v>99.68000000000001</v>
+      </c>
+      <c r="AM36" s="2" t="n">
+        <v>92.98999999999999</v>
+      </c>
+      <c r="AN36" s="2" t="n">
+        <v>91.18000000000001</v>
+      </c>
+      <c r="AO36" s="2" t="n">
+        <v>103.28</v>
+      </c>
+      <c r="AP36" s="2" t="n">
+        <v>99.84999999999999</v>
+      </c>
+      <c r="AQ36" s="2" t="n">
+        <v>100.28</v>
+      </c>
+      <c r="AR36" s="2" t="n">
+        <v>99.03</v>
+      </c>
+      <c r="AS36" s="2" t="n">
+        <v>99.62</v>
+      </c>
+      <c r="AT36" s="2" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="AU36" s="2" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="AV36" s="2" t="n">
+        <v>100.93</v>
+      </c>
+      <c r="AW36" s="2" t="n">
+        <v>97.93000000000001</v>
+      </c>
+      <c r="AX36" s="2" t="n">
+        <v>101.67</v>
+      </c>
+      <c r="AY36" s="2" t="n">
+        <v>98.87</v>
+      </c>
+      <c r="AZ36" s="2" t="n">
+        <v>97.72</v>
+      </c>
+      <c r="BA36" s="2" t="n">
+        <v>96.08</v>
+      </c>
+      <c r="BB36" s="2" t="n">
+        <v>94.92</v>
+      </c>
+      <c r="BC36" s="2" t="n">
+        <v>99.31999999999999</v>
+      </c>
+      <c r="BD36" s="2" t="n">
+        <v>101.07</v>
+      </c>
+      <c r="BE36" s="2" t="n">
+        <v>96.36</v>
+      </c>
+      <c r="BF36" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG36" s="2" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="BH36" s="2" t="n">
+        <v>99.09</v>
+      </c>
+      <c r="BI36" s="2" t="n">
+        <v>94.39</v>
+      </c>
+      <c r="BJ36" s="2" t="n">
+        <v>93.61</v>
+      </c>
+      <c r="BK36" s="2" t="n">
+        <v>89.01000000000001</v>
+      </c>
+      <c r="BL36" s="2" t="n">
+        <v>98.34</v>
+      </c>
+      <c r="BM36" s="2" t="n">
+        <v>99.13</v>
+      </c>
+      <c r="BN36" s="2" t="n">
+        <v>100.51</v>
+      </c>
+      <c r="BO36" s="2" t="n">
+        <v>101.38</v>
+      </c>
+      <c r="BP36" s="2" t="n">
+        <v>100.68</v>
+      </c>
+      <c r="BQ36" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR36" s="2" t="n">
+        <v>100.28</v>
+      </c>
+      <c r="BS36" s="2" t="n">
+        <v>99.20999999999999</v>
+      </c>
+      <c r="BT36" s="2" t="n">
+        <v>92.62</v>
+      </c>
+      <c r="BU36" s="2" t="n">
+        <v>91.47</v>
+      </c>
+      <c r="BV36" s="2" t="n">
+        <v>85.53</v>
+      </c>
+      <c r="BW36" s="2" t="n">
+        <v>98.81</v>
+      </c>
+      <c r="BX36" s="2" t="n">
+        <v>99.77</v>
+      </c>
+      <c r="BY36" s="2" t="n">
+        <v>101.66</v>
+      </c>
+      <c r="BZ36" s="2" t="n">
+        <v>102.31</v>
+      </c>
+      <c r="CA36" s="2" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="CB36" s="2" t="n">
+        <v>50.04</v>
+      </c>
+      <c r="CC36" s="2" t="n">
+        <v>100.89</v>
+      </c>
+      <c r="CD36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE36" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>46.32</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>101.29</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>31.02</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>100.53</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>100.03</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>98.94</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="T37" s="2" t="n">
+        <v>97.84</v>
+      </c>
+      <c r="U37" s="2" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="V37" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="W37" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="X37" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="Y37" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="Z37" s="2" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AA37" s="2" t="n">
+        <v>100.69</v>
+      </c>
+      <c r="AB37" s="2" t="n">
+        <v>98.42</v>
+      </c>
+      <c r="AC37" s="2" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="AD37" s="2" t="n">
+        <v>106.52</v>
+      </c>
+      <c r="AE37" s="2" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="AF37" s="2" t="n">
+        <v>82.87</v>
+      </c>
+      <c r="AG37" s="2" t="n">
+        <v>78.05</v>
+      </c>
+      <c r="AH37" s="2" t="n">
+        <v>83.36</v>
+      </c>
+      <c r="AI37" s="2" t="n">
+        <v>88.98</v>
+      </c>
+      <c r="AJ37" s="2" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="AK37" s="2" t="n">
+        <v>73.78</v>
+      </c>
+      <c r="AL37" s="2" t="n">
+        <v>75.61</v>
+      </c>
+      <c r="AM37" s="2" t="n">
+        <v>108.41</v>
+      </c>
+      <c r="AN37" s="2" t="n">
+        <v>107.09</v>
+      </c>
+      <c r="AO37" s="2" t="n">
+        <v>99.14</v>
+      </c>
+      <c r="AP37" s="2" t="n">
+        <v>99.16</v>
+      </c>
+      <c r="AQ37" s="2" t="n">
+        <v>97.94</v>
+      </c>
+      <c r="AR37" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="AS37" s="2" t="n">
+        <v>99.27</v>
+      </c>
+      <c r="AT37" s="2" t="n">
+        <v>96.98999999999999</v>
+      </c>
+      <c r="AU37" s="2" t="n">
+        <v>99.53</v>
+      </c>
+      <c r="AV37" s="2" t="n">
+        <v>97.63</v>
+      </c>
+      <c r="AW37" s="2" t="n">
+        <v>95.67</v>
+      </c>
+      <c r="AX37" s="2" t="n">
+        <v>95.72</v>
+      </c>
+      <c r="AY37" s="2" t="n">
+        <v>94.70999999999999</v>
+      </c>
+      <c r="AZ37" s="2" t="n">
+        <v>94.61</v>
+      </c>
+      <c r="BA37" s="2" t="n">
+        <v>93.69</v>
+      </c>
+      <c r="BB37" s="2" t="n">
+        <v>93.70999999999999</v>
+      </c>
+      <c r="BC37" s="2" t="n">
+        <v>94.29000000000001</v>
+      </c>
+      <c r="BD37" s="2" t="n">
+        <v>96.66</v>
+      </c>
+      <c r="BE37" s="2" t="n">
+        <v>93.01000000000001</v>
+      </c>
+      <c r="BF37" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG37" s="2" t="n">
+        <v>99.16</v>
+      </c>
+      <c r="BH37" s="2" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="BI37" s="2" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="BJ37" s="2" t="n">
+        <v>97.47</v>
+      </c>
+      <c r="BK37" s="2" t="n">
+        <v>95.81</v>
+      </c>
+      <c r="BL37" s="2" t="n">
+        <v>100.47</v>
+      </c>
+      <c r="BM37" s="2" t="n">
+        <v>100.06</v>
+      </c>
+      <c r="BN37" s="2" t="n">
+        <v>99.78</v>
+      </c>
+      <c r="BO37" s="2" t="n">
+        <v>101.69</v>
+      </c>
+      <c r="BP37" s="2" t="n">
+        <v>100.58</v>
+      </c>
+      <c r="BQ37" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR37" s="2" t="n">
+        <v>100.08</v>
+      </c>
+      <c r="BS37" s="2" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="BT37" s="2" t="n">
+        <v>98.72</v>
+      </c>
+      <c r="BU37" s="2" t="n">
+        <v>97.05</v>
+      </c>
+      <c r="BV37" s="2" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="BW37" s="2" t="n">
+        <v>100.47</v>
+      </c>
+      <c r="BX37" s="2" t="n">
+        <v>100.79</v>
+      </c>
+      <c r="BY37" s="2" t="n">
+        <v>100.66</v>
+      </c>
+      <c r="BZ37" s="2" t="n">
+        <v>102.96</v>
+      </c>
+      <c r="CA37" s="2" t="n">
+        <v>100.38</v>
+      </c>
+      <c r="CB37" s="2" t="n">
+        <v>64.12</v>
+      </c>
+      <c r="CC37" s="2" t="n">
+        <v>100.82</v>
+      </c>
+      <c r="CD37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE37" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>94.93000000000001</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>99.45</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>77.83</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>101.97</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>26.93</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>101.23</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>106.66</v>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>72.51000000000001</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>93.69</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>95.84</v>
+      </c>
+      <c r="S38" s="2" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="T38" s="2" t="n">
+        <v>96.97</v>
+      </c>
+      <c r="U38" s="2" t="n">
+        <v>98.06999999999999</v>
+      </c>
+      <c r="V38" s="2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W38" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X38" s="2" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Y38" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z38" s="2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA38" s="2" t="n">
+        <v>105.01</v>
+      </c>
+      <c r="AB38" s="2" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="AC38" s="2" t="n">
+        <v>103.96</v>
+      </c>
+      <c r="AD38" s="2" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="AE38" s="2" t="n">
+        <v>128.94</v>
+      </c>
+      <c r="AF38" s="2" t="n">
+        <v>139.51</v>
+      </c>
+      <c r="AG38" s="2" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="AH38" s="2" t="n">
+        <v>98.64</v>
+      </c>
+      <c r="AI38" s="2" t="n">
+        <v>91.95999999999999</v>
+      </c>
+      <c r="AJ38" s="2" t="n">
+        <v>152.43</v>
+      </c>
+      <c r="AK38" s="2" t="n">
+        <v>148.39</v>
+      </c>
+      <c r="AL38" s="2" t="n">
+        <v>119.3</v>
+      </c>
+      <c r="AM38" s="2" t="n">
+        <v>94.42</v>
+      </c>
+      <c r="AN38" s="2" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="AO38" s="2" t="n">
+        <v>94.68000000000001</v>
+      </c>
+      <c r="AP38" s="2" t="n">
+        <v>96.61</v>
+      </c>
+      <c r="AQ38" s="2" t="n">
+        <v>97.03</v>
+      </c>
+      <c r="AR38" s="2" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="AS38" s="2" t="n">
+        <v>97.97</v>
+      </c>
+      <c r="AT38" s="2" t="n">
+        <v>97.61</v>
+      </c>
+      <c r="AU38" s="2" t="n">
+        <v>98.44</v>
+      </c>
+      <c r="AV38" s="2" t="n">
+        <v>97.66</v>
+      </c>
+      <c r="AW38" s="2" t="n">
+        <v>96.95</v>
+      </c>
+      <c r="AX38" s="2" t="n">
+        <v>96.88</v>
+      </c>
+      <c r="AY38" s="2" t="n">
+        <v>97.23999999999999</v>
+      </c>
+      <c r="AZ38" s="2" t="n">
+        <v>95.45</v>
+      </c>
+      <c r="BA38" s="2" t="n">
+        <v>97.61</v>
+      </c>
+      <c r="BB38" s="2" t="n">
+        <v>96.25</v>
+      </c>
+      <c r="BC38" s="2" t="n">
+        <v>94.05</v>
+      </c>
+      <c r="BD38" s="2" t="n">
+        <v>95.16</v>
+      </c>
+      <c r="BE38" s="2" t="n">
+        <v>91.22</v>
+      </c>
+      <c r="BF38" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG38" s="2" t="n">
+        <v>99.36</v>
+      </c>
+      <c r="BH38" s="2" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="BI38" s="2" t="n">
+        <v>100.37</v>
+      </c>
+      <c r="BJ38" s="2" t="n">
+        <v>99.33</v>
+      </c>
+      <c r="BK38" s="2" t="n">
+        <v>99.06</v>
+      </c>
+      <c r="BL38" s="2" t="n">
+        <v>100.53</v>
+      </c>
+      <c r="BM38" s="2" t="n">
+        <v>102.03</v>
+      </c>
+      <c r="BN38" s="2" t="n">
+        <v>100.48</v>
+      </c>
+      <c r="BO38" s="2" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="BP38" s="2" t="n">
+        <v>102.23</v>
+      </c>
+      <c r="BQ38" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR38" s="2" t="n">
+        <v>98.41</v>
+      </c>
+      <c r="BS38" s="2" t="n">
+        <v>99.27</v>
+      </c>
+      <c r="BT38" s="2" t="n">
+        <v>99.27</v>
+      </c>
+      <c r="BU38" s="2" t="n">
+        <v>98.68000000000001</v>
+      </c>
+      <c r="BV38" s="2" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="BW38" s="2" t="n">
+        <v>100.59</v>
+      </c>
+      <c r="BX38" s="2" t="n">
+        <v>101.89</v>
+      </c>
+      <c r="BY38" s="2" t="n">
+        <v>98.94</v>
+      </c>
+      <c r="BZ38" s="2" t="n">
+        <v>101.34</v>
+      </c>
+      <c r="CA38" s="2" t="n">
+        <v>101.12</v>
+      </c>
+      <c r="CB38" s="2" t="n">
+        <v>66.23</v>
+      </c>
+      <c r="CC38" s="2" t="n">
+        <v>101.59</v>
+      </c>
+      <c r="CD38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE38" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>96.84999999999999</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>101.92</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>101.02</v>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>102.36</v>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v>42.09</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>99.05</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>97.84999999999999</v>
+      </c>
+      <c r="S39" s="2" t="n">
+        <v>98.38</v>
+      </c>
+      <c r="T39" s="2" t="n">
+        <v>97.98999999999999</v>
+      </c>
+      <c r="U39" s="2" t="n">
+        <v>86.48999999999999</v>
+      </c>
+      <c r="V39" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="W39" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="X39" s="2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y39" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z39" s="2" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AA39" s="2" t="n">
+        <v>102.27</v>
+      </c>
+      <c r="AB39" s="2" t="n">
+        <v>96.77</v>
+      </c>
+      <c r="AC39" s="2" t="n">
+        <v>101.98</v>
+      </c>
+      <c r="AD39" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="AE39" s="2" t="n">
+        <v>73.72</v>
+      </c>
+      <c r="AF39" s="2" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="AG39" s="2" t="n">
+        <v>69.43000000000001</v>
+      </c>
+      <c r="AH39" s="2" t="n">
+        <v>78.18000000000001</v>
+      </c>
+      <c r="AI39" s="2" t="n">
+        <v>95.59</v>
+      </c>
+      <c r="AJ39" s="2" t="n">
+        <v>117.31</v>
+      </c>
+      <c r="AK39" s="2" t="n">
+        <v>90.44</v>
+      </c>
+      <c r="AL39" s="2" t="n">
+        <v>106.37</v>
+      </c>
+      <c r="AM39" s="2" t="n">
+        <v>98.87</v>
+      </c>
+      <c r="AN39" s="2" t="n">
+        <v>106.29</v>
+      </c>
+      <c r="AO39" s="2" t="n">
+        <v>98.28</v>
+      </c>
+      <c r="AP39" s="2" t="n">
+        <v>97.79000000000001</v>
+      </c>
+      <c r="AQ39" s="2" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="AR39" s="2" t="n">
+        <v>96.87</v>
+      </c>
+      <c r="AS39" s="2" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="AT39" s="2" t="n">
+        <v>94.66</v>
+      </c>
+      <c r="AU39" s="2" t="n">
+        <v>98.92</v>
+      </c>
+      <c r="AV39" s="2" t="n">
+        <v>97.19</v>
+      </c>
+      <c r="AW39" s="2" t="n">
+        <v>93.19</v>
+      </c>
+      <c r="AX39" s="2" t="n">
+        <v>95.47</v>
+      </c>
+      <c r="AY39" s="2" t="n">
+        <v>91.43000000000001</v>
+      </c>
+      <c r="AZ39" s="2" t="n">
+        <v>91.01000000000001</v>
+      </c>
+      <c r="BA39" s="2" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="BB39" s="2" t="n">
+        <v>89.18000000000001</v>
+      </c>
+      <c r="BC39" s="2" t="n">
+        <v>89.56999999999999</v>
+      </c>
+      <c r="BD39" s="2" t="n">
+        <v>92.47</v>
+      </c>
+      <c r="BE39" s="2" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="BF39" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG39" s="2" t="n">
+        <v>100.19</v>
+      </c>
+      <c r="BH39" s="2" t="n">
+        <v>100.27</v>
+      </c>
+      <c r="BI39" s="2" t="n">
+        <v>99.43000000000001</v>
+      </c>
+      <c r="BJ39" s="2" t="n">
+        <v>99.95999999999999</v>
+      </c>
+      <c r="BK39" s="2" t="n">
+        <v>97.69</v>
+      </c>
+      <c r="BL39" s="2" t="n">
+        <v>100.52</v>
+      </c>
+      <c r="BM39" s="2" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="BN39" s="2" t="n">
+        <v>102.36</v>
+      </c>
+      <c r="BO39" s="2" t="n">
+        <v>102.94</v>
+      </c>
+      <c r="BP39" s="2" t="n">
+        <v>104.08</v>
+      </c>
+      <c r="BQ39" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR39" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS39" s="2" t="n">
+        <v>100.47</v>
+      </c>
+      <c r="BT39" s="2" t="n">
+        <v>99.87</v>
+      </c>
+      <c r="BU39" s="2" t="n">
+        <v>101.81</v>
+      </c>
+      <c r="BV39" s="2" t="n">
+        <v>98.31</v>
+      </c>
+      <c r="BW39" s="2" t="n">
+        <v>101.01</v>
+      </c>
+      <c r="BX39" s="2" t="n">
+        <v>101.86</v>
+      </c>
+      <c r="BY39" s="2" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="BZ39" s="2" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="CA39" s="2" t="n">
+        <v>105.92</v>
+      </c>
+      <c r="CB39" s="2" t="n">
+        <v>70.09</v>
+      </c>
+      <c r="CC39" s="2" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="CD39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE39" s="2" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/results.xlsx
+++ b/data/results.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00;[RED]-#,##0.00"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -58,12 +56,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,92 +424,93 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE3"/>
+  <dimension ref="A1:CF8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="8" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="8" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="8" customWidth="1" min="27" max="27"/>
-    <col width="8" customWidth="1" min="28" max="28"/>
-    <col width="8" customWidth="1" min="29" max="29"/>
-    <col width="8" customWidth="1" min="30" max="30"/>
-    <col width="13" customWidth="1" min="31" max="31"/>
-    <col width="13" customWidth="1" min="32" max="32"/>
-    <col width="14" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="12" customWidth="1" min="36" max="36"/>
-    <col width="12" customWidth="1" min="37" max="37"/>
-    <col width="12" customWidth="1" min="38" max="38"/>
-    <col width="13" customWidth="1" min="39" max="39"/>
-    <col width="13" customWidth="1" min="40" max="40"/>
-    <col width="16" customWidth="1" min="41" max="41"/>
-    <col width="17" customWidth="1" min="42" max="42"/>
-    <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="16" customWidth="1" min="44" max="44"/>
-    <col width="17" customWidth="1" min="45" max="45"/>
-    <col width="17" customWidth="1" min="46" max="46"/>
-    <col width="17" customWidth="1" min="47" max="47"/>
-    <col width="18" customWidth="1" min="48" max="48"/>
-    <col width="18" customWidth="1" min="49" max="49"/>
-    <col width="17" customWidth="1" min="50" max="50"/>
-    <col width="18" customWidth="1" min="51" max="51"/>
-    <col width="18" customWidth="1" min="52" max="52"/>
-    <col width="17" customWidth="1" min="53" max="53"/>
-    <col width="18" customWidth="1" min="54" max="54"/>
-    <col width="18" customWidth="1" min="55" max="55"/>
-    <col width="16" customWidth="1" min="56" max="56"/>
-    <col width="17" customWidth="1" min="57" max="57"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="21" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="27" max="27"/>
+    <col width="20" customWidth="1" min="28" max="28"/>
+    <col width="20" customWidth="1" min="29" max="29"/>
+    <col width="20" customWidth="1" min="30" max="30"/>
+    <col width="20" customWidth="1" min="31" max="31"/>
+    <col width="20" customWidth="1" min="32" max="32"/>
+    <col width="20" customWidth="1" min="33" max="33"/>
+    <col width="20" customWidth="1" min="34" max="34"/>
+    <col width="20" customWidth="1" min="35" max="35"/>
+    <col width="20" customWidth="1" min="36" max="36"/>
+    <col width="20" customWidth="1" min="37" max="37"/>
+    <col width="20" customWidth="1" min="38" max="38"/>
+    <col width="20" customWidth="1" min="39" max="39"/>
+    <col width="20" customWidth="1" min="40" max="40"/>
+    <col width="20" customWidth="1" min="41" max="41"/>
+    <col width="20" customWidth="1" min="42" max="42"/>
+    <col width="20" customWidth="1" min="43" max="43"/>
+    <col width="20" customWidth="1" min="44" max="44"/>
+    <col width="20" customWidth="1" min="45" max="45"/>
+    <col width="20" customWidth="1" min="46" max="46"/>
+    <col width="20" customWidth="1" min="47" max="47"/>
+    <col width="20" customWidth="1" min="48" max="48"/>
+    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="20" customWidth="1" min="50" max="50"/>
+    <col width="20" customWidth="1" min="51" max="51"/>
+    <col width="20" customWidth="1" min="52" max="52"/>
+    <col width="20" customWidth="1" min="53" max="53"/>
+    <col width="20" customWidth="1" min="54" max="54"/>
+    <col width="20" customWidth="1" min="55" max="55"/>
+    <col width="20" customWidth="1" min="56" max="56"/>
+    <col width="20" customWidth="1" min="57" max="57"/>
     <col width="7" customWidth="1" min="58" max="58"/>
-    <col width="8" customWidth="1" min="59" max="59"/>
-    <col width="8" customWidth="1" min="60" max="60"/>
-    <col width="8" customWidth="1" min="61" max="61"/>
-    <col width="8" customWidth="1" min="62" max="62"/>
-    <col width="8" customWidth="1" min="63" max="63"/>
-    <col width="8" customWidth="1" min="64" max="64"/>
-    <col width="7" customWidth="1" min="65" max="65"/>
-    <col width="7" customWidth="1" min="66" max="66"/>
-    <col width="8" customWidth="1" min="67" max="67"/>
-    <col width="8" customWidth="1" min="68" max="68"/>
+    <col width="20" customWidth="1" min="59" max="59"/>
+    <col width="20" customWidth="1" min="60" max="60"/>
+    <col width="19" customWidth="1" min="61" max="61"/>
+    <col width="20" customWidth="1" min="62" max="62"/>
+    <col width="19" customWidth="1" min="63" max="63"/>
+    <col width="20" customWidth="1" min="64" max="64"/>
+    <col width="20" customWidth="1" min="65" max="65"/>
+    <col width="20" customWidth="1" min="66" max="66"/>
+    <col width="20" customWidth="1" min="67" max="67"/>
+    <col width="20" customWidth="1" min="68" max="68"/>
     <col width="7" customWidth="1" min="69" max="69"/>
-    <col width="8" customWidth="1" min="70" max="70"/>
-    <col width="8" customWidth="1" min="71" max="71"/>
-    <col width="8" customWidth="1" min="72" max="72"/>
-    <col width="8" customWidth="1" min="73" max="73"/>
-    <col width="8" customWidth="1" min="74" max="74"/>
-    <col width="8" customWidth="1" min="75" max="75"/>
-    <col width="8" customWidth="1" min="76" max="76"/>
-    <col width="7" customWidth="1" min="77" max="77"/>
-    <col width="8" customWidth="1" min="78" max="78"/>
-    <col width="7" customWidth="1" min="79" max="79"/>
-    <col width="10" customWidth="1" min="80" max="80"/>
-    <col width="15" customWidth="1" min="81" max="81"/>
+    <col width="20" customWidth="1" min="70" max="70"/>
+    <col width="20" customWidth="1" min="71" max="71"/>
+    <col width="19" customWidth="1" min="72" max="72"/>
+    <col width="20" customWidth="1" min="73" max="73"/>
+    <col width="19" customWidth="1" min="74" max="74"/>
+    <col width="20" customWidth="1" min="75" max="75"/>
+    <col width="20" customWidth="1" min="76" max="76"/>
+    <col width="20" customWidth="1" min="77" max="77"/>
+    <col width="20" customWidth="1" min="78" max="78"/>
+    <col width="20" customWidth="1" min="79" max="79"/>
+    <col width="20" customWidth="1" min="80" max="80"/>
+    <col width="20" customWidth="1" min="81" max="81"/>
     <col width="20" customWidth="1" min="82" max="82"/>
     <col width="20" customWidth="1" min="83" max="83"/>
+    <col width="9" customWidth="1" min="84" max="84"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -933,515 +929,1830 @@
           <t>Bullish Divergence</t>
         </is>
       </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>weekday</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NOKIA.HE</t>
+          <t>SFM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2" t="n">
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="E2" t="n">
+        <v>102.9367104059533</v>
+      </c>
+      <c r="F2" t="n">
+        <v>107.2506366198576</v>
+      </c>
+      <c r="G2" t="n">
+        <v>95.07026740477141</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J2" t="n">
+        <v>104.2835477032239</v>
+      </c>
+      <c r="K2" t="n">
+        <v>29.3143470379756</v>
+      </c>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>109.53</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>111.38</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>61.34</v>
-      </c>
-      <c r="H2" s="2" t="n">
+      <c r="M2" t="n">
+        <v>102.6531673383109</v>
+      </c>
+      <c r="N2" t="n">
+        <v>106.6025282461432</v>
+      </c>
+      <c r="O2" t="n">
+        <v>10.25626980711295</v>
+      </c>
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="Q2" t="n">
+        <v>107.2708863849881</v>
+      </c>
+      <c r="R2" t="n">
+        <v>110.1772182802611</v>
+      </c>
+      <c r="S2" t="n">
+        <v>120.8911364591574</v>
+      </c>
+      <c r="T2" t="n">
+        <v>127.1088573600672</v>
+      </c>
+      <c r="U2" t="n">
+        <v>137.7316400069225</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2.111391477947002</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.371778464970988</v>
+      </c>
+      <c r="X2" t="n">
+        <v>4.922886648550141</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>7.438075216717154</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>11.26466375241516</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>105.3670916979826</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>112.5367060794106</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>111.4329123195214</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>84.74936956091771</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>140.9602170000696</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>129.6683417294166</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>126.0502892676559</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>132.3877657764499</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>125.9874614335754</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>206.3037606352984</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>147.9907035575093</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>146.1468883606505</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>131.1642672664908</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>175.7027111508501</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>108.6886079039755</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>112.6683535032634</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>122.3640503702284</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>112.4516447043117</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>117.5412651738034</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>127.368607533129</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>122.6308856432951</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>128.3736711333069</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>135.1782272918315</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>134.1164566233188</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>137.1959498924545</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>141.9032905675188</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>140.2754431615902</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>141.982783450356</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>145.2182269518889</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>136.4540756032437</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>152.3357464754129</v>
+      </c>
+      <c r="BF2" t="n">
         <v>100</v>
       </c>
-      <c r="J2" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="L2" s="2" t="n">
+      <c r="BG2" t="n">
+        <v>100.0178744396967</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>99.61084915950865</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>99.14112517343587</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>98.39409285400554</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>96.99192377838604</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>100.3056034695902</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>98.95332720550806</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>100.3091812663073</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>102.625630113995</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>100.8483014191927</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>99.77974867194236</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>99.35491647480248</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>98.95306709330993</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>97.72151683752682</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>95.97254265108941</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>101.0384332749026</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>98.94964679744724</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>101.154982804954</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>104.7178303089793</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>102.3971949485297</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>7.10701119722178</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>104.1417684434335</v>
+      </c>
+      <c r="CD2" t="n">
         <v>0</v>
       </c>
-      <c r="M2" s="2" t="n">
-        <v>103.04</v>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>105.87</v>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>70.88</v>
-      </c>
-      <c r="P2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="2" t="n">
-        <v>109.6</v>
-      </c>
-      <c r="R2" s="2" t="n">
-        <v>112.47</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>112.62</v>
-      </c>
-      <c r="T2" s="2" t="n">
-        <v>109.11</v>
-      </c>
-      <c r="U2" s="2" t="n">
-        <v>106.61</v>
-      </c>
-      <c r="V2" s="2" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="W2" s="2" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="X2" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Y2" s="2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z2" s="2" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AA2" s="2" t="n">
-        <v>108.45</v>
-      </c>
-      <c r="AB2" s="2" t="n">
-        <v>111.14</v>
-      </c>
-      <c r="AC2" s="2" t="n">
-        <v>115.47</v>
-      </c>
-      <c r="AD2" s="2" t="n">
-        <v>116.98</v>
-      </c>
-      <c r="AE2" s="2" t="n">
-        <v>109.93</v>
-      </c>
-      <c r="AF2" s="2" t="n">
-        <v>92.18000000000001</v>
-      </c>
-      <c r="AG2" s="2" t="n">
-        <v>81.27</v>
-      </c>
-      <c r="AH2" s="2" t="n">
-        <v>84.15000000000001</v>
-      </c>
-      <c r="AI2" s="2" t="n">
-        <v>90.18000000000001</v>
-      </c>
-      <c r="AJ2" s="2" t="n">
-        <v>313.97</v>
-      </c>
-      <c r="AK2" s="2" t="n">
-        <v>149.95</v>
-      </c>
-      <c r="AL2" s="2" t="n">
-        <v>116.44</v>
-      </c>
-      <c r="AM2" s="2" t="n">
-        <v>107.99</v>
-      </c>
-      <c r="AN2" s="2" t="n">
-        <v>93.88</v>
-      </c>
-      <c r="AO2" s="2" t="n">
-        <v>112.49</v>
-      </c>
-      <c r="AP2" s="2" t="n">
-        <v>112.51</v>
-      </c>
-      <c r="AQ2" s="2" t="n">
-        <v>110.99</v>
-      </c>
-      <c r="AR2" s="2" t="n">
-        <v>112.68</v>
-      </c>
-      <c r="AS2" s="2" t="n">
-        <v>112.61</v>
-      </c>
-      <c r="AT2" s="2" t="n">
-        <v>110.16</v>
-      </c>
-      <c r="AU2" s="2" t="n">
-        <v>112.54</v>
-      </c>
-      <c r="AV2" s="2" t="n">
-        <v>110.56</v>
-      </c>
-      <c r="AW2" s="2" t="n">
-        <v>109.99</v>
-      </c>
-      <c r="AX2" s="2" t="n">
-        <v>108.59</v>
-      </c>
-      <c r="AY2" s="2" t="n">
-        <v>107.72</v>
-      </c>
-      <c r="AZ2" s="2" t="n">
-        <v>109.88</v>
-      </c>
-      <c r="BA2" s="2" t="n">
-        <v>106.85</v>
-      </c>
-      <c r="BB2" s="2" t="n">
-        <v>109.42</v>
-      </c>
-      <c r="BC2" s="2" t="n">
-        <v>110.38</v>
-      </c>
-      <c r="BD2" s="2" t="n">
-        <v>110.77</v>
-      </c>
-      <c r="BE2" s="2" t="n">
-        <v>108.46</v>
-      </c>
-      <c r="BF2" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="BG2" s="2" t="n">
-        <v>102.21</v>
-      </c>
-      <c r="BH2" s="2" t="n">
-        <v>100.72</v>
-      </c>
-      <c r="BI2" s="2" t="n">
-        <v>99.86</v>
-      </c>
-      <c r="BJ2" s="2" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="BK2" s="2" t="n">
-        <v>98.95999999999999</v>
-      </c>
-      <c r="BL2" s="2" t="n">
-        <v>100.36</v>
-      </c>
-      <c r="BM2" s="2" t="n">
-        <v>97.38</v>
-      </c>
-      <c r="BN2" s="2" t="n">
-        <v>98.23</v>
-      </c>
-      <c r="BO2" s="2" t="n">
-        <v>95.94</v>
-      </c>
-      <c r="BP2" s="2" t="n">
-        <v>99.98</v>
-      </c>
-      <c r="BQ2" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="BR2" s="2" t="n">
-        <v>103.52</v>
-      </c>
-      <c r="BS2" s="2" t="n">
-        <v>102.57</v>
-      </c>
-      <c r="BT2" s="2" t="n">
-        <v>102.44</v>
-      </c>
-      <c r="BU2" s="2" t="n">
-        <v>100.23</v>
-      </c>
-      <c r="BV2" s="2" t="n">
-        <v>101.03</v>
-      </c>
-      <c r="BW2" s="2" t="n">
-        <v>100.6</v>
-      </c>
-      <c r="BX2" s="2" t="n">
-        <v>95.56</v>
-      </c>
-      <c r="BY2" s="2" t="n">
-        <v>95.87</v>
-      </c>
-      <c r="BZ2" s="2" t="n">
-        <v>93.45</v>
-      </c>
-      <c r="CA2" s="2" t="n">
-        <v>98.91</v>
-      </c>
-      <c r="CB2" s="2" t="n">
-        <v>39.65</v>
-      </c>
-      <c r="CC2" s="2" t="n">
-        <v>105.84</v>
-      </c>
-      <c r="CD2" s="2" t="n">
+      <c r="CE2" t="n">
         <v>0</v>
       </c>
-      <c r="CE2" s="2" t="n">
-        <v>0</v>
+      <c r="CF2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NOKIA.HE</t>
+          <t>SFM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Piercing Pattern</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E3" t="n">
+        <v>101.9628926819132</v>
+      </c>
+      <c r="F3" t="n">
+        <v>104.0917917476327</v>
+      </c>
+      <c r="G3" t="n">
+        <v>39.44970182266147</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J3" t="n">
+        <v>103.7988274723466</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20.56563437739031</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>99.26757813591394</v>
+      </c>
+      <c r="N3" t="n">
+        <v>103.4277364100853</v>
+      </c>
+      <c r="O3" t="n">
+        <v>95.07026740477141</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>104.6484395168954</v>
+      </c>
+      <c r="R3" t="n">
+        <v>107.3046832188266</v>
+      </c>
+      <c r="S3" t="n">
+        <v>117.5878924490825</v>
+      </c>
+      <c r="T3" t="n">
+        <v>132.7929625989055</v>
+      </c>
+      <c r="U3" t="n">
+        <v>135.576171642897</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.9033232792716746</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.642634594693139</v>
+      </c>
+      <c r="X3" t="n">
+        <v>5.182260403457925</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>8.394641164995759</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>11.07531739755949</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>100.4296824272024</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>100.3320276687737</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>109.1601534312941</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>77.10937295691113</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>114.5775656125489</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>123.9268780741626</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>127.8387613777254</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>128.2480414514688</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>118.5676552996295</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>149.8330033023949</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>170.2005524498932</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>148.5212215628555</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>146.2610570791897</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>168.5670817861504</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>106.7675768320623</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>111.7695292566787</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>121.3061508341707</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>112.4902306126024</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>116.8818337189878</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>125.8037086456461</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>121.2734368253732</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>127.3525375522295</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>132.9291968356193</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>133.4316382790858</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>134.7255835723045</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>138.5957004339144</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>136.0195288655232</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>138.505856119009</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>141.1337868700357</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>133.8572245261487</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>147.2813939708263</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>99.93165593737589</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>98.92656197810402</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>99.23419023700703</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>98.0419280645296</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>96.51135551141789</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>99.98212875468829</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>97.56871086666233</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>99.2289771845707</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>101.1301708645189</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>101.8525021706511</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>100.0618903458153</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>98.86357063639572</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>99.35740894577904</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>97.20268087481145</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>95.42845944102001</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>100.2207375053447</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>97.72536824913362</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>100.1308412658412</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>102.310383787913</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>104.3275725036654</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>2.563052866730388</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>103.4472643815389</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SFM</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="E4" t="n">
+        <v>100.9643849069264</v>
+      </c>
+      <c r="F4" t="n">
+        <v>102.4025073930131</v>
+      </c>
+      <c r="G4" t="n">
+        <v>27.64705618360762</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J4" t="n">
+        <v>101.497338876719</v>
+      </c>
+      <c r="K4" t="n">
+        <v>28.24851938378779</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>97.77514823298613</v>
+      </c>
+      <c r="N4" t="n">
+        <v>101.4381224860867</v>
+      </c>
+      <c r="O4" t="n">
+        <v>79.44575027046457</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>101.8610985489177</v>
+      </c>
+      <c r="R4" t="n">
+        <v>106.1839079732756</v>
+      </c>
+      <c r="S4" t="n">
+        <v>115.0579439643202</v>
+      </c>
+      <c r="T4" t="n">
+        <v>117.2828021854366</v>
+      </c>
+      <c r="U4" t="n">
+        <v>122.9253013146168</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.3468434694905866</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.798809566283605</v>
+      </c>
+      <c r="X4" t="n">
+        <v>5.624250393803055</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>6.252945465636911</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>6.853142939175644</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>94.20522923003654</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>92.03959385365491</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>86.99771350509981</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>93.08857268232694</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>148.9968125765601</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>146.7517486705061</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>127.390830221901</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>112.2654519298585</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>103.3512069976236</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>121.9289269708131</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>121.8842778290222</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>127.4349540796709</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>136.1956409830796</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>134.4435561307999</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>105.05371975422</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>110.3197710910551</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>115.1505800205124</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>112.0379002971533</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>114.6104403756778</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>118.5428479153346</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>117.1829804542023</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>118.6092544988806</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>121.3120719276165</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>120.0355285435588</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>122.4752554549913</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>123.6976573092291</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>124.9149823664238</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>124.0148893563524</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>126.4453100973595</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>123.6015572716727</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>128.9389229884224</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>100.1117625192066</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>99.24649602460785</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>97.8321797424731</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>96.37400050405725</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>96.73121953981743</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>99.21585796969377</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>100.4737932772611</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>100.8663153913793</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>99.81057510937133</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>101.1781751425839</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>100.1874685092555</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>98.75541982481273</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>96.98794132433514</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>94.51158982560813</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>95.30287809016525</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>99.25606952441258</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>100.4061009863531</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>101.0580095568972</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>99.99654351708023</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>102.2252121903081</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>19.14063538036321</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>100.9897624380398</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SFM</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E5" t="n">
+        <v>100.858210337586</v>
+      </c>
+      <c r="F5" t="n">
+        <v>102.6919959800876</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7.60009765625</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J5" t="n">
+        <v>101.6724116105583</v>
+      </c>
+      <c r="K5" t="n">
+        <v>17.10524554617125</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>101.701747256121</v>
+      </c>
+      <c r="N5" t="n">
+        <v>103.4768616074971</v>
+      </c>
+      <c r="O5" t="n">
+        <v>44.21493335351013</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>103.0880887541506</v>
+      </c>
+      <c r="R5" t="n">
+        <v>105.8314361046471</v>
+      </c>
+      <c r="S5" t="n">
+        <v>108.0099743433421</v>
+      </c>
+      <c r="T5" t="n">
+        <v>108.4354139555072</v>
+      </c>
+      <c r="U5" t="n">
+        <v>109.4696717440875</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.6968363056427194</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.660009965424125</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.629421272998699</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.252660837951285</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.498697471945422</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>101.8337856425016</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>98.36426634079962</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>90.48631919129873</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>78.60339046639648</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>97.51903384547276</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>89.92091325015541</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>87.93039176656443</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>90.85147516087983</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>86.79554673816025</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>84.53797050504183</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>86.50921999639888</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>93.27754366895783</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>111.0110802942778</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>124.9023322965001</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>105.0597776736374</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>106.634633992212</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>107.8130253847911</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>107.8764742113261</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>107.2713249493006</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>109.1747947819934</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>106.6661756872751</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>108.1706141447059</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>111.7424617967853</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>109.6750526021367</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>111.0782646146862</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>115.6348553806398</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>112.4814766272357</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>115.3143094488648</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>117.826595219465</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>113.7222895950909</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>112.6731809017672</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>100.1860967212266</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>100.2741852286333</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>99.4279131148817</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>99.96122984974447</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>97.68821620658917</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>100.5154915524992</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>101.2992695158487</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>102.3586260101063</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>102.9420410485024</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>104.0776959868957</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>100.0024773952283</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>100.4717060611434</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>99.8715758352367</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>101.8123522425598</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>98.30757203756498</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>101.0147394172266</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>101.8553604910347</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>103.4544315262139</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>104.6497455289689</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>105.9194064127667</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>34.81796401948304</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>101.4743596272571</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF5" t="n">
         <v>3</v>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>98.79000000000001</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>103.45</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>44.38</v>
-      </c>
-      <c r="H3" s="2" t="n">
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SFM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="E6" t="n">
+        <v>102.3969559669065</v>
+      </c>
+      <c r="F6" t="n">
+        <v>105.3736876879702</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5.225692808420259</v>
+      </c>
+      <c r="H6" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I6" t="n">
         <v>100</v>
       </c>
-      <c r="J3" s="2" t="n">
-        <v>102.79</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>62.84</v>
-      </c>
-      <c r="L3" s="2" t="n">
+      <c r="J6" t="n">
+        <v>104.0302711604448</v>
+      </c>
+      <c r="K6" t="n">
+        <v>27.71900330874086</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="M3" s="2" t="n">
-        <v>101.8</v>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>103.99</v>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>22.81</v>
-      </c>
-      <c r="P3" s="2" t="n">
+      <c r="M6" t="n">
+        <v>101.2161502579203</v>
+      </c>
+      <c r="N6" t="n">
+        <v>105.4231873187729</v>
+      </c>
+      <c r="O6" t="n">
+        <v>62.52090065138226</v>
+      </c>
+      <c r="P6" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" s="2" t="n">
-        <v>103.09</v>
-      </c>
-      <c r="R3" s="2" t="n">
-        <v>107.76</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>107.77</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>111.94</v>
-      </c>
-      <c r="U3" s="2" t="n">
-        <v>112.85</v>
-      </c>
-      <c r="V3" s="2" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="W3" s="2" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="X3" s="2" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="Y3" s="2" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="Z3" s="2" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="AA3" s="2" t="n">
-        <v>102.22</v>
-      </c>
-      <c r="AB3" s="2" t="n">
-        <v>101.73</v>
-      </c>
-      <c r="AC3" s="2" t="n">
-        <v>107.53</v>
-      </c>
-      <c r="AD3" s="2" t="n">
-        <v>108.36</v>
-      </c>
-      <c r="AE3" s="2" t="n">
-        <v>146.07</v>
-      </c>
-      <c r="AF3" s="2" t="n">
-        <v>133.89</v>
-      </c>
-      <c r="AG3" s="2" t="n">
-        <v>107.67</v>
-      </c>
-      <c r="AH3" s="2" t="n">
-        <v>99.19</v>
-      </c>
-      <c r="AI3" s="2" t="n">
-        <v>103.96</v>
-      </c>
-      <c r="AJ3" s="2" t="n">
-        <v>89.31999999999999</v>
-      </c>
-      <c r="AK3" s="2" t="n">
-        <v>129.93</v>
-      </c>
-      <c r="AL3" s="2" t="n">
-        <v>93.70999999999999</v>
-      </c>
-      <c r="AM3" s="2" t="n">
-        <v>91.48</v>
-      </c>
-      <c r="AN3" s="2" t="n">
-        <v>98.88</v>
-      </c>
-      <c r="AO3" s="2" t="n">
-        <v>105.66</v>
-      </c>
-      <c r="AP3" s="2" t="n">
-        <v>106.89</v>
-      </c>
-      <c r="AQ3" s="2" t="n">
-        <v>109.46</v>
-      </c>
-      <c r="AR3" s="2" t="n">
-        <v>108.06</v>
-      </c>
-      <c r="AS3" s="2" t="n">
-        <v>108.65</v>
-      </c>
-      <c r="AT3" s="2" t="n">
-        <v>110.55</v>
-      </c>
-      <c r="AU3" s="2" t="n">
-        <v>109.23</v>
-      </c>
-      <c r="AV3" s="2" t="n">
-        <v>111.14</v>
-      </c>
-      <c r="AW3" s="2" t="n">
-        <v>109.32</v>
-      </c>
-      <c r="AX3" s="2" t="n">
-        <v>113.05</v>
-      </c>
-      <c r="AY3" s="2" t="n">
-        <v>112.46</v>
-      </c>
-      <c r="AZ3" s="2" t="n">
-        <v>107.49</v>
-      </c>
-      <c r="BA3" s="2" t="n">
-        <v>111.87</v>
-      </c>
-      <c r="BB3" s="2" t="n">
-        <v>107.5</v>
-      </c>
-      <c r="BC3" s="2" t="n">
-        <v>104.28</v>
-      </c>
-      <c r="BD3" s="2" t="n">
-        <v>104.65</v>
-      </c>
-      <c r="BE3" s="2" t="n">
-        <v>87.66</v>
-      </c>
-      <c r="BF3" s="2" t="n">
+      <c r="Q6" t="n">
+        <v>105.1686439906283</v>
+      </c>
+      <c r="R6" t="n">
+        <v>106.5898379458905</v>
+      </c>
+      <c r="S6" t="n">
+        <v>111.7584711475844</v>
+      </c>
+      <c r="T6" t="n">
+        <v>115.491766101082</v>
+      </c>
+      <c r="U6" t="n">
+        <v>118.2705316657381</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.3217152334142881</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.9159765755472358</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.098484276469901</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.799397856748029</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.969716504903118</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>102.9767425099981</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>106.8090259361666</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>102.2343235704986</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>97.3768000797518</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>75.50277444531552</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>74.4307490702294</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>103.7616906685783</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>89.11467798230821</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>81.97338867493845</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>165.4628885546425</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>80.71560012416946</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>83.8067430123313</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>80.55902440780828</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>87.43608082798548</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>105.9195430325278</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>107.7168974995134</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>112.0596820112645</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>107.3916478112057</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>110.2658619991723</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>113.2595684900973</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>113.1400761871388</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>115.206115038523</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>114.8713198405482</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>117.2721538899071</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>116.2532749810223</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>115.3613149380564</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>115.2343960721374</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>114.5365246425734</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>115.3436388874623</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>113.7112410770118</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>107.9836721076701</v>
+      </c>
+      <c r="BF6" t="n">
         <v>100</v>
       </c>
-      <c r="BG3" s="2" t="n">
-        <v>99.13</v>
-      </c>
-      <c r="BH3" s="2" t="n">
-        <v>98.34999999999999</v>
-      </c>
-      <c r="BI3" s="2" t="n">
-        <v>100.44</v>
-      </c>
-      <c r="BJ3" s="2" t="n">
-        <v>95.97</v>
-      </c>
-      <c r="BK3" s="2" t="n">
-        <v>97.3</v>
-      </c>
-      <c r="BL3" s="2" t="n">
-        <v>100.88</v>
-      </c>
-      <c r="BM3" s="2" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="BN3" s="2" t="n">
-        <v>101.4</v>
-      </c>
-      <c r="BO3" s="2" t="n">
-        <v>101.75</v>
-      </c>
-      <c r="BP3" s="2" t="n">
-        <v>100.08</v>
-      </c>
-      <c r="BQ3" s="2" t="n">
+      <c r="BG6" t="n">
+        <v>98.55982788912586</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>98.12079927777705</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>98.39667684419501</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>98.33497891351838</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>96.86264021536209</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>99.74050776090651</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>98.90513544851549</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>100.2291756081222</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>100.5489764229486</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>101.8694601359333</v>
+      </c>
+      <c r="BQ6" t="n">
         <v>100</v>
       </c>
-      <c r="BR3" s="2" t="n">
-        <v>99.47</v>
-      </c>
-      <c r="BS3" s="2" t="n">
-        <v>98.16</v>
-      </c>
-      <c r="BT3" s="2" t="n">
-        <v>101.64</v>
-      </c>
-      <c r="BU3" s="2" t="n">
-        <v>96.42</v>
-      </c>
-      <c r="BV3" s="2" t="n">
-        <v>97.95999999999999</v>
-      </c>
-      <c r="BW3" s="2" t="n">
-        <v>100.71</v>
-      </c>
-      <c r="BX3" s="2" t="n">
-        <v>101.87</v>
-      </c>
-      <c r="BY3" s="2" t="n">
-        <v>103.2</v>
-      </c>
-      <c r="BZ3" s="2" t="n">
-        <v>106.36</v>
-      </c>
-      <c r="CA3" s="2" t="n">
-        <v>103.5</v>
-      </c>
-      <c r="CB3" s="2" t="n">
-        <v>28.77</v>
-      </c>
-      <c r="CC3" s="2" t="n">
-        <v>102.53</v>
-      </c>
-      <c r="CD3" s="2" t="n">
+      <c r="BR6" t="n">
+        <v>98.64812916662981</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>97.76091607464529</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>97.88826331773718</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>97.12093680399204</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>96.0540617300815</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>99.4256844074889</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>97.48640291783245</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>98.81257499565136</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>99.09418028831743</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>100.6017914767923</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>19.26448890751337</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>103.3585521077478</v>
+      </c>
+      <c r="CD6" t="n">
         <v>0</v>
       </c>
-      <c r="CE3" s="2" t="n">
+      <c r="CE6" t="n">
         <v>0</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SFM</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2024-12-24</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bullish Engulfing</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E7" t="n">
+        <v>99.06990812440016</v>
+      </c>
+      <c r="F7" t="n">
+        <v>101.658657044476</v>
+      </c>
+      <c r="G7" t="n">
+        <v>50.59881538942987</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>100</v>
+      </c>
+      <c r="J7" t="n">
+        <v>102.0151842804438</v>
+      </c>
+      <c r="K7" t="n">
+        <v>83.46176192683971</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>100.4262928488177</v>
+      </c>
+      <c r="N7" t="n">
+        <v>101.8989279701684</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.157776385743426</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>102.0771915881523</v>
+      </c>
+      <c r="R7" t="n">
+        <v>107.4252065678311</v>
+      </c>
+      <c r="S7" t="n">
+        <v>113.8738128226098</v>
+      </c>
+      <c r="T7" t="n">
+        <v>117.1291196038534</v>
+      </c>
+      <c r="U7" t="n">
+        <v>114.6953889530486</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.8913358299464704</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.437900505064959</v>
+      </c>
+      <c r="X7" t="n">
+        <v>5.579978534676422</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>5.993143621471189</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5.889048044184127</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>99.59695841323737</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>103.0537919012046</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>106.9446528897617</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>116.3772972595798</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>167.2636685053807</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>138.5302149980272</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>111.7339873275722</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>105.5272312782544</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>108.178280479974</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>44.76353311619487</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>65.81461739016069</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>88.26446536744625</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>101.0227685928035</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>95.12676296061335</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>105.8905570427612</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>110.0945555265802</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>113.7091108639334</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>112.808862444422</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>114.3745120753407</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>114.8910981135847</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>115.9401617062594</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>117.015187237115</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>114.4663581084637</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>118.0902127679705</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>115.4076841518286</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>112.9677521789188</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>112.7251555356867</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>111.9175289798124</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>107.8197134276038</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>106.3571497926487</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>75.60618251767646</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>98.19223149680978</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>100.1749959296692</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>99.91506872836399</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>100.1629102404349</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>99.12798720646933</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>98.85430899687809</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>97.16077653018974</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>96.47353331066559</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>99.2817947806314</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>99.54039619395373</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>97.66717976071997</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>100.9332642915839</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>98.02973854783123</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>97.39270027759765</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>95.44556524288518</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>98.51070710119004</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>96.22880798953656</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>95.64140953050327</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>98.36454742604587</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>96.92457176926591</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>19.66198984029427</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>101.8679184029718</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SFM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="E8" t="n">
+        <v>102.3552849063574</v>
+      </c>
+      <c r="F8" t="n">
+        <v>104.3379934398376</v>
+      </c>
+      <c r="G8" t="n">
+        <v>65.10051306208973</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>100</v>
+      </c>
+      <c r="J8" t="n">
+        <v>102.0492360402641</v>
+      </c>
+      <c r="K8" t="n">
+        <v>26.62359859500324</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>99.93346234099464</v>
+      </c>
+      <c r="N8" t="n">
+        <v>101.4637371281254</v>
+      </c>
+      <c r="O8" t="n">
+        <v>31.30435936390837</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>104.0851625182829</v>
+      </c>
+      <c r="R8" t="n">
+        <v>104.9234821997549</v>
+      </c>
+      <c r="S8" t="n">
+        <v>110.1530234178245</v>
+      </c>
+      <c r="T8" t="n">
+        <v>104.5508956746562</v>
+      </c>
+      <c r="U8" t="n">
+        <v>100.7717921746881</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.7917514419453866</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.8621026222172783</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.849593717953805</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.636224523355996</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.064929698256723</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>100.10645619352</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>103.4597450716295</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>110.1131048833099</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>107.0392558990244</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>60.0874213650728</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>84.64071591009777</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>91.96373194719277</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>97.14108508815971</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>89.29715880563514</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>98.20136448211701</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>143.0269647656458</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>108.9887474526714</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>105.3220709412564</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>93.73726335686227</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>104.628074892125</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>105.6207570694232</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>104.2222195375237</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>105.1124414356419</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>105.8163660103222</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>103.4983341727528</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>106.5202905850025</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>104.5735158391405</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>100.0745147669644</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>102.6267410932785</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>101.1803023351835</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>95.35994396379881</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>99.73386357708851</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>95.5755136947883</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>90.67997142352723</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>94.91443555527221</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>71.68882093725105</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>99.85393798175373</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>98.55636695048993</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>98.95407535437528</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>98.9270234590029</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>97.42370318041027</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>101.1237102302982</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>102.0974509463518</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>102.024137577378</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>102.7648858747025</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>105.0947736284644</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>99.71962571845782</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>97.51660594552801</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>98.6038012002788</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>97.2296272738173</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>95.21097749991783</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>102.0472687979631</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>104.3412550860204</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>103.284255717482</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>104.913430780001</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>108.3918146109794</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>38.23075618406079</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>101.3040528378454</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/results.xlsx
+++ b/data/results.xlsx
@@ -424,90 +424,90 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF8"/>
+  <dimension ref="A1:CF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-    <col width="21" customWidth="1" min="22" max="22"/>
-    <col width="20" customWidth="1" min="23" max="23"/>
-    <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="20" customWidth="1" min="25" max="25"/>
-    <col width="20" customWidth="1" min="26" max="26"/>
-    <col width="20" customWidth="1" min="27" max="27"/>
-    <col width="20" customWidth="1" min="28" max="28"/>
-    <col width="20" customWidth="1" min="29" max="29"/>
-    <col width="20" customWidth="1" min="30" max="30"/>
-    <col width="20" customWidth="1" min="31" max="31"/>
-    <col width="20" customWidth="1" min="32" max="32"/>
-    <col width="20" customWidth="1" min="33" max="33"/>
-    <col width="20" customWidth="1" min="34" max="34"/>
-    <col width="20" customWidth="1" min="35" max="35"/>
-    <col width="20" customWidth="1" min="36" max="36"/>
-    <col width="20" customWidth="1" min="37" max="37"/>
-    <col width="20" customWidth="1" min="38" max="38"/>
-    <col width="20" customWidth="1" min="39" max="39"/>
-    <col width="20" customWidth="1" min="40" max="40"/>
-    <col width="20" customWidth="1" min="41" max="41"/>
-    <col width="20" customWidth="1" min="42" max="42"/>
-    <col width="20" customWidth="1" min="43" max="43"/>
-    <col width="20" customWidth="1" min="44" max="44"/>
-    <col width="20" customWidth="1" min="45" max="45"/>
-    <col width="20" customWidth="1" min="46" max="46"/>
-    <col width="20" customWidth="1" min="47" max="47"/>
-    <col width="20" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
-    <col width="20" customWidth="1" min="50" max="50"/>
-    <col width="20" customWidth="1" min="51" max="51"/>
-    <col width="20" customWidth="1" min="52" max="52"/>
-    <col width="20" customWidth="1" min="53" max="53"/>
-    <col width="20" customWidth="1" min="54" max="54"/>
-    <col width="20" customWidth="1" min="55" max="55"/>
-    <col width="20" customWidth="1" min="56" max="56"/>
-    <col width="20" customWidth="1" min="57" max="57"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
+    <col width="13" customWidth="1" min="32" max="32"/>
+    <col width="14" customWidth="1" min="33" max="33"/>
+    <col width="14" customWidth="1" min="34" max="34"/>
+    <col width="14" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="12" customWidth="1" min="37" max="37"/>
+    <col width="12" customWidth="1" min="38" max="38"/>
+    <col width="13" customWidth="1" min="39" max="39"/>
+    <col width="13" customWidth="1" min="40" max="40"/>
+    <col width="16" customWidth="1" min="41" max="41"/>
+    <col width="17" customWidth="1" min="42" max="42"/>
+    <col width="17" customWidth="1" min="43" max="43"/>
+    <col width="16" customWidth="1" min="44" max="44"/>
+    <col width="17" customWidth="1" min="45" max="45"/>
+    <col width="17" customWidth="1" min="46" max="46"/>
+    <col width="17" customWidth="1" min="47" max="47"/>
+    <col width="18" customWidth="1" min="48" max="48"/>
+    <col width="18" customWidth="1" min="49" max="49"/>
+    <col width="17" customWidth="1" min="50" max="50"/>
+    <col width="18" customWidth="1" min="51" max="51"/>
+    <col width="18" customWidth="1" min="52" max="52"/>
+    <col width="17" customWidth="1" min="53" max="53"/>
+    <col width="18" customWidth="1" min="54" max="54"/>
+    <col width="18" customWidth="1" min="55" max="55"/>
+    <col width="16" customWidth="1" min="56" max="56"/>
+    <col width="17" customWidth="1" min="57" max="57"/>
     <col width="7" customWidth="1" min="58" max="58"/>
-    <col width="20" customWidth="1" min="59" max="59"/>
-    <col width="20" customWidth="1" min="60" max="60"/>
-    <col width="19" customWidth="1" min="61" max="61"/>
-    <col width="20" customWidth="1" min="62" max="62"/>
-    <col width="19" customWidth="1" min="63" max="63"/>
-    <col width="20" customWidth="1" min="64" max="64"/>
-    <col width="20" customWidth="1" min="65" max="65"/>
-    <col width="20" customWidth="1" min="66" max="66"/>
-    <col width="20" customWidth="1" min="67" max="67"/>
-    <col width="20" customWidth="1" min="68" max="68"/>
+    <col width="8" customWidth="1" min="59" max="59"/>
+    <col width="8" customWidth="1" min="60" max="60"/>
+    <col width="8" customWidth="1" min="61" max="61"/>
+    <col width="8" customWidth="1" min="62" max="62"/>
+    <col width="8" customWidth="1" min="63" max="63"/>
+    <col width="8" customWidth="1" min="64" max="64"/>
+    <col width="8" customWidth="1" min="65" max="65"/>
+    <col width="8" customWidth="1" min="66" max="66"/>
+    <col width="8" customWidth="1" min="67" max="67"/>
+    <col width="8" customWidth="1" min="68" max="68"/>
     <col width="7" customWidth="1" min="69" max="69"/>
-    <col width="20" customWidth="1" min="70" max="70"/>
-    <col width="20" customWidth="1" min="71" max="71"/>
-    <col width="19" customWidth="1" min="72" max="72"/>
-    <col width="20" customWidth="1" min="73" max="73"/>
-    <col width="19" customWidth="1" min="74" max="74"/>
-    <col width="20" customWidth="1" min="75" max="75"/>
-    <col width="20" customWidth="1" min="76" max="76"/>
-    <col width="20" customWidth="1" min="77" max="77"/>
-    <col width="20" customWidth="1" min="78" max="78"/>
-    <col width="20" customWidth="1" min="79" max="79"/>
-    <col width="20" customWidth="1" min="80" max="80"/>
-    <col width="20" customWidth="1" min="81" max="81"/>
+    <col width="8" customWidth="1" min="70" max="70"/>
+    <col width="8" customWidth="1" min="71" max="71"/>
+    <col width="8" customWidth="1" min="72" max="72"/>
+    <col width="8" customWidth="1" min="73" max="73"/>
+    <col width="8" customWidth="1" min="74" max="74"/>
+    <col width="8" customWidth="1" min="75" max="75"/>
+    <col width="8" customWidth="1" min="76" max="76"/>
+    <col width="8" customWidth="1" min="77" max="77"/>
+    <col width="8" customWidth="1" min="78" max="78"/>
+    <col width="8" customWidth="1" min="79" max="79"/>
+    <col width="10" customWidth="1" min="80" max="80"/>
+    <col width="15" customWidth="1" min="81" max="81"/>
     <col width="20" customWidth="1" min="82" max="82"/>
     <col width="20" customWidth="1" min="83" max="83"/>
     <col width="9" customWidth="1" min="84" max="84"/>
@@ -946,22 +946,20 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Hammer</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.843</v>
+        <v>0.84</v>
       </c>
       <c r="E2" t="n">
-        <v>102.9367104059533</v>
+        <v>102.94</v>
       </c>
       <c r="F2" t="n">
-        <v>107.2506366198576</v>
+        <v>107.25</v>
       </c>
       <c r="G2" t="n">
-        <v>95.07026740477141</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -970,220 +968,220 @@
         <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>104.2835477032239</v>
+        <v>104.28</v>
       </c>
       <c r="K2" t="n">
-        <v>29.3143470379756</v>
+        <v>29.31</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>102.6531673383109</v>
+        <v>102.65</v>
       </c>
       <c r="N2" t="n">
-        <v>106.6025282461432</v>
+        <v>106.6</v>
       </c>
       <c r="O2" t="n">
-        <v>10.25626980711295</v>
+        <v>10.26</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>107.2708863849881</v>
+        <v>107.27</v>
       </c>
       <c r="R2" t="n">
-        <v>110.1772182802611</v>
+        <v>110.18</v>
       </c>
       <c r="S2" t="n">
-        <v>120.8911364591574</v>
+        <v>120.89</v>
       </c>
       <c r="T2" t="n">
-        <v>127.1088573600672</v>
+        <v>127.11</v>
       </c>
       <c r="U2" t="n">
-        <v>137.7316400069225</v>
+        <v>137.73</v>
       </c>
       <c r="V2" t="n">
-        <v>2.111391477947002</v>
+        <v>2.11</v>
       </c>
       <c r="W2" t="n">
-        <v>2.371778464970988</v>
+        <v>2.37</v>
       </c>
       <c r="X2" t="n">
-        <v>4.922886648550141</v>
+        <v>4.92</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.438075216717154</v>
+        <v>7.44</v>
       </c>
       <c r="Z2" t="n">
-        <v>11.26466375241516</v>
+        <v>11.26</v>
       </c>
       <c r="AA2" t="n">
-        <v>105.3670916979826</v>
+        <v>105.37</v>
       </c>
       <c r="AB2" t="n">
-        <v>112.5367060794106</v>
+        <v>112.54</v>
       </c>
       <c r="AC2" t="n">
-        <v>111.4329123195214</v>
+        <v>111.43</v>
       </c>
       <c r="AD2" t="n">
-        <v>84.74936956091771</v>
+        <v>84.75</v>
       </c>
       <c r="AE2" t="n">
-        <v>140.9602170000696</v>
+        <v>140.96</v>
       </c>
       <c r="AF2" t="n">
-        <v>129.6683417294166</v>
+        <v>129.67</v>
       </c>
       <c r="AG2" t="n">
-        <v>126.0502892676559</v>
+        <v>126.05</v>
       </c>
       <c r="AH2" t="n">
-        <v>132.3877657764499</v>
+        <v>132.39</v>
       </c>
       <c r="AI2" t="n">
-        <v>125.9874614335754</v>
+        <v>125.99</v>
       </c>
       <c r="AJ2" t="n">
-        <v>206.3037606352984</v>
+        <v>206.3</v>
       </c>
       <c r="AK2" t="n">
-        <v>147.9907035575093</v>
+        <v>147.99</v>
       </c>
       <c r="AL2" t="n">
-        <v>146.1468883606505</v>
+        <v>146.15</v>
       </c>
       <c r="AM2" t="n">
-        <v>131.1642672664908</v>
+        <v>131.16</v>
       </c>
       <c r="AN2" t="n">
-        <v>175.7027111508501</v>
+        <v>175.7</v>
       </c>
       <c r="AO2" t="n">
-        <v>108.6886079039755</v>
+        <v>108.69</v>
       </c>
       <c r="AP2" t="n">
-        <v>112.6683535032634</v>
+        <v>112.67</v>
       </c>
       <c r="AQ2" t="n">
-        <v>122.3640503702284</v>
+        <v>122.36</v>
       </c>
       <c r="AR2" t="n">
-        <v>112.4516447043117</v>
+        <v>112.45</v>
       </c>
       <c r="AS2" t="n">
-        <v>117.5412651738034</v>
+        <v>117.54</v>
       </c>
       <c r="AT2" t="n">
-        <v>127.368607533129</v>
+        <v>127.37</v>
       </c>
       <c r="AU2" t="n">
-        <v>122.6308856432951</v>
+        <v>122.63</v>
       </c>
       <c r="AV2" t="n">
-        <v>128.3736711333069</v>
+        <v>128.37</v>
       </c>
       <c r="AW2" t="n">
-        <v>135.1782272918315</v>
+        <v>135.18</v>
       </c>
       <c r="AX2" t="n">
-        <v>134.1164566233188</v>
+        <v>134.12</v>
       </c>
       <c r="AY2" t="n">
-        <v>137.1959498924545</v>
+        <v>137.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>141.9032905675188</v>
+        <v>141.9</v>
       </c>
       <c r="BA2" t="n">
-        <v>140.2754431615902</v>
+        <v>140.28</v>
       </c>
       <c r="BB2" t="n">
-        <v>141.982783450356</v>
+        <v>141.98</v>
       </c>
       <c r="BC2" t="n">
-        <v>145.2182269518889</v>
+        <v>145.22</v>
       </c>
       <c r="BD2" t="n">
-        <v>136.4540756032437</v>
+        <v>136.45</v>
       </c>
       <c r="BE2" t="n">
-        <v>152.3357464754129</v>
+        <v>152.34</v>
       </c>
       <c r="BF2" t="n">
         <v>100</v>
       </c>
       <c r="BG2" t="n">
-        <v>100.0178744396967</v>
+        <v>100.02</v>
       </c>
       <c r="BH2" t="n">
-        <v>99.61084915950865</v>
+        <v>99.61</v>
       </c>
       <c r="BI2" t="n">
-        <v>99.14112517343587</v>
+        <v>99.14</v>
       </c>
       <c r="BJ2" t="n">
-        <v>98.39409285400554</v>
+        <v>98.39</v>
       </c>
       <c r="BK2" t="n">
-        <v>96.99192377838604</v>
+        <v>96.98999999999999</v>
       </c>
       <c r="BL2" t="n">
-        <v>100.3056034695902</v>
+        <v>100.31</v>
       </c>
       <c r="BM2" t="n">
-        <v>98.95332720550806</v>
+        <v>98.95</v>
       </c>
       <c r="BN2" t="n">
-        <v>100.3091812663073</v>
+        <v>100.31</v>
       </c>
       <c r="BO2" t="n">
-        <v>102.625630113995</v>
+        <v>102.63</v>
       </c>
       <c r="BP2" t="n">
-        <v>100.8483014191927</v>
+        <v>100.85</v>
       </c>
       <c r="BQ2" t="n">
         <v>100</v>
       </c>
       <c r="BR2" t="n">
-        <v>99.77974867194236</v>
+        <v>99.78</v>
       </c>
       <c r="BS2" t="n">
-        <v>99.35491647480248</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>98.95306709330993</v>
+        <v>98.95</v>
       </c>
       <c r="BU2" t="n">
-        <v>97.72151683752682</v>
+        <v>97.72</v>
       </c>
       <c r="BV2" t="n">
-        <v>95.97254265108941</v>
+        <v>95.97</v>
       </c>
       <c r="BW2" t="n">
-        <v>101.0384332749026</v>
+        <v>101.04</v>
       </c>
       <c r="BX2" t="n">
-        <v>98.94964679744724</v>
+        <v>98.95</v>
       </c>
       <c r="BY2" t="n">
-        <v>101.154982804954</v>
+        <v>101.15</v>
       </c>
       <c r="BZ2" t="n">
-        <v>104.7178303089793</v>
+        <v>104.72</v>
       </c>
       <c r="CA2" t="n">
-        <v>102.3971949485297</v>
+        <v>102.4</v>
       </c>
       <c r="CB2" t="n">
-        <v>7.10701119722178</v>
+        <v>7.11</v>
       </c>
       <c r="CC2" t="n">
-        <v>104.1417684434335</v>
+        <v>104.14</v>
       </c>
       <c r="CD2" t="n">
         <v>0</v>
@@ -1206,22 +1204,20 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Piercing Pattern</t>
-        </is>
+      <c r="C3" t="n">
+        <v>3</v>
       </c>
       <c r="D3" t="n">
         <v>0.55</v>
       </c>
       <c r="E3" t="n">
-        <v>101.9628926819132</v>
+        <v>101.96</v>
       </c>
       <c r="F3" t="n">
-        <v>104.0917917476327</v>
+        <v>104.09</v>
       </c>
       <c r="G3" t="n">
-        <v>39.44970182266147</v>
+        <v>39.45</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -1230,220 +1226,220 @@
         <v>100</v>
       </c>
       <c r="J3" t="n">
-        <v>103.7988274723466</v>
+        <v>103.8</v>
       </c>
       <c r="K3" t="n">
-        <v>20.56563437739031</v>
+        <v>20.57</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>99.26757813591394</v>
+        <v>99.27</v>
       </c>
       <c r="N3" t="n">
-        <v>103.4277364100853</v>
+        <v>103.43</v>
       </c>
       <c r="O3" t="n">
-        <v>95.07026740477141</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>104.6484395168954</v>
+        <v>104.65</v>
       </c>
       <c r="R3" t="n">
-        <v>107.3046832188266</v>
+        <v>107.3</v>
       </c>
       <c r="S3" t="n">
-        <v>117.5878924490825</v>
+        <v>117.59</v>
       </c>
       <c r="T3" t="n">
-        <v>132.7929625989055</v>
+        <v>132.79</v>
       </c>
       <c r="U3" t="n">
-        <v>135.576171642897</v>
+        <v>135.58</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9033232792716746</v>
+        <v>0.9</v>
       </c>
       <c r="W3" t="n">
-        <v>1.642634594693139</v>
+        <v>1.64</v>
       </c>
       <c r="X3" t="n">
-        <v>5.182260403457925</v>
+        <v>5.18</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.394641164995759</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.07531739755949</v>
+        <v>11.08</v>
       </c>
       <c r="AA3" t="n">
-        <v>100.4296824272024</v>
+        <v>100.43</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.3320276687737</v>
+        <v>100.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>109.1601534312941</v>
+        <v>109.16</v>
       </c>
       <c r="AD3" t="n">
-        <v>77.10937295691113</v>
+        <v>77.11</v>
       </c>
       <c r="AE3" t="n">
-        <v>114.5775656125489</v>
+        <v>114.58</v>
       </c>
       <c r="AF3" t="n">
-        <v>123.9268780741626</v>
+        <v>123.93</v>
       </c>
       <c r="AG3" t="n">
-        <v>127.8387613777254</v>
+        <v>127.84</v>
       </c>
       <c r="AH3" t="n">
-        <v>128.2480414514688</v>
+        <v>128.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>118.5676552996295</v>
+        <v>118.57</v>
       </c>
       <c r="AJ3" t="n">
-        <v>149.8330033023949</v>
+        <v>149.83</v>
       </c>
       <c r="AK3" t="n">
-        <v>170.2005524498932</v>
+        <v>170.2</v>
       </c>
       <c r="AL3" t="n">
-        <v>148.5212215628555</v>
+        <v>148.52</v>
       </c>
       <c r="AM3" t="n">
-        <v>146.2610570791897</v>
+        <v>146.26</v>
       </c>
       <c r="AN3" t="n">
-        <v>168.5670817861504</v>
+        <v>168.57</v>
       </c>
       <c r="AO3" t="n">
-        <v>106.7675768320623</v>
+        <v>106.77</v>
       </c>
       <c r="AP3" t="n">
-        <v>111.7695292566787</v>
+        <v>111.77</v>
       </c>
       <c r="AQ3" t="n">
-        <v>121.3061508341707</v>
+        <v>121.31</v>
       </c>
       <c r="AR3" t="n">
-        <v>112.4902306126024</v>
+        <v>112.49</v>
       </c>
       <c r="AS3" t="n">
-        <v>116.8818337189878</v>
+        <v>116.88</v>
       </c>
       <c r="AT3" t="n">
-        <v>125.8037086456461</v>
+        <v>125.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>121.2734368253732</v>
+        <v>121.27</v>
       </c>
       <c r="AV3" t="n">
-        <v>127.3525375522295</v>
+        <v>127.35</v>
       </c>
       <c r="AW3" t="n">
-        <v>132.9291968356193</v>
+        <v>132.93</v>
       </c>
       <c r="AX3" t="n">
-        <v>133.4316382790858</v>
+        <v>133.43</v>
       </c>
       <c r="AY3" t="n">
-        <v>134.7255835723045</v>
+        <v>134.73</v>
       </c>
       <c r="AZ3" t="n">
-        <v>138.5957004339144</v>
+        <v>138.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>136.0195288655232</v>
+        <v>136.02</v>
       </c>
       <c r="BB3" t="n">
-        <v>138.505856119009</v>
+        <v>138.51</v>
       </c>
       <c r="BC3" t="n">
-        <v>141.1337868700357</v>
+        <v>141.13</v>
       </c>
       <c r="BD3" t="n">
-        <v>133.8572245261487</v>
+        <v>133.86</v>
       </c>
       <c r="BE3" t="n">
-        <v>147.2813939708263</v>
+        <v>147.28</v>
       </c>
       <c r="BF3" t="n">
         <v>100</v>
       </c>
       <c r="BG3" t="n">
-        <v>99.93165593737589</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="BH3" t="n">
-        <v>98.92656197810402</v>
+        <v>98.93000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>99.23419023700703</v>
+        <v>99.23</v>
       </c>
       <c r="BJ3" t="n">
-        <v>98.0419280645296</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>96.51135551141789</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="BL3" t="n">
-        <v>99.98212875468829</v>
+        <v>99.98</v>
       </c>
       <c r="BM3" t="n">
-        <v>97.56871086666233</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="BN3" t="n">
-        <v>99.2289771845707</v>
+        <v>99.23</v>
       </c>
       <c r="BO3" t="n">
-        <v>101.1301708645189</v>
+        <v>101.13</v>
       </c>
       <c r="BP3" t="n">
-        <v>101.8525021706511</v>
+        <v>101.85</v>
       </c>
       <c r="BQ3" t="n">
         <v>100</v>
       </c>
       <c r="BR3" t="n">
-        <v>100.0618903458153</v>
+        <v>100.06</v>
       </c>
       <c r="BS3" t="n">
-        <v>98.86357063639572</v>
+        <v>98.86</v>
       </c>
       <c r="BT3" t="n">
-        <v>99.35740894577904</v>
+        <v>99.36</v>
       </c>
       <c r="BU3" t="n">
-        <v>97.20268087481145</v>
+        <v>97.2</v>
       </c>
       <c r="BV3" t="n">
-        <v>95.42845944102001</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="BW3" t="n">
-        <v>100.2207375053447</v>
+        <v>100.22</v>
       </c>
       <c r="BX3" t="n">
-        <v>97.72536824913362</v>
+        <v>97.73</v>
       </c>
       <c r="BY3" t="n">
-        <v>100.1308412658412</v>
+        <v>100.13</v>
       </c>
       <c r="BZ3" t="n">
-        <v>102.310383787913</v>
+        <v>102.31</v>
       </c>
       <c r="CA3" t="n">
-        <v>104.3275725036654</v>
+        <v>104.33</v>
       </c>
       <c r="CB3" t="n">
-        <v>2.563052866730388</v>
+        <v>2.56</v>
       </c>
       <c r="CC3" t="n">
-        <v>103.4472643815389</v>
+        <v>103.45</v>
       </c>
       <c r="CD3" t="n">
         <v>0</v>
@@ -1463,25 +1459,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Hammer</t>
-        </is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.858</v>
+        <v>0.99</v>
       </c>
       <c r="E4" t="n">
-        <v>100.9643849069264</v>
+        <v>101.96</v>
       </c>
       <c r="F4" t="n">
-        <v>102.4025073930131</v>
+        <v>104.09</v>
       </c>
       <c r="G4" t="n">
-        <v>27.64705618360762</v>
+        <v>39.45</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -1490,220 +1484,220 @@
         <v>100</v>
       </c>
       <c r="J4" t="n">
-        <v>101.497338876719</v>
+        <v>103.8</v>
       </c>
       <c r="K4" t="n">
-        <v>28.24851938378779</v>
+        <v>20.57</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>97.77514823298613</v>
+        <v>99.27</v>
       </c>
       <c r="N4" t="n">
-        <v>101.4381224860867</v>
+        <v>103.43</v>
       </c>
       <c r="O4" t="n">
-        <v>79.44575027046457</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>101.8610985489177</v>
+        <v>104.65</v>
       </c>
       <c r="R4" t="n">
-        <v>106.1839079732756</v>
+        <v>107.3</v>
       </c>
       <c r="S4" t="n">
-        <v>115.0579439643202</v>
+        <v>117.59</v>
       </c>
       <c r="T4" t="n">
-        <v>117.2828021854366</v>
+        <v>132.79</v>
       </c>
       <c r="U4" t="n">
-        <v>122.9253013146168</v>
+        <v>135.58</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3468434694905866</v>
+        <v>0.9</v>
       </c>
       <c r="W4" t="n">
-        <v>1.798809566283605</v>
+        <v>1.64</v>
       </c>
       <c r="X4" t="n">
-        <v>5.624250393803055</v>
+        <v>5.18</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.252945465636911</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.853142939175644</v>
+        <v>11.08</v>
       </c>
       <c r="AA4" t="n">
-        <v>94.20522923003654</v>
+        <v>100.43</v>
       </c>
       <c r="AB4" t="n">
-        <v>92.03959385365491</v>
+        <v>100.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>86.99771350509981</v>
+        <v>109.16</v>
       </c>
       <c r="AD4" t="n">
-        <v>93.08857268232694</v>
+        <v>77.11</v>
       </c>
       <c r="AE4" t="n">
-        <v>148.9968125765601</v>
+        <v>114.58</v>
       </c>
       <c r="AF4" t="n">
-        <v>146.7517486705061</v>
+        <v>123.93</v>
       </c>
       <c r="AG4" t="n">
-        <v>127.390830221901</v>
+        <v>127.84</v>
       </c>
       <c r="AH4" t="n">
-        <v>112.2654519298585</v>
+        <v>128.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>103.3512069976236</v>
+        <v>118.57</v>
       </c>
       <c r="AJ4" t="n">
-        <v>121.9289269708131</v>
+        <v>149.83</v>
       </c>
       <c r="AK4" t="n">
-        <v>121.8842778290222</v>
+        <v>170.2</v>
       </c>
       <c r="AL4" t="n">
-        <v>127.4349540796709</v>
+        <v>148.52</v>
       </c>
       <c r="AM4" t="n">
-        <v>136.1956409830796</v>
+        <v>146.26</v>
       </c>
       <c r="AN4" t="n">
-        <v>134.4435561307999</v>
+        <v>168.57</v>
       </c>
       <c r="AO4" t="n">
-        <v>105.05371975422</v>
+        <v>106.77</v>
       </c>
       <c r="AP4" t="n">
-        <v>110.3197710910551</v>
+        <v>111.77</v>
       </c>
       <c r="AQ4" t="n">
-        <v>115.1505800205124</v>
+        <v>121.31</v>
       </c>
       <c r="AR4" t="n">
-        <v>112.0379002971533</v>
+        <v>112.49</v>
       </c>
       <c r="AS4" t="n">
-        <v>114.6104403756778</v>
+        <v>116.88</v>
       </c>
       <c r="AT4" t="n">
-        <v>118.5428479153346</v>
+        <v>125.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>117.1829804542023</v>
+        <v>121.27</v>
       </c>
       <c r="AV4" t="n">
-        <v>118.6092544988806</v>
+        <v>127.35</v>
       </c>
       <c r="AW4" t="n">
-        <v>121.3120719276165</v>
+        <v>132.93</v>
       </c>
       <c r="AX4" t="n">
-        <v>120.0355285435588</v>
+        <v>133.43</v>
       </c>
       <c r="AY4" t="n">
-        <v>122.4752554549913</v>
+        <v>134.73</v>
       </c>
       <c r="AZ4" t="n">
-        <v>123.6976573092291</v>
+        <v>138.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>124.9149823664238</v>
+        <v>136.02</v>
       </c>
       <c r="BB4" t="n">
-        <v>124.0148893563524</v>
+        <v>138.51</v>
       </c>
       <c r="BC4" t="n">
-        <v>126.4453100973595</v>
+        <v>141.13</v>
       </c>
       <c r="BD4" t="n">
-        <v>123.6015572716727</v>
+        <v>133.86</v>
       </c>
       <c r="BE4" t="n">
-        <v>128.9389229884224</v>
+        <v>147.28</v>
       </c>
       <c r="BF4" t="n">
         <v>100</v>
       </c>
       <c r="BG4" t="n">
-        <v>100.1117625192066</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="BH4" t="n">
-        <v>99.24649602460785</v>
+        <v>98.93000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>97.8321797424731</v>
+        <v>99.23</v>
       </c>
       <c r="BJ4" t="n">
-        <v>96.37400050405725</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>96.73121953981743</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="BL4" t="n">
-        <v>99.21585796969377</v>
+        <v>99.98</v>
       </c>
       <c r="BM4" t="n">
-        <v>100.4737932772611</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="BN4" t="n">
-        <v>100.8663153913793</v>
+        <v>99.23</v>
       </c>
       <c r="BO4" t="n">
-        <v>99.81057510937133</v>
+        <v>101.13</v>
       </c>
       <c r="BP4" t="n">
-        <v>101.1781751425839</v>
+        <v>101.85</v>
       </c>
       <c r="BQ4" t="n">
         <v>100</v>
       </c>
       <c r="BR4" t="n">
-        <v>100.1874685092555</v>
+        <v>100.06</v>
       </c>
       <c r="BS4" t="n">
-        <v>98.75541982481273</v>
+        <v>98.86</v>
       </c>
       <c r="BT4" t="n">
-        <v>96.98794132433514</v>
+        <v>99.36</v>
       </c>
       <c r="BU4" t="n">
-        <v>94.51158982560813</v>
+        <v>97.2</v>
       </c>
       <c r="BV4" t="n">
-        <v>95.30287809016525</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="BW4" t="n">
-        <v>99.25606952441258</v>
+        <v>100.22</v>
       </c>
       <c r="BX4" t="n">
-        <v>100.4061009863531</v>
+        <v>97.73</v>
       </c>
       <c r="BY4" t="n">
-        <v>101.0580095568972</v>
+        <v>100.13</v>
       </c>
       <c r="BZ4" t="n">
-        <v>99.99654351708023</v>
+        <v>102.31</v>
       </c>
       <c r="CA4" t="n">
-        <v>102.2252121903081</v>
+        <v>104.33</v>
       </c>
       <c r="CB4" t="n">
-        <v>19.14063538036321</v>
+        <v>2.56</v>
       </c>
       <c r="CC4" t="n">
-        <v>100.9897624380398</v>
+        <v>103.45</v>
       </c>
       <c r="CD4" t="n">
         <v>0</v>
@@ -1712,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="CF4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -1723,247 +1717,245 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Hammer</t>
-        </is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.99</v>
+        <v>0.86</v>
       </c>
       <c r="E5" t="n">
-        <v>100.858210337586</v>
+        <v>100.96</v>
       </c>
       <c r="F5" t="n">
-        <v>102.6919959800876</v>
+        <v>102.4</v>
       </c>
       <c r="G5" t="n">
-        <v>7.60009765625</v>
+        <v>27.65</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>100</v>
       </c>
       <c r="J5" t="n">
-        <v>101.6724116105583</v>
+        <v>101.5</v>
       </c>
       <c r="K5" t="n">
-        <v>17.10524554617125</v>
+        <v>28.25</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>101.701747256121</v>
+        <v>97.78</v>
       </c>
       <c r="N5" t="n">
-        <v>103.4768616074971</v>
+        <v>101.44</v>
       </c>
       <c r="O5" t="n">
-        <v>44.21493335351013</v>
+        <v>79.45</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>103.0880887541506</v>
+        <v>101.86</v>
       </c>
       <c r="R5" t="n">
-        <v>105.8314361046471</v>
+        <v>106.18</v>
       </c>
       <c r="S5" t="n">
-        <v>108.0099743433421</v>
+        <v>115.06</v>
       </c>
       <c r="T5" t="n">
-        <v>108.4354139555072</v>
+        <v>117.28</v>
       </c>
       <c r="U5" t="n">
-        <v>109.4696717440875</v>
+        <v>122.93</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6968363056427194</v>
+        <v>0.35</v>
       </c>
       <c r="W5" t="n">
-        <v>1.660009965424125</v>
+        <v>1.8</v>
       </c>
       <c r="X5" t="n">
-        <v>2.629421272998699</v>
+        <v>5.62</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.252660837951285</v>
+        <v>6.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.498697471945422</v>
+        <v>6.85</v>
       </c>
       <c r="AA5" t="n">
-        <v>101.8337856425016</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="AB5" t="n">
-        <v>98.36426634079962</v>
+        <v>92.04000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>90.48631919129873</v>
+        <v>87</v>
       </c>
       <c r="AD5" t="n">
-        <v>78.60339046639648</v>
+        <v>93.09</v>
       </c>
       <c r="AE5" t="n">
-        <v>97.51903384547276</v>
+        <v>149</v>
       </c>
       <c r="AF5" t="n">
-        <v>89.92091325015541</v>
+        <v>146.75</v>
       </c>
       <c r="AG5" t="n">
-        <v>87.93039176656443</v>
+        <v>127.39</v>
       </c>
       <c r="AH5" t="n">
-        <v>90.85147516087983</v>
+        <v>112.27</v>
       </c>
       <c r="AI5" t="n">
-        <v>86.79554673816025</v>
+        <v>103.35</v>
       </c>
       <c r="AJ5" t="n">
-        <v>84.53797050504183</v>
+        <v>121.93</v>
       </c>
       <c r="AK5" t="n">
-        <v>86.50921999639888</v>
+        <v>121.88</v>
       </c>
       <c r="AL5" t="n">
-        <v>93.27754366895783</v>
+        <v>127.43</v>
       </c>
       <c r="AM5" t="n">
-        <v>111.0110802942778</v>
+        <v>136.2</v>
       </c>
       <c r="AN5" t="n">
-        <v>124.9023322965001</v>
+        <v>134.44</v>
       </c>
       <c r="AO5" t="n">
-        <v>105.0597776736374</v>
+        <v>105.05</v>
       </c>
       <c r="AP5" t="n">
-        <v>106.634633992212</v>
+        <v>110.32</v>
       </c>
       <c r="AQ5" t="n">
-        <v>107.8130253847911</v>
+        <v>115.15</v>
       </c>
       <c r="AR5" t="n">
-        <v>107.8764742113261</v>
+        <v>112.04</v>
       </c>
       <c r="AS5" t="n">
-        <v>107.2713249493006</v>
+        <v>114.61</v>
       </c>
       <c r="AT5" t="n">
-        <v>109.1747947819934</v>
+        <v>118.54</v>
       </c>
       <c r="AU5" t="n">
-        <v>106.6661756872751</v>
+        <v>117.18</v>
       </c>
       <c r="AV5" t="n">
-        <v>108.1706141447059</v>
+        <v>118.61</v>
       </c>
       <c r="AW5" t="n">
-        <v>111.7424617967853</v>
+        <v>121.31</v>
       </c>
       <c r="AX5" t="n">
-        <v>109.6750526021367</v>
+        <v>120.04</v>
       </c>
       <c r="AY5" t="n">
-        <v>111.0782646146862</v>
+        <v>122.48</v>
       </c>
       <c r="AZ5" t="n">
-        <v>115.6348553806398</v>
+        <v>123.7</v>
       </c>
       <c r="BA5" t="n">
-        <v>112.4814766272357</v>
+        <v>124.91</v>
       </c>
       <c r="BB5" t="n">
-        <v>115.3143094488648</v>
+        <v>124.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>117.826595219465</v>
+        <v>126.45</v>
       </c>
       <c r="BD5" t="n">
-        <v>113.7222895950909</v>
+        <v>123.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>112.6731809017672</v>
+        <v>128.94</v>
       </c>
       <c r="BF5" t="n">
         <v>100</v>
       </c>
       <c r="BG5" t="n">
-        <v>100.1860967212266</v>
+        <v>100.11</v>
       </c>
       <c r="BH5" t="n">
-        <v>100.2741852286333</v>
+        <v>99.25</v>
       </c>
       <c r="BI5" t="n">
-        <v>99.4279131148817</v>
+        <v>97.83</v>
       </c>
       <c r="BJ5" t="n">
-        <v>99.96122984974447</v>
+        <v>96.37</v>
       </c>
       <c r="BK5" t="n">
-        <v>97.68821620658917</v>
+        <v>96.73</v>
       </c>
       <c r="BL5" t="n">
-        <v>100.5154915524992</v>
+        <v>99.22</v>
       </c>
       <c r="BM5" t="n">
-        <v>101.2992695158487</v>
+        <v>100.47</v>
       </c>
       <c r="BN5" t="n">
-        <v>102.3586260101063</v>
+        <v>100.87</v>
       </c>
       <c r="BO5" t="n">
-        <v>102.9420410485024</v>
+        <v>99.81</v>
       </c>
       <c r="BP5" t="n">
-        <v>104.0776959868957</v>
+        <v>101.18</v>
       </c>
       <c r="BQ5" t="n">
         <v>100</v>
       </c>
       <c r="BR5" t="n">
-        <v>100.0024773952283</v>
+        <v>100.19</v>
       </c>
       <c r="BS5" t="n">
-        <v>100.4717060611434</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="BT5" t="n">
-        <v>99.8715758352367</v>
+        <v>96.98999999999999</v>
       </c>
       <c r="BU5" t="n">
-        <v>101.8123522425598</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="BV5" t="n">
-        <v>98.30757203756498</v>
+        <v>95.3</v>
       </c>
       <c r="BW5" t="n">
-        <v>101.0147394172266</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="BX5" t="n">
-        <v>101.8553604910347</v>
+        <v>100.41</v>
       </c>
       <c r="BY5" t="n">
-        <v>103.4544315262139</v>
+        <v>101.06</v>
       </c>
       <c r="BZ5" t="n">
-        <v>104.6497455289689</v>
+        <v>100</v>
       </c>
       <c r="CA5" t="n">
-        <v>105.9194064127667</v>
+        <v>102.23</v>
       </c>
       <c r="CB5" t="n">
-        <v>34.81796401948304</v>
+        <v>19.14</v>
       </c>
       <c r="CC5" t="n">
-        <v>101.4743596272571</v>
+        <v>100.99</v>
       </c>
       <c r="CD5" t="n">
         <v>0</v>
@@ -1972,7 +1964,7 @@
         <v>0</v>
       </c>
       <c r="CF5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1983,247 +1975,245 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Hammer</t>
-        </is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.736</v>
+        <v>0.99</v>
       </c>
       <c r="E6" t="n">
-        <v>102.3969559669065</v>
+        <v>100.86</v>
       </c>
       <c r="F6" t="n">
-        <v>105.3736876879702</v>
+        <v>102.69</v>
       </c>
       <c r="G6" t="n">
-        <v>5.225692808420259</v>
+        <v>7.6</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>100</v>
       </c>
       <c r="J6" t="n">
-        <v>104.0302711604448</v>
+        <v>101.67</v>
       </c>
       <c r="K6" t="n">
-        <v>27.71900330874086</v>
+        <v>17.11</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>101.2161502579203</v>
+        <v>101.7</v>
       </c>
       <c r="N6" t="n">
-        <v>105.4231873187729</v>
+        <v>103.48</v>
       </c>
       <c r="O6" t="n">
-        <v>62.52090065138226</v>
+        <v>44.21</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>105.1686439906283</v>
+        <v>103.09</v>
       </c>
       <c r="R6" t="n">
-        <v>106.5898379458905</v>
+        <v>105.83</v>
       </c>
       <c r="S6" t="n">
-        <v>111.7584711475844</v>
+        <v>108.01</v>
       </c>
       <c r="T6" t="n">
-        <v>115.491766101082</v>
+        <v>108.44</v>
       </c>
       <c r="U6" t="n">
-        <v>118.2705316657381</v>
+        <v>109.47</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3217152334142881</v>
+        <v>0.7</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9159765755472358</v>
+        <v>1.66</v>
       </c>
       <c r="X6" t="n">
-        <v>2.098484276469901</v>
+        <v>2.63</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.799397856748029</v>
+        <v>2.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.969716504903118</v>
+        <v>2.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>102.9767425099981</v>
+        <v>101.83</v>
       </c>
       <c r="AB6" t="n">
-        <v>106.8090259361666</v>
+        <v>98.36</v>
       </c>
       <c r="AC6" t="n">
-        <v>102.2343235704986</v>
+        <v>90.48999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>97.3768000797518</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="AE6" t="n">
-        <v>75.50277444531552</v>
+        <v>97.52</v>
       </c>
       <c r="AF6" t="n">
-        <v>74.4307490702294</v>
+        <v>89.92</v>
       </c>
       <c r="AG6" t="n">
-        <v>103.7616906685783</v>
+        <v>87.93000000000001</v>
       </c>
       <c r="AH6" t="n">
-        <v>89.11467798230821</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="AI6" t="n">
-        <v>81.97338867493845</v>
+        <v>86.8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>165.4628885546425</v>
+        <v>84.54000000000001</v>
       </c>
       <c r="AK6" t="n">
-        <v>80.71560012416946</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="AL6" t="n">
-        <v>83.8067430123313</v>
+        <v>93.28</v>
       </c>
       <c r="AM6" t="n">
-        <v>80.55902440780828</v>
+        <v>111.01</v>
       </c>
       <c r="AN6" t="n">
-        <v>87.43608082798548</v>
+        <v>124.9</v>
       </c>
       <c r="AO6" t="n">
-        <v>105.9195430325278</v>
+        <v>105.06</v>
       </c>
       <c r="AP6" t="n">
-        <v>107.7168974995134</v>
+        <v>106.63</v>
       </c>
       <c r="AQ6" t="n">
-        <v>112.0596820112645</v>
+        <v>107.81</v>
       </c>
       <c r="AR6" t="n">
-        <v>107.3916478112057</v>
+        <v>107.88</v>
       </c>
       <c r="AS6" t="n">
-        <v>110.2658619991723</v>
+        <v>107.27</v>
       </c>
       <c r="AT6" t="n">
-        <v>113.2595684900973</v>
+        <v>109.17</v>
       </c>
       <c r="AU6" t="n">
-        <v>113.1400761871388</v>
+        <v>106.67</v>
       </c>
       <c r="AV6" t="n">
-        <v>115.206115038523</v>
+        <v>108.17</v>
       </c>
       <c r="AW6" t="n">
-        <v>114.8713198405482</v>
+        <v>111.74</v>
       </c>
       <c r="AX6" t="n">
-        <v>117.2721538899071</v>
+        <v>109.68</v>
       </c>
       <c r="AY6" t="n">
-        <v>116.2532749810223</v>
+        <v>111.08</v>
       </c>
       <c r="AZ6" t="n">
-        <v>115.3613149380564</v>
+        <v>115.63</v>
       </c>
       <c r="BA6" t="n">
-        <v>115.2343960721374</v>
+        <v>112.48</v>
       </c>
       <c r="BB6" t="n">
-        <v>114.5365246425734</v>
+        <v>115.31</v>
       </c>
       <c r="BC6" t="n">
-        <v>115.3436388874623</v>
+        <v>117.83</v>
       </c>
       <c r="BD6" t="n">
-        <v>113.7112410770118</v>
+        <v>113.72</v>
       </c>
       <c r="BE6" t="n">
-        <v>107.9836721076701</v>
+        <v>112.67</v>
       </c>
       <c r="BF6" t="n">
         <v>100</v>
       </c>
       <c r="BG6" t="n">
-        <v>98.55982788912586</v>
+        <v>100.19</v>
       </c>
       <c r="BH6" t="n">
-        <v>98.12079927777705</v>
+        <v>100.27</v>
       </c>
       <c r="BI6" t="n">
-        <v>98.39667684419501</v>
+        <v>99.43000000000001</v>
       </c>
       <c r="BJ6" t="n">
-        <v>98.33497891351838</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="BK6" t="n">
-        <v>96.86264021536209</v>
+        <v>97.69</v>
       </c>
       <c r="BL6" t="n">
-        <v>99.74050776090651</v>
+        <v>100.52</v>
       </c>
       <c r="BM6" t="n">
-        <v>98.90513544851549</v>
+        <v>101.3</v>
       </c>
       <c r="BN6" t="n">
-        <v>100.2291756081222</v>
+        <v>102.36</v>
       </c>
       <c r="BO6" t="n">
-        <v>100.5489764229486</v>
+        <v>102.94</v>
       </c>
       <c r="BP6" t="n">
-        <v>101.8694601359333</v>
+        <v>104.08</v>
       </c>
       <c r="BQ6" t="n">
         <v>100</v>
       </c>
       <c r="BR6" t="n">
-        <v>98.64812916662981</v>
+        <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>97.76091607464529</v>
+        <v>100.47</v>
       </c>
       <c r="BT6" t="n">
-        <v>97.88826331773718</v>
+        <v>99.87</v>
       </c>
       <c r="BU6" t="n">
-        <v>97.12093680399204</v>
+        <v>101.81</v>
       </c>
       <c r="BV6" t="n">
-        <v>96.0540617300815</v>
+        <v>98.31</v>
       </c>
       <c r="BW6" t="n">
-        <v>99.4256844074889</v>
+        <v>101.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>97.48640291783245</v>
+        <v>101.86</v>
       </c>
       <c r="BY6" t="n">
-        <v>98.81257499565136</v>
+        <v>103.45</v>
       </c>
       <c r="BZ6" t="n">
-        <v>99.09418028831743</v>
+        <v>104.65</v>
       </c>
       <c r="CA6" t="n">
-        <v>100.6017914767923</v>
+        <v>105.92</v>
       </c>
       <c r="CB6" t="n">
-        <v>19.26448890751337</v>
+        <v>34.82</v>
       </c>
       <c r="CC6" t="n">
-        <v>103.3585521077478</v>
+        <v>101.47</v>
       </c>
       <c r="CD6" t="n">
         <v>0</v>
@@ -2243,25 +2233,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-12-24</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bullish Engulfing</t>
-        </is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.88</v>
+        <v>0.74</v>
       </c>
       <c r="E7" t="n">
-        <v>99.06990812440016</v>
+        <v>102.4</v>
       </c>
       <c r="F7" t="n">
-        <v>101.658657044476</v>
+        <v>105.37</v>
       </c>
       <c r="G7" t="n">
-        <v>50.59881538942987</v>
+        <v>5.23</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -2270,220 +2258,220 @@
         <v>100</v>
       </c>
       <c r="J7" t="n">
-        <v>102.0151842804438</v>
+        <v>104.03</v>
       </c>
       <c r="K7" t="n">
-        <v>83.46176192683971</v>
+        <v>27.72</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>100.4262928488177</v>
+        <v>101.22</v>
       </c>
       <c r="N7" t="n">
-        <v>101.8989279701684</v>
+        <v>105.42</v>
       </c>
       <c r="O7" t="n">
-        <v>3.157776385743426</v>
+        <v>62.52</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>102.0771915881523</v>
+        <v>105.17</v>
       </c>
       <c r="R7" t="n">
-        <v>107.4252065678311</v>
+        <v>106.59</v>
       </c>
       <c r="S7" t="n">
-        <v>113.8738128226098</v>
+        <v>111.76</v>
       </c>
       <c r="T7" t="n">
-        <v>117.1291196038534</v>
+        <v>115.49</v>
       </c>
       <c r="U7" t="n">
-        <v>114.6953889530486</v>
+        <v>118.27</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8913358299464704</v>
+        <v>0.32</v>
       </c>
       <c r="W7" t="n">
-        <v>2.437900505064959</v>
+        <v>0.92</v>
       </c>
       <c r="X7" t="n">
-        <v>5.579978534676422</v>
+        <v>2.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.993143621471189</v>
+        <v>3.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.889048044184127</v>
+        <v>4.97</v>
       </c>
       <c r="AA7" t="n">
-        <v>99.59695841323737</v>
+        <v>102.98</v>
       </c>
       <c r="AB7" t="n">
-        <v>103.0537919012046</v>
+        <v>106.81</v>
       </c>
       <c r="AC7" t="n">
-        <v>106.9446528897617</v>
+        <v>102.23</v>
       </c>
       <c r="AD7" t="n">
-        <v>116.3772972595798</v>
+        <v>97.38</v>
       </c>
       <c r="AE7" t="n">
-        <v>167.2636685053807</v>
+        <v>75.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>138.5302149980272</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="AG7" t="n">
-        <v>111.7339873275722</v>
+        <v>103.76</v>
       </c>
       <c r="AH7" t="n">
-        <v>105.5272312782544</v>
+        <v>89.11</v>
       </c>
       <c r="AI7" t="n">
-        <v>108.178280479974</v>
+        <v>81.97</v>
       </c>
       <c r="AJ7" t="n">
-        <v>44.76353311619487</v>
+        <v>165.46</v>
       </c>
       <c r="AK7" t="n">
-        <v>65.81461739016069</v>
+        <v>80.72</v>
       </c>
       <c r="AL7" t="n">
-        <v>88.26446536744625</v>
+        <v>83.81</v>
       </c>
       <c r="AM7" t="n">
-        <v>101.0227685928035</v>
+        <v>80.56</v>
       </c>
       <c r="AN7" t="n">
-        <v>95.12676296061335</v>
+        <v>87.44</v>
       </c>
       <c r="AO7" t="n">
-        <v>105.8905570427612</v>
+        <v>105.92</v>
       </c>
       <c r="AP7" t="n">
-        <v>110.0945555265802</v>
+        <v>107.72</v>
       </c>
       <c r="AQ7" t="n">
-        <v>113.7091108639334</v>
+        <v>112.06</v>
       </c>
       <c r="AR7" t="n">
-        <v>112.808862444422</v>
+        <v>107.39</v>
       </c>
       <c r="AS7" t="n">
-        <v>114.3745120753407</v>
+        <v>110.27</v>
       </c>
       <c r="AT7" t="n">
-        <v>114.8910981135847</v>
+        <v>113.26</v>
       </c>
       <c r="AU7" t="n">
-        <v>115.9401617062594</v>
+        <v>113.14</v>
       </c>
       <c r="AV7" t="n">
-        <v>117.015187237115</v>
+        <v>115.21</v>
       </c>
       <c r="AW7" t="n">
-        <v>114.4663581084637</v>
+        <v>114.87</v>
       </c>
       <c r="AX7" t="n">
-        <v>118.0902127679705</v>
+        <v>117.27</v>
       </c>
       <c r="AY7" t="n">
-        <v>115.4076841518286</v>
+        <v>116.25</v>
       </c>
       <c r="AZ7" t="n">
-        <v>112.9677521789188</v>
+        <v>115.36</v>
       </c>
       <c r="BA7" t="n">
-        <v>112.7251555356867</v>
+        <v>115.23</v>
       </c>
       <c r="BB7" t="n">
-        <v>111.9175289798124</v>
+        <v>114.54</v>
       </c>
       <c r="BC7" t="n">
-        <v>107.8197134276038</v>
+        <v>115.34</v>
       </c>
       <c r="BD7" t="n">
-        <v>106.3571497926487</v>
+        <v>113.71</v>
       </c>
       <c r="BE7" t="n">
-        <v>75.60618251767646</v>
+        <v>107.98</v>
       </c>
       <c r="BF7" t="n">
         <v>100</v>
       </c>
       <c r="BG7" t="n">
-        <v>98.19223149680978</v>
+        <v>98.56</v>
       </c>
       <c r="BH7" t="n">
-        <v>100.1749959296692</v>
+        <v>98.12</v>
       </c>
       <c r="BI7" t="n">
-        <v>99.91506872836399</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="BJ7" t="n">
-        <v>100.1629102404349</v>
+        <v>98.33</v>
       </c>
       <c r="BK7" t="n">
-        <v>99.12798720646933</v>
+        <v>96.86</v>
       </c>
       <c r="BL7" t="n">
-        <v>98.85430899687809</v>
+        <v>99.73999999999999</v>
       </c>
       <c r="BM7" t="n">
-        <v>97.16077653018974</v>
+        <v>98.91</v>
       </c>
       <c r="BN7" t="n">
-        <v>96.47353331066559</v>
+        <v>100.23</v>
       </c>
       <c r="BO7" t="n">
-        <v>99.2817947806314</v>
+        <v>100.55</v>
       </c>
       <c r="BP7" t="n">
-        <v>99.54039619395373</v>
+        <v>101.87</v>
       </c>
       <c r="BQ7" t="n">
         <v>100</v>
       </c>
       <c r="BR7" t="n">
-        <v>97.66717976071997</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="BS7" t="n">
-        <v>100.9332642915839</v>
+        <v>97.76000000000001</v>
       </c>
       <c r="BT7" t="n">
-        <v>98.02973854783123</v>
+        <v>97.89</v>
       </c>
       <c r="BU7" t="n">
-        <v>97.39270027759765</v>
+        <v>97.12</v>
       </c>
       <c r="BV7" t="n">
-        <v>95.44556524288518</v>
+        <v>96.05</v>
       </c>
       <c r="BW7" t="n">
-        <v>98.51070710119004</v>
+        <v>99.43000000000001</v>
       </c>
       <c r="BX7" t="n">
-        <v>96.22880798953656</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="BY7" t="n">
-        <v>95.64140953050327</v>
+        <v>98.81</v>
       </c>
       <c r="BZ7" t="n">
-        <v>98.36454742604587</v>
+        <v>99.09</v>
       </c>
       <c r="CA7" t="n">
-        <v>96.92457176926591</v>
+        <v>100.6</v>
       </c>
       <c r="CB7" t="n">
-        <v>19.66198984029427</v>
+        <v>19.26</v>
       </c>
       <c r="CC7" t="n">
-        <v>101.8679184029718</v>
+        <v>103.36</v>
       </c>
       <c r="CD7" t="n">
         <v>0</v>
@@ -2492,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="CF7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -2503,25 +2491,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Hammer</t>
-        </is>
+          <t>2024-12-24</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.876</v>
+        <v>0.88</v>
       </c>
       <c r="E8" t="n">
-        <v>102.3552849063574</v>
+        <v>99.06999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>104.3379934398376</v>
+        <v>101.66</v>
       </c>
       <c r="G8" t="n">
-        <v>65.10051306208973</v>
+        <v>50.6</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -2530,220 +2516,220 @@
         <v>100</v>
       </c>
       <c r="J8" t="n">
-        <v>102.0492360402641</v>
+        <v>102.02</v>
       </c>
       <c r="K8" t="n">
-        <v>26.62359859500324</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>99.93346234099464</v>
+        <v>100.43</v>
       </c>
       <c r="N8" t="n">
-        <v>101.4637371281254</v>
+        <v>101.9</v>
       </c>
       <c r="O8" t="n">
-        <v>31.30435936390837</v>
+        <v>3.16</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>104.0851625182829</v>
+        <v>102.08</v>
       </c>
       <c r="R8" t="n">
-        <v>104.9234821997549</v>
+        <v>107.43</v>
       </c>
       <c r="S8" t="n">
-        <v>110.1530234178245</v>
+        <v>113.87</v>
       </c>
       <c r="T8" t="n">
-        <v>104.5508956746562</v>
+        <v>117.13</v>
       </c>
       <c r="U8" t="n">
-        <v>100.7717921746881</v>
+        <v>114.7</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7917514419453866</v>
+        <v>0.89</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8621026222172783</v>
+        <v>2.44</v>
       </c>
       <c r="X8" t="n">
-        <v>1.849593717953805</v>
+        <v>5.58</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.636224523355996</v>
+        <v>5.99</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.064929698256723</v>
+        <v>5.89</v>
       </c>
       <c r="AA8" t="n">
-        <v>100.10645619352</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AB8" t="n">
-        <v>103.4597450716295</v>
+        <v>103.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>110.1131048833099</v>
+        <v>106.94</v>
       </c>
       <c r="AD8" t="n">
-        <v>107.0392558990244</v>
+        <v>116.38</v>
       </c>
       <c r="AE8" t="n">
-        <v>60.0874213650728</v>
+        <v>167.26</v>
       </c>
       <c r="AF8" t="n">
-        <v>84.64071591009777</v>
+        <v>138.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>91.96373194719277</v>
+        <v>111.73</v>
       </c>
       <c r="AH8" t="n">
-        <v>97.14108508815971</v>
+        <v>105.53</v>
       </c>
       <c r="AI8" t="n">
-        <v>89.29715880563514</v>
+        <v>108.18</v>
       </c>
       <c r="AJ8" t="n">
-        <v>98.20136448211701</v>
+        <v>44.76</v>
       </c>
       <c r="AK8" t="n">
-        <v>143.0269647656458</v>
+        <v>65.81</v>
       </c>
       <c r="AL8" t="n">
-        <v>108.9887474526714</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="AM8" t="n">
-        <v>105.3220709412564</v>
+        <v>101.02</v>
       </c>
       <c r="AN8" t="n">
-        <v>93.73726335686227</v>
+        <v>95.13</v>
       </c>
       <c r="AO8" t="n">
-        <v>104.628074892125</v>
+        <v>105.89</v>
       </c>
       <c r="AP8" t="n">
-        <v>105.6207570694232</v>
+        <v>110.09</v>
       </c>
       <c r="AQ8" t="n">
-        <v>104.2222195375237</v>
+        <v>113.71</v>
       </c>
       <c r="AR8" t="n">
-        <v>105.1124414356419</v>
+        <v>112.81</v>
       </c>
       <c r="AS8" t="n">
-        <v>105.8163660103222</v>
+        <v>114.37</v>
       </c>
       <c r="AT8" t="n">
-        <v>103.4983341727528</v>
+        <v>114.89</v>
       </c>
       <c r="AU8" t="n">
-        <v>106.5202905850025</v>
+        <v>115.94</v>
       </c>
       <c r="AV8" t="n">
-        <v>104.5735158391405</v>
+        <v>117.02</v>
       </c>
       <c r="AW8" t="n">
-        <v>100.0745147669644</v>
+        <v>114.47</v>
       </c>
       <c r="AX8" t="n">
-        <v>102.6267410932785</v>
+        <v>118.09</v>
       </c>
       <c r="AY8" t="n">
-        <v>101.1803023351835</v>
+        <v>115.41</v>
       </c>
       <c r="AZ8" t="n">
-        <v>95.35994396379881</v>
+        <v>112.97</v>
       </c>
       <c r="BA8" t="n">
-        <v>99.73386357708851</v>
+        <v>112.73</v>
       </c>
       <c r="BB8" t="n">
-        <v>95.5755136947883</v>
+        <v>111.92</v>
       </c>
       <c r="BC8" t="n">
-        <v>90.67997142352723</v>
+        <v>107.82</v>
       </c>
       <c r="BD8" t="n">
-        <v>94.91443555527221</v>
+        <v>106.36</v>
       </c>
       <c r="BE8" t="n">
-        <v>71.68882093725105</v>
+        <v>75.61</v>
       </c>
       <c r="BF8" t="n">
         <v>100</v>
       </c>
       <c r="BG8" t="n">
-        <v>99.85393798175373</v>
+        <v>98.19</v>
       </c>
       <c r="BH8" t="n">
-        <v>98.55636695048993</v>
+        <v>100.17</v>
       </c>
       <c r="BI8" t="n">
-        <v>98.95407535437528</v>
+        <v>99.92</v>
       </c>
       <c r="BJ8" t="n">
-        <v>98.9270234590029</v>
+        <v>100.16</v>
       </c>
       <c r="BK8" t="n">
-        <v>97.42370318041027</v>
+        <v>99.13</v>
       </c>
       <c r="BL8" t="n">
-        <v>101.1237102302982</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="BM8" t="n">
-        <v>102.0974509463518</v>
+        <v>97.16</v>
       </c>
       <c r="BN8" t="n">
-        <v>102.024137577378</v>
+        <v>96.47</v>
       </c>
       <c r="BO8" t="n">
-        <v>102.7648858747025</v>
+        <v>99.28</v>
       </c>
       <c r="BP8" t="n">
-        <v>105.0947736284644</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="BQ8" t="n">
         <v>100</v>
       </c>
       <c r="BR8" t="n">
-        <v>99.71962571845782</v>
+        <v>97.67</v>
       </c>
       <c r="BS8" t="n">
-        <v>97.51660594552801</v>
+        <v>100.93</v>
       </c>
       <c r="BT8" t="n">
-        <v>98.6038012002788</v>
+        <v>98.03</v>
       </c>
       <c r="BU8" t="n">
-        <v>97.2296272738173</v>
+        <v>97.39</v>
       </c>
       <c r="BV8" t="n">
-        <v>95.21097749991783</v>
+        <v>95.45</v>
       </c>
       <c r="BW8" t="n">
-        <v>102.0472687979631</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="BX8" t="n">
-        <v>104.3412550860204</v>
+        <v>96.23</v>
       </c>
       <c r="BY8" t="n">
-        <v>103.284255717482</v>
+        <v>95.64</v>
       </c>
       <c r="BZ8" t="n">
-        <v>104.913430780001</v>
+        <v>98.36</v>
       </c>
       <c r="CA8" t="n">
-        <v>108.3918146109794</v>
+        <v>96.92</v>
       </c>
       <c r="CB8" t="n">
-        <v>38.23075618406079</v>
+        <v>19.66</v>
       </c>
       <c r="CC8" t="n">
-        <v>101.3040528378454</v>
+        <v>101.87</v>
       </c>
       <c r="CD8" t="n">
         <v>0</v>
@@ -2752,6 +2738,264 @@
         <v>0</v>
       </c>
       <c r="CF8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SFM</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E9" t="n">
+        <v>102.36</v>
+      </c>
+      <c r="F9" t="n">
+        <v>104.34</v>
+      </c>
+      <c r="G9" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>100</v>
+      </c>
+      <c r="J9" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="K9" t="n">
+        <v>26.62</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>99.93000000000001</v>
+      </c>
+      <c r="N9" t="n">
+        <v>101.46</v>
+      </c>
+      <c r="O9" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>104.09</v>
+      </c>
+      <c r="R9" t="n">
+        <v>104.92</v>
+      </c>
+      <c r="S9" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="T9" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="U9" t="n">
+        <v>100.77</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>100.11</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>103.46</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>110.11</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>107.04</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>60.09</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>84.64</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>91.95999999999999</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>97.14</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>143.03</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>108.99</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>105.32</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>93.73999999999999</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>104.63</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>105.62</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>104.22</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>105.11</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>105.82</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>106.52</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>104.57</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>100.07</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>102.63</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>101.18</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>95.36</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>99.73</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>95.58</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>94.91</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>71.69</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>99.84999999999999</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>98.56</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>98.95</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>98.93000000000001</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>97.42</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>101.12</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>102.02</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>102.76</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>105.09</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>100</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>97.52</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>97.23</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>95.20999999999999</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>104.34</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>103.28</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>104.91</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>108.39</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>38.23</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF9" t="n">
         <v>1</v>
       </c>
     </row>
